--- a/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
+++ b/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELGRANO 1646\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA47A755-07FA-4551-8664-10719B7CD5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90BB971-2B50-48B3-B655-D18EB9D9A53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="168">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>TOTAL GASTOS DE ADMINISTRACION</t>
-  </si>
-  <si>
-    <t>Sr. Diego Britez (1)</t>
   </si>
   <si>
     <t>TOTAL GASTOS GENERALES / MANTENIMIENTO</t>
@@ -477,60 +474,24 @@
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Ingreso mes de MAYO</t>
   </si>
   <si>
     <t xml:space="preserve">Kromacolor </t>
   </si>
   <si>
-    <t>Servisur - cambio de luminarias 18/06</t>
-  </si>
-  <si>
-    <t>SA seguridad - 10/06 - Servicio tecnico realizado en motor de porton, se lubrica caja reductora</t>
-  </si>
-  <si>
-    <t>Zaffalon Veronica - Por vaciamiento de monta coches con agua y mucho residuo de aceite, extraido con bomba y balde por la pesadez de lo econtrado</t>
-  </si>
-  <si>
-    <t>Eba - Elcetrica de buenos aires</t>
-  </si>
-  <si>
-    <t>Casa ruan - materiales de trabajo</t>
-  </si>
-  <si>
-    <t>Ferreteria Arcamone - Yeso de 5 kilos</t>
-  </si>
-  <si>
     <t>Numero 1859135 Debito automatico 02/06</t>
   </si>
   <si>
     <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 04/06</t>
   </si>
   <si>
-    <t>Fotocopias Poliza</t>
-  </si>
-  <si>
-    <t>Servisur - canaleta en la pared para pasar corrugado para elevar el toma corriente en altura - reemplazo de 13 plafones, etc</t>
-  </si>
-  <si>
     <t>Debito 12/06</t>
   </si>
   <si>
     <t>Pago mis cuentas 12/06</t>
   </si>
   <si>
-    <t>SA seguridad - 10/06 - Servicio tecnico realizado en sistema, se repara visibilidad de la camara y se cambia balun de conexión</t>
-  </si>
-  <si>
-    <t>Cerrajeria Walter - Cambio de baterias control de acceso</t>
-  </si>
-  <si>
-    <t>Contessi - Cuota 1 de arreglo montavehiculos</t>
-  </si>
-  <si>
     <t>Contessi - Mantenimiento de ascensores</t>
   </si>
   <si>
@@ -540,24 +501,9 @@
     <t>Seguro de vida Sra. Monica</t>
   </si>
   <si>
-    <t>Doartero - Mano de obra de materiales colocacion para ventanales de pileta</t>
-  </si>
-  <si>
-    <t>Guido Alterini : diferencia colocacion cesped</t>
-  </si>
-  <si>
-    <t>Servisur - Instalacion electrica para aire acondicionado del SUM</t>
-  </si>
-  <si>
-    <t>Combustible comprado por el Sr Fabio Tolosa 19/05</t>
-  </si>
-  <si>
     <t>Subidos en jun de 2025</t>
   </si>
   <si>
-    <t>Debito 27/06</t>
-  </si>
-  <si>
     <t>Kromacolor - Compra de materiales para hall, gimnasio, membrana, recuplast para terraza, lija, etc</t>
   </si>
   <si>
@@ -567,15 +513,6 @@
     <t>Kromacolor</t>
   </si>
   <si>
-    <t>Leonardo Balcalazza - Pintura gimnasio, pasillo + cielo raso y sellado de aberturas salida a zona de tender</t>
-  </si>
-  <si>
-    <t>Leonardo Balcalazza - Pintura SUM (se tapo el agujero del aire original con durlock y se pinto)</t>
-  </si>
-  <si>
-    <t>Leonardo Balcalazza - Pintura hall</t>
-  </si>
-  <si>
     <t>QUEDARON PENDIENTES TRES PARA JULI</t>
   </si>
   <si>
@@ -585,9 +522,6 @@
     <t>PERÍODO: JULIO</t>
   </si>
   <si>
-    <t>Honorarios JULIO y SAC</t>
-  </si>
-  <si>
     <t>Energoup MES DE JULIO</t>
   </si>
   <si>
@@ -600,7 +534,37 @@
     <t>Fumigacion 07/07</t>
   </si>
   <si>
-    <t>Contessi Acortamiento de 16 cables de acero en el montacarga</t>
+    <t>Casa ruan - materiales de trabajo - plafones y dicroicas</t>
+  </si>
+  <si>
+    <t>Servisur - reemplazo de plafones y dicroicas</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Montoya Alejandra</t>
+  </si>
+  <si>
+    <t>Debito 27/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doartero - Mano de obra de impermeabilizacion terraza debajo de pileta </t>
+  </si>
+  <si>
+    <t>Contessi - Cuota 2  de arreglo montavehiculos</t>
+  </si>
+  <si>
+    <t>Riesgo Uno - Reemplazo de detector, verificacion de cableado, pulsadores y panel - Mano de obra y materiales</t>
+  </si>
+  <si>
+    <t>Limpieza de SUM - Sra. Monica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Diego Britez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Balcalazza - </t>
+  </si>
+  <si>
+    <t>Honorarios JULIO</t>
   </si>
 </sst>
 </file>
@@ -608,14 +572,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1324,11 +1288,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1338,7 +1302,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1350,7 +1314,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1361,12 +1325,12 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1418,7 +1382,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1426,7 +1390,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1442,17 +1406,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1465,12 +1429,12 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1478,54 +1442,54 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
@@ -1536,41 +1500,41 @@
     <xf numFmtId="10" fontId="2" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1579,48 +1543,107 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1630,142 +1653,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2131,33 +2085,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P150"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P137"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="97" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="64"/>
       <c r="B2" s="65" t="s">
         <v>0</v>
@@ -2166,118 +2120,118 @@
       <c r="D2" s="65"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="67"/>
       <c r="B3" s="68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="68"/>
       <c r="D3" s="68"/>
       <c r="E3" s="69"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="68"/>
       <c r="D4" s="68"/>
       <c r="E4" s="69"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" s="68"/>
       <c r="C6" s="68"/>
       <c r="D6" s="68"/>
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="71"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
       <c r="E7" s="72"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="206" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="207"/>
-      <c r="D14" s="208"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="209"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="211"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="209"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="211"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="212"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="214"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="199" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="201"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="202"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="204"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="202"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="204"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="205"/>
+      <c r="C17" s="206"/>
+      <c r="D17" s="207"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
       <c r="E21" s="146" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F21" s="145" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="121" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="130"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="121" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="182">
+      <c r="D23" s="180">
         <v>1869737.25</v>
       </c>
       <c r="E23" s="134">
@@ -2289,13 +2243,13 @@
         <v>151261.743525</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="121" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="182">
+      <c r="D24" s="180">
         <v>-406667.86</v>
       </c>
       <c r="E24" s="134">
@@ -2307,13 +2261,13 @@
         <v>-32899.429874000001</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="121" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="182">
+      <c r="D25" s="180">
         <v>0.61</v>
       </c>
       <c r="E25" s="134">
@@ -2325,15 +2279,15 @@
         <v>4.9348999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="121"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="182"/>
+      <c r="D26" s="180"/>
       <c r="E26" s="134"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="95" t="s">
         <v>3</v>
       </c>
@@ -2360,13 +2314,13 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="183">
+      <c r="D28" s="181">
         <v>0</v>
       </c>
       <c r="E28" s="134">
@@ -2379,11 +2333,11 @@
       </c>
       <c r="H28" s="150"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="182">
+      <c r="D29" s="180">
         <v>0</v>
       </c>
       <c r="E29" s="134">
@@ -2396,27 +2350,27 @@
       </c>
       <c r="H29" s="150"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="182"/>
+      <c r="D30" s="180"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="150"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="182"/>
+      <c r="D31" s="180"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="150"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="95"/>
       <c r="C32" s="95"/>
@@ -2441,13 +2395,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="183"/>
+      <c r="D33" s="181"/>
       <c r="E33" s="134">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2458,13 +2412,13 @@
       </c>
       <c r="H33" s="150"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="182"/>
+      <c r="D34" s="180"/>
       <c r="E34" s="134">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2475,13 +2429,13 @@
       </c>
       <c r="H34" s="150"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="94" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="182"/>
+      <c r="D35" s="180"/>
       <c r="E35" s="134">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2492,9 +2446,9 @@
       </c>
       <c r="H35" s="150"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" s="95"/>
       <c r="C36" s="95"/>
@@ -2512,36 +2466,36 @@
       </c>
       <c r="H36" s="150"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="129"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="182"/>
+      <c r="D37" s="180"/>
       <c r="E37" s="120"/>
       <c r="F37" s="120"/>
       <c r="H37" s="150"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="129"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="182"/>
+      <c r="D38" s="180"/>
       <c r="E38" s="120"/>
       <c r="F38" s="120"/>
       <c r="H38" s="150"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
       <c r="C39" s="111"/>
-      <c r="D39" s="182"/>
+      <c r="D39" s="180"/>
       <c r="E39" s="120"/>
       <c r="F39" s="120"/>
       <c r="H39" s="150"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B40" s="95"/>
       <c r="C40" s="95"/>
@@ -2556,13 +2510,13 @@
       </c>
       <c r="H40" s="150"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="94" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="113">
+      <c r="D41" s="195">
         <v>3567.21</v>
       </c>
       <c r="E41" s="134">
@@ -2575,13 +2529,13 @@
       </c>
       <c r="H41" s="150"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="94" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="113">
+      <c r="D42" s="195">
         <v>37000</v>
       </c>
       <c r="E42" s="134">
@@ -2594,11 +2548,11 @@
       </c>
       <c r="H42" s="150"/>
     </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="185"/>
+      <c r="D43" s="183"/>
       <c r="E43" s="134">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2609,9 +2563,9 @@
       </c>
       <c r="H43" s="150"/>
     </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="95"/>
       <c r="C44" s="95"/>
@@ -2633,20 +2587,20 @@
       </c>
       <c r="H44" s="150"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="185"/>
+      <c r="D45" s="183"/>
       <c r="E45" s="114"/>
       <c r="F45" s="100"/>
       <c r="H45" s="150"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
@@ -2663,15 +2617,15 @@
       </c>
       <c r="H46" s="150"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="197">
+      <c r="D47" s="195">
         <f>157828.92+9348.69+84138.18</f>
         <v>251315.79</v>
       </c>
@@ -2685,15 +2639,15 @@
       </c>
       <c r="H47" s="150"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="197">
+      <c r="D48" s="195">
         <v>828107.55</v>
       </c>
       <c r="E48" s="134">
@@ -2706,7 +2660,7 @@
       </c>
       <c r="H48" s="150"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
@@ -2733,181 +2687,178 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="185"/>
+      <c r="D50" s="183"/>
       <c r="E50" s="115"/>
       <c r="F50" s="7"/>
       <c r="H50" s="150"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="114" t="s">
-        <v>179</v>
+    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="188" t="s">
+        <v>162</v>
       </c>
       <c r="B51" s="176"/>
       <c r="C51" s="177"/>
-      <c r="D51" s="248">
+      <c r="D51" s="196">
         <v>960000</v>
       </c>
       <c r="E51" s="149">
-        <f t="shared" ref="E51" si="7">D51</f>
+        <f>D51</f>
         <v>960000</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="109">
-        <f t="shared" ref="G51" si="8">D51</f>
+        <f>D51</f>
         <v>960000</v>
       </c>
       <c r="H51" s="161">
-        <f t="shared" ref="H51" si="9">E51+F51</f>
+        <f>E51+F51</f>
         <v>960000</v>
       </c>
       <c r="I51" s="178">
-        <f>H51-D51</f>
+        <f t="shared" ref="I51:I69" si="7">H51-D51</f>
         <v>0</v>
       </c>
       <c r="J51" s="178">
-        <f>G51-D51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="190" t="s">
-        <v>155</v>
+        <f t="shared" ref="J51:J69" si="8">G51-D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="188" t="s">
+        <v>143</v>
       </c>
       <c r="B52" s="176"/>
       <c r="C52" s="177"/>
-      <c r="D52" s="113">
-        <v>1000000</v>
+      <c r="D52" s="195">
+        <v>372000</v>
       </c>
       <c r="E52" s="149">
         <f>D52</f>
-        <v>1000000</v>
+        <v>372000</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="109">
         <f>D52</f>
-        <v>1000000</v>
+        <v>372000</v>
       </c>
       <c r="H52" s="161">
         <f>E52+F52</f>
-        <v>1000000</v>
+        <v>372000</v>
       </c>
       <c r="I52" s="178">
-        <f t="shared" ref="I52:I82" si="10">H52-D52</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="178">
-        <f t="shared" ref="J52:J82" si="11">G52-D52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="190" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53" s="176"/>
-      <c r="C53" s="177"/>
-      <c r="D53" s="197">
-        <v>372000</v>
+        <f>H52-D52</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="178"/>
+    </row>
+    <row r="53" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="242" t="s">
+        <v>163</v>
+      </c>
+      <c r="B53" s="243"/>
+      <c r="C53" s="244"/>
+      <c r="D53" s="195">
+        <v>165500</v>
       </c>
       <c r="E53" s="149">
-        <f>D53</f>
-        <v>372000</v>
-      </c>
-      <c r="F53" s="7"/>
+        <f t="shared" ref="E53:E58" si="9">D53*91.91%</f>
+        <v>152111.04999999999</v>
+      </c>
+      <c r="F53" s="134">
+        <f t="shared" ref="F53:F58" si="10">D53*8.09%</f>
+        <v>13388.95</v>
+      </c>
       <c r="G53" s="109">
-        <f>D53</f>
-        <v>372000</v>
+        <f t="shared" ref="G53:G69" si="11">D53</f>
+        <v>165500</v>
       </c>
       <c r="H53" s="161">
-        <f>E53+F53</f>
-        <v>372000</v>
+        <f t="shared" ref="H53:H69" si="12">E53+F53</f>
+        <v>165500</v>
       </c>
       <c r="I53" s="178">
-        <f>H53-D53</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="178"/>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="121" t="s">
         <v>8</v>
       </c>
       <c r="B54" s="163"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="197">
-        <v>165500</v>
+      <c r="D54" s="195">
+        <v>148124.67000000001</v>
       </c>
       <c r="E54" s="149">
-        <f t="shared" ref="E54:E59" si="12">D54*91.91%</f>
-        <v>152111.04999999999</v>
+        <f t="shared" si="9"/>
+        <v>136141.38419700001</v>
       </c>
       <c r="F54" s="134">
-        <f t="shared" ref="F54:F59" si="13">D54*8.09%</f>
-        <v>13388.95</v>
+        <f t="shared" si="10"/>
+        <v>11983.285803000001</v>
       </c>
       <c r="G54" s="109">
-        <f t="shared" ref="G54:G82" si="14">D54</f>
-        <v>165500</v>
+        <f t="shared" si="11"/>
+        <v>148124.67000000001</v>
       </c>
       <c r="H54" s="161">
-        <f t="shared" ref="H54:H82" si="15">E54+F54</f>
-        <v>165500</v>
-      </c>
-      <c r="I54" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>148124.67000000001</v>
+      </c>
+      <c r="I54" s="178"/>
+      <c r="J54" s="178"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="94" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="113">
-        <v>129675</v>
+      <c r="D55" s="195">
+        <v>148200</v>
       </c>
       <c r="E55" s="149">
+        <f t="shared" si="9"/>
+        <v>136210.62</v>
+      </c>
+      <c r="F55" s="134">
+        <f t="shared" si="10"/>
+        <v>11989.38</v>
+      </c>
+      <c r="G55" s="109">
+        <f t="shared" si="11"/>
+        <v>148200</v>
+      </c>
+      <c r="H55" s="161">
         <f t="shared" si="12"/>
-        <v>119184.2925</v>
-      </c>
-      <c r="F55" s="134">
-        <f t="shared" si="13"/>
-        <v>10490.7075</v>
-      </c>
-      <c r="G55" s="109">
-        <f t="shared" si="14"/>
-        <v>129675</v>
-      </c>
-      <c r="H55" s="161">
-        <f t="shared" si="15"/>
-        <v>129675</v>
+        <v>148200</v>
       </c>
       <c r="I55" s="178">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J55" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="94" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="113">
@@ -2918,11 +2869,11 @@
         <v>68586.642669999987</v>
       </c>
       <c r="F56" s="134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>6037.0573299999996</v>
       </c>
       <c r="G56" s="109">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>74623.7</v>
       </c>
       <c r="H56" s="161">
@@ -2930,1610 +2881,1208 @@
         <v>74623.699999999983</v>
       </c>
       <c r="I56" s="178">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J56" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="94" t="s">
         <v>11</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="197">
+      <c r="D57" s="195">
         <v>614674.98</v>
       </c>
       <c r="E57" s="149">
+        <f t="shared" si="9"/>
+        <v>564947.77411799994</v>
+      </c>
+      <c r="F57" s="134">
+        <f t="shared" si="10"/>
+        <v>49727.205881999995</v>
+      </c>
+      <c r="G57" s="109">
+        <f t="shared" si="11"/>
+        <v>614674.98</v>
+      </c>
+      <c r="H57" s="161">
         <f t="shared" si="12"/>
-        <v>564947.77411799994</v>
-      </c>
-      <c r="F57" s="134">
-        <f t="shared" si="13"/>
-        <v>49727.205881999995</v>
-      </c>
-      <c r="G57" s="109">
-        <f t="shared" si="14"/>
         <v>614674.98</v>
       </c>
-      <c r="H57" s="161">
-        <f t="shared" si="15"/>
-        <v>614674.98</v>
-      </c>
       <c r="I57" s="178">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J57" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="129" t="s">
         <v>10</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C58" s="98"/>
-      <c r="D58" s="113">
-        <v>1031156.2</v>
+      <c r="D58" s="195">
+        <v>1101493.94</v>
       </c>
       <c r="E58" s="149">
+        <f t="shared" si="9"/>
+        <v>1012383.0802539999</v>
+      </c>
+      <c r="F58" s="134">
+        <f t="shared" si="10"/>
+        <v>89110.859746000002</v>
+      </c>
+      <c r="G58" s="109">
+        <f t="shared" si="11"/>
+        <v>1101493.94</v>
+      </c>
+      <c r="H58" s="161">
         <f t="shared" si="12"/>
-        <v>947735.66341999988</v>
-      </c>
-      <c r="F58" s="134">
+        <v>1101493.94</v>
+      </c>
+      <c r="I58" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="219" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="220"/>
+      <c r="C59" s="221"/>
+      <c r="D59" s="195">
+        <v>65500</v>
+      </c>
+      <c r="E59" s="149">
+        <f t="shared" ref="E59:E63" si="13">D59</f>
+        <v>65500</v>
+      </c>
+      <c r="F59" s="134"/>
+      <c r="G59" s="109">
+        <f t="shared" si="11"/>
+        <v>65500</v>
+      </c>
+      <c r="H59" s="161">
+        <f t="shared" si="12"/>
+        <v>65500</v>
+      </c>
+      <c r="I59" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="191" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="192"/>
+      <c r="C60" s="187"/>
+      <c r="D60" s="195">
+        <v>90000</v>
+      </c>
+      <c r="E60" s="149">
         <f t="shared" si="13"/>
-        <v>83420.53658</v>
-      </c>
-      <c r="G58" s="109">
-        <f t="shared" si="14"/>
-        <v>1031156.2</v>
-      </c>
-      <c r="H58" s="161">
-        <f t="shared" si="15"/>
-        <v>1031156.1999999998</v>
-      </c>
-      <c r="I58" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="178">
+        <v>90000</v>
+      </c>
+      <c r="F60" s="134"/>
+      <c r="G60" s="109">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="98" t="s">
-        <v>160</v>
-      </c>
-      <c r="B59" s="179"/>
-      <c r="C59" s="180"/>
-      <c r="D59" s="113">
-        <v>305000</v>
-      </c>
-      <c r="E59" s="149">
+        <v>90000</v>
+      </c>
+      <c r="H60" s="161">
         <f t="shared" si="12"/>
-        <v>280325.5</v>
-      </c>
-      <c r="F59" s="134">
+        <v>90000</v>
+      </c>
+      <c r="I60" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B61" s="114"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="195">
+        <v>29200</v>
+      </c>
+      <c r="E61" s="149">
         <f t="shared" si="13"/>
-        <v>24674.5</v>
-      </c>
-      <c r="G59" s="109">
-        <f t="shared" si="14"/>
-        <v>305000</v>
-      </c>
-      <c r="H59" s="161">
-        <f t="shared" si="15"/>
-        <v>305000</v>
-      </c>
-      <c r="I59" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="223" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="224"/>
-      <c r="C60" s="225"/>
-      <c r="D60" s="113">
-        <v>98393.96</v>
-      </c>
-      <c r="E60" s="149">
-        <f>D60*91.91%</f>
-        <v>90433.888636000003</v>
-      </c>
-      <c r="F60" s="134">
-        <f>D60*8.09%</f>
-        <v>7960.0713640000004</v>
-      </c>
-      <c r="G60" s="109">
-        <f t="shared" si="14"/>
-        <v>98393.96</v>
-      </c>
-      <c r="H60" s="161">
-        <f>E60+F60</f>
-        <v>98393.96</v>
-      </c>
-      <c r="I60" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="200" t="s">
-        <v>178</v>
-      </c>
-      <c r="B61" s="201"/>
-      <c r="C61" s="202"/>
-      <c r="D61" s="197">
-        <v>65500</v>
-      </c>
-      <c r="E61" s="149">
-        <f t="shared" ref="E61:E72" si="16">D61</f>
-        <v>65500</v>
+        <v>29200</v>
       </c>
       <c r="F61" s="134"/>
       <c r="G61" s="109">
-        <f t="shared" si="14"/>
-        <v>65500</v>
+        <f t="shared" si="11"/>
+        <v>29200</v>
       </c>
       <c r="H61" s="161">
-        <f t="shared" si="15"/>
-        <v>65500</v>
+        <f t="shared" si="12"/>
+        <v>29200</v>
       </c>
       <c r="I61" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="178"/>
+    </row>
+    <row r="62" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="219" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" s="220"/>
+      <c r="C62" s="221"/>
+      <c r="D62" s="241"/>
+      <c r="E62" s="149">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="226" t="s">
-        <v>154</v>
-      </c>
-      <c r="B62" s="227"/>
-      <c r="C62" s="228"/>
-      <c r="D62" s="113">
-        <v>180000</v>
-      </c>
-      <c r="E62" s="149">
-        <f t="shared" si="16"/>
-        <v>180000</v>
-      </c>
-      <c r="F62" s="134"/>
-      <c r="G62" s="109">
-        <f t="shared" si="14"/>
-        <v>180000</v>
-      </c>
       <c r="H62" s="161">
-        <f t="shared" si="15"/>
-        <v>180000</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="I62" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="198" t="s">
-        <v>150</v>
-      </c>
-      <c r="B63" s="199"/>
-      <c r="C63" s="203"/>
-      <c r="D63" s="113">
-        <v>315000</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="178"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="194" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="194"/>
+      <c r="C63" s="194"/>
+      <c r="D63" s="241">
+        <v>736429.26</v>
       </c>
       <c r="E63" s="149">
-        <f t="shared" si="16"/>
-        <v>315000</v>
+        <f t="shared" si="13"/>
+        <v>736429.26</v>
       </c>
       <c r="F63" s="134"/>
       <c r="G63" s="109">
+        <f t="shared" si="11"/>
+        <v>736429.26</v>
+      </c>
+      <c r="H63" s="161">
+        <f t="shared" si="12"/>
+        <v>736429.26</v>
+      </c>
+      <c r="I63" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="194" t="s">
+        <v>149</v>
+      </c>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="195">
+        <v>232510.18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="194" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="194" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="194"/>
+      <c r="D64" s="241"/>
+      <c r="E64" s="149">
+        <f t="shared" ref="E64:E68" si="14">D64*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="134">
+        <f t="shared" ref="F64:F68" si="15">D64*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="109">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M64" s="194" t="s">
+        <v>138</v>
+      </c>
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="195">
+        <v>357622.29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="194" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="194" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="194"/>
+      <c r="D65" s="241"/>
+      <c r="E65" s="149">
         <f t="shared" si="14"/>
-        <v>315000</v>
-      </c>
-      <c r="H63" s="161">
+        <v>0</v>
+      </c>
+      <c r="F65" s="134">
         <f t="shared" si="15"/>
-        <v>315000</v>
-      </c>
-      <c r="I63" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="178"/>
-    </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="193" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="194"/>
-      <c r="C64" s="189"/>
-      <c r="D64" s="113">
-        <v>35000</v>
-      </c>
-      <c r="E64" s="149">
-        <f t="shared" si="16"/>
-        <v>35000</v>
-      </c>
-      <c r="F64" s="134"/>
-      <c r="G64" s="109">
+        <v>0</v>
+      </c>
+      <c r="G65" s="109">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="161">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M65" s="194" t="s">
+        <v>138</v>
+      </c>
+      <c r="N65" s="7"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="195">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="194" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="194" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="194"/>
+      <c r="D66" s="241"/>
+      <c r="E66" s="149">
         <f t="shared" si="14"/>
-        <v>35000</v>
-      </c>
-      <c r="H64" s="161">
+        <v>0</v>
+      </c>
+      <c r="F66" s="134">
         <f t="shared" si="15"/>
-        <v>35000</v>
-      </c>
-      <c r="I64" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="178">
+        <v>0</v>
+      </c>
+      <c r="G66" s="109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="193" t="s">
-        <v>161</v>
-      </c>
-      <c r="B65" s="194"/>
-      <c r="C65" s="189"/>
-      <c r="D65" s="113">
-        <v>40000</v>
-      </c>
-      <c r="E65" s="149">
-        <f t="shared" si="16"/>
-        <v>40000</v>
-      </c>
-      <c r="F65" s="134"/>
-      <c r="G65" s="109">
-        <f t="shared" si="14"/>
-        <v>40000</v>
-      </c>
-      <c r="H65" s="161">
-        <f t="shared" si="15"/>
-        <v>40000</v>
-      </c>
-      <c r="I65" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="B66" s="114"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="113">
-        <v>143416.32999999999</v>
-      </c>
-      <c r="E66" s="149">
-        <f t="shared" si="16"/>
-        <v>143416.32999999999</v>
-      </c>
-      <c r="F66" s="134"/>
-      <c r="G66" s="109">
-        <f t="shared" si="14"/>
-        <v>143416.32999999999</v>
-      </c>
       <c r="H66" s="161">
-        <f t="shared" si="15"/>
-        <v>143416.32999999999</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="I66" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="178"/>
-    </row>
-    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" s="114"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="113">
-        <f>12100+10400+13800</f>
-        <v>36300</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="194" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="194"/>
+      <c r="C67" s="194"/>
+      <c r="D67" s="241">
+        <v>186859.86</v>
       </c>
       <c r="E67" s="149">
-        <f t="shared" si="16"/>
-        <v>36300</v>
+        <f t="shared" ref="E67" si="16">D67</f>
+        <v>186859.86</v>
       </c>
       <c r="F67" s="134"/>
       <c r="G67" s="109">
+        <f t="shared" si="11"/>
+        <v>186859.86</v>
+      </c>
+      <c r="H67" s="161">
+        <f t="shared" si="12"/>
+        <v>186859.86</v>
+      </c>
+      <c r="I67" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="195">
+        <v>83283.39</v>
+      </c>
+      <c r="E68" s="149">
         <f t="shared" si="14"/>
-        <v>36300</v>
-      </c>
-      <c r="H67" s="161">
+        <v>76545.763748999991</v>
+      </c>
+      <c r="F68" s="134">
         <f t="shared" si="15"/>
-        <v>36300</v>
-      </c>
-      <c r="I67" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="178"/>
-    </row>
-    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" s="114"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="113">
-        <v>4200</v>
-      </c>
-      <c r="E68" s="149">
-        <f t="shared" si="16"/>
-        <v>4200</v>
-      </c>
-      <c r="F68" s="7"/>
+        <v>6737.6262509999997</v>
+      </c>
       <c r="G68" s="109">
-        <f t="shared" si="14"/>
-        <v>4200</v>
+        <f t="shared" si="11"/>
+        <v>83283.39</v>
       </c>
       <c r="H68" s="161">
-        <f t="shared" si="15"/>
-        <v>4200</v>
+        <f t="shared" si="12"/>
+        <v>83283.389999999985</v>
       </c>
       <c r="I68" s="178">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J68" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="B69" s="114"/>
+      <c r="C69" s="162"/>
+      <c r="D69" s="195">
+        <v>300000</v>
+      </c>
+      <c r="E69" s="149">
+        <f t="shared" ref="E69" si="17">D69</f>
+        <v>300000</v>
+      </c>
+      <c r="F69" s="134"/>
+      <c r="G69" s="109">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="200" t="s">
-        <v>168</v>
-      </c>
-      <c r="B69" s="201"/>
-      <c r="C69" s="202"/>
-      <c r="D69" s="113">
-        <v>450000</v>
-      </c>
-      <c r="E69" s="149">
-        <f t="shared" si="16"/>
-        <v>450000</v>
-      </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="109">
-        <f t="shared" si="14"/>
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="H69" s="161">
-        <f t="shared" si="15"/>
-        <v>450000</v>
+        <f t="shared" si="12"/>
+        <v>300000</v>
       </c>
       <c r="I69" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="178"/>
-    </row>
-    <row r="70" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="200" t="s">
-        <v>170</v>
-      </c>
-      <c r="B70" s="201"/>
-      <c r="C70" s="202"/>
-      <c r="D70" s="113">
-        <v>180000</v>
-      </c>
-      <c r="E70" s="149">
-        <f t="shared" si="16"/>
-        <v>180000</v>
-      </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="109">
-        <f t="shared" si="14"/>
-        <v>180000</v>
-      </c>
-      <c r="H70" s="161">
-        <f t="shared" si="15"/>
-        <v>180000</v>
-      </c>
-      <c r="I70" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="178"/>
-    </row>
-    <row r="71" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="200" t="s">
-        <v>169</v>
-      </c>
-      <c r="B71" s="201"/>
-      <c r="C71" s="202"/>
-      <c r="D71" s="113">
-        <v>250000</v>
-      </c>
-      <c r="E71" s="149">
-        <f t="shared" si="16"/>
-        <v>250000</v>
-      </c>
-      <c r="F71" s="7"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="155"/>
+      <c r="B70" s="156"/>
+      <c r="C70" s="156"/>
+      <c r="D70" s="166"/>
+      <c r="E70" s="149"/>
+      <c r="F70" s="134"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="161"/>
+      <c r="I70" t="str">
+        <f>IF(G70=H70, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="96"/>
+      <c r="C71" s="96"/>
+      <c r="D71" s="108">
+        <f>SUM(D51:D70)</f>
+        <v>5075889.8</v>
+      </c>
+      <c r="E71" s="108">
+        <f>SUM(E51:E70)</f>
+        <v>4886915.4349879995</v>
+      </c>
+      <c r="F71" s="108">
+        <f>SUM(F51:F70)</f>
+        <v>188974.36501199999</v>
+      </c>
       <c r="G71" s="109">
-        <f t="shared" si="14"/>
-        <v>250000</v>
-      </c>
-      <c r="H71" s="161">
-        <f t="shared" si="15"/>
-        <v>250000</v>
+        <f>E71+F71</f>
+        <v>5075889.8</v>
+      </c>
+      <c r="H71" s="150" t="str">
+        <f>IF(D71=G71, "", "Error")</f>
+        <v/>
       </c>
       <c r="I71" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="178"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A72" s="98" t="s">
-        <v>165</v>
-      </c>
+        <f>D71-G71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="113">
-        <v>736429.26</v>
-      </c>
-      <c r="E72" s="149">
-        <f t="shared" si="16"/>
-        <v>736429.26</v>
-      </c>
-      <c r="F72" s="134"/>
-      <c r="G72" s="109">
-        <f t="shared" si="14"/>
-        <v>736429.26</v>
-      </c>
-      <c r="H72" s="161">
-        <f t="shared" si="15"/>
-        <v>736429.26</v>
-      </c>
-      <c r="I72" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="196" t="s">
-        <v>167</v>
-      </c>
-      <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="197">
-        <v>232510.18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="196" t="s">
-        <v>167</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="D72" s="183"/>
+      <c r="E72" s="115"/>
+      <c r="F72" s="7"/>
+      <c r="H72" s="150"/>
+    </row>
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="113"/>
-      <c r="E73" s="149">
-        <f t="shared" ref="E73:E80" si="17">D73*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="134">
-        <f t="shared" ref="F73:F81" si="18">D73*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="109">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="161">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="197">
-        <v>357622.29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="D73" s="183"/>
+      <c r="E73" s="114"/>
+      <c r="F73" s="7"/>
+      <c r="H73" s="150"/>
+    </row>
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="113"/>
-      <c r="E74" s="149">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="134">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="109">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="161">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="197">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="D74" s="183"/>
+      <c r="E74" s="114"/>
+      <c r="F74" s="7"/>
+      <c r="H74" s="150"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="94" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="98"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="113"/>
+      <c r="D75" s="195">
+        <f>127080+80450</f>
+        <v>207530</v>
+      </c>
       <c r="E75" s="149">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>D75*91.91%</f>
+        <v>190740.82299999997</v>
       </c>
       <c r="F75" s="134">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="109">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="161">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="98" t="s">
-        <v>166</v>
-      </c>
+        <f>D75*8.09%</f>
+        <v>16789.177</v>
+      </c>
+      <c r="G75" s="160"/>
+      <c r="H75" s="150"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
-      <c r="D76" s="113">
-        <v>186859.86</v>
-      </c>
-      <c r="E76" s="149">
-        <f t="shared" ref="E76:E78" si="19">D76</f>
-        <v>186859.86</v>
-      </c>
-      <c r="F76" s="134"/>
-      <c r="G76" s="109">
-        <f t="shared" si="14"/>
-        <v>186859.86</v>
-      </c>
-      <c r="H76" s="161">
-        <f t="shared" si="15"/>
-        <v>186859.86</v>
-      </c>
-      <c r="I76" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="113">
-        <v>36300</v>
-      </c>
-      <c r="E77" s="149">
-        <f t="shared" si="19"/>
-        <v>36300</v>
-      </c>
-      <c r="F77" s="134"/>
+      <c r="D76" s="113"/>
+      <c r="E76" s="164">
+        <f>D76</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="H76" s="150"/>
+      <c r="I76" s="109"/>
+    </row>
+    <row r="77" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="95"/>
+      <c r="C77" s="95"/>
+      <c r="D77" s="107">
+        <f>SUM(D75:D76)</f>
+        <v>207530</v>
+      </c>
+      <c r="E77" s="107">
+        <f>SUM(E75:E76)</f>
+        <v>190740.82299999997</v>
+      </c>
+      <c r="F77" s="107">
+        <f>SUM(F75:F76)</f>
+        <v>16789.177</v>
+      </c>
       <c r="G77" s="109">
-        <f t="shared" si="14"/>
-        <v>36300</v>
-      </c>
-      <c r="H77" s="161">
-        <f t="shared" si="15"/>
-        <v>36300</v>
-      </c>
-      <c r="I77" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="200" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="201"/>
-      <c r="C78" s="202"/>
-      <c r="D78" s="113">
-        <v>36300</v>
-      </c>
-      <c r="E78" s="149">
-        <f t="shared" si="19"/>
-        <v>36300</v>
-      </c>
-      <c r="F78" s="134"/>
-      <c r="G78" s="109">
-        <f t="shared" si="14"/>
-        <v>36300</v>
-      </c>
-      <c r="H78" s="161">
-        <f t="shared" si="15"/>
-        <v>36300</v>
-      </c>
-      <c r="I78" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="178"/>
-    </row>
-    <row r="79" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="200" t="s">
-        <v>143</v>
-      </c>
-      <c r="B79" s="201"/>
-      <c r="C79" s="202"/>
-      <c r="D79" s="113">
-        <v>430000</v>
-      </c>
-      <c r="E79" s="149">
-        <f t="shared" ref="E79:E82" si="20">D79</f>
-        <v>430000</v>
-      </c>
+        <f>E77+F77</f>
+        <v>207529.99999999997</v>
+      </c>
+      <c r="H77" s="150" t="str">
+        <f>IF(D77=G77, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J77" s="109"/>
+    </row>
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="183"/>
+      <c r="E78" s="115"/>
+      <c r="F78" s="7"/>
+      <c r="H78" s="150"/>
+    </row>
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="183"/>
+      <c r="E79" s="114"/>
       <c r="F79" s="7"/>
-      <c r="G79" s="109">
-        <f t="shared" si="14"/>
-        <v>430000</v>
-      </c>
-      <c r="H79" s="161">
-        <f t="shared" si="15"/>
-        <v>430000</v>
-      </c>
-      <c r="I79" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="H79" s="150"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="197">
-        <v>83283.39</v>
-      </c>
-      <c r="E80" s="149">
-        <f t="shared" si="17"/>
-        <v>76545.763748999991</v>
-      </c>
-      <c r="F80" s="134">
-        <f t="shared" si="18"/>
-        <v>6737.6262509999997</v>
-      </c>
-      <c r="G80" s="109">
-        <f t="shared" si="14"/>
-        <v>83283.39</v>
-      </c>
-      <c r="H80" s="161">
-        <f t="shared" si="15"/>
-        <v>83283.389999999985</v>
-      </c>
-      <c r="I80" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B81" s="114"/>
+      <c r="D80" s="183"/>
+      <c r="E80" s="114"/>
+      <c r="F80" s="7"/>
+      <c r="H80" s="150"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="C81" s="7"/>
-      <c r="D81" s="113">
-        <v>1820</v>
+      <c r="D81" s="195">
+        <v>246000</v>
       </c>
       <c r="E81" s="149">
         <f>D81*91.91%</f>
-        <v>1672.7619999999999</v>
-      </c>
-      <c r="F81" s="7">
-        <f t="shared" si="18"/>
-        <v>147.238</v>
-      </c>
-      <c r="G81" s="109">
-        <f t="shared" si="14"/>
-        <v>1820</v>
-      </c>
-      <c r="H81" s="161">
-        <f t="shared" si="15"/>
-        <v>1820</v>
-      </c>
-      <c r="I81" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="98" t="s">
-        <v>159</v>
-      </c>
-      <c r="B82" s="114"/>
-      <c r="C82" s="162"/>
-      <c r="D82" s="113">
-        <v>320000</v>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F81" s="134">
+        <f>D81*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G81" t="s">
+        <v>146</v>
+      </c>
+      <c r="H81" s="150"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="195">
+        <v>30000</v>
       </c>
       <c r="E82" s="149">
-        <f t="shared" si="20"/>
-        <v>320000</v>
-      </c>
-      <c r="F82" s="134"/>
-      <c r="G82" s="109">
-        <f t="shared" si="14"/>
-        <v>320000</v>
-      </c>
-      <c r="H82" s="161">
-        <f t="shared" si="15"/>
-        <v>320000</v>
-      </c>
-      <c r="I82" s="178">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="155"/>
-      <c r="B83" s="156"/>
-      <c r="C83" s="156"/>
-      <c r="D83" s="166"/>
-      <c r="E83" s="149"/>
-      <c r="F83" s="134"/>
-      <c r="G83" s="109"/>
-      <c r="H83" s="161"/>
-      <c r="I83" t="str">
-        <f>IF(G83=H83, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="B84" s="96"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="108">
-        <f>SUM(D51:D83)</f>
-        <v>8281432.6799999997</v>
-      </c>
-      <c r="E84" s="108">
-        <f>SUM(E51:E83)</f>
-        <v>8078848.7870930005</v>
-      </c>
-      <c r="F84" s="108">
-        <f>SUM(F51:F83)</f>
-        <v>202583.89290700003</v>
+        <f>D82*91.91%</f>
+        <v>27572.999999999996</v>
+      </c>
+      <c r="F82" s="134">
+        <f>D82*8.09%</f>
+        <v>2427</v>
+      </c>
+      <c r="H82" s="150"/>
+      <c r="J82" s="113"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="183"/>
+      <c r="E83" s="116"/>
+      <c r="F83" s="7"/>
+      <c r="H83" s="150"/>
+      <c r="J83" s="109"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="95"/>
+      <c r="C84" s="95"/>
+      <c r="D84" s="107">
+        <f>SUM(D81:D83)</f>
+        <v>276000</v>
+      </c>
+      <c r="E84" s="107">
+        <f>SUM(E81:E83)</f>
+        <v>253671.59999999998</v>
+      </c>
+      <c r="F84" s="107">
+        <f>SUM(F81:F83)</f>
+        <v>22328.400000000001</v>
       </c>
       <c r="G84" s="109">
         <f>E84+F84</f>
-        <v>8281432.6800000006</v>
+        <v>276000</v>
       </c>
       <c r="H84" s="150" t="str">
         <f>IF(D84=G84, "", "Error")</f>
         <v/>
       </c>
-      <c r="I84" s="178">
-        <f>D84-G84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J84" s="109"/>
+    </row>
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="185"/>
-      <c r="E85" s="115"/>
+      <c r="D85" s="113"/>
+      <c r="E85" s="117"/>
       <c r="F85" s="7"/>
       <c r="H85" s="150"/>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="7"/>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="94" t="s">
+        <v>101</v>
+      </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="185"/>
-      <c r="E86" s="114"/>
-      <c r="F86" s="7"/>
+      <c r="D86" s="241">
+        <v>116023.77</v>
+      </c>
+      <c r="E86" s="149">
+        <f>D86*91.91%</f>
+        <v>106637.447007</v>
+      </c>
+      <c r="F86" s="134">
+        <f>D86*8.09%</f>
+        <v>9386.3229929999998</v>
+      </c>
       <c r="H86" s="150"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="7"/>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="94" t="s">
+        <v>102</v>
+      </c>
       <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="185"/>
-      <c r="E87" s="114"/>
-      <c r="F87" s="7"/>
+      <c r="C87" s="122"/>
+      <c r="D87" s="241">
+        <v>44400</v>
+      </c>
+      <c r="E87" s="149">
+        <f>D87*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F87" s="134">
+        <f>D87*8.09%</f>
+        <v>3591.96</v>
+      </c>
       <c r="H87" s="150"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="94" t="s">
-        <v>138</v>
-      </c>
-      <c r="B88" s="98"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="113">
-        <f>67780+35700</f>
-        <v>103480</v>
-      </c>
-      <c r="E88" s="149">
-        <f>D88*91.91%</f>
-        <v>95108.467999999993</v>
-      </c>
-      <c r="F88" s="134">
-        <f>D88*8.09%</f>
-        <v>8371.5319999999992</v>
-      </c>
-      <c r="G88" s="160"/>
-      <c r="H88" s="150"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="95"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="158">
+        <f>SUM(D86:D87)</f>
+        <v>160423.77000000002</v>
+      </c>
+      <c r="E88" s="147">
+        <f t="shared" ref="E88:F88" si="18">SUM(E86:E87)</f>
+        <v>147445.48700699999</v>
+      </c>
+      <c r="F88" s="147">
+        <f t="shared" si="18"/>
+        <v>12978.282993000001</v>
+      </c>
+      <c r="G88" s="109">
+        <f>E88+F88</f>
+        <v>160423.76999999999</v>
+      </c>
+      <c r="H88" s="150" t="str">
+        <f>IF(D88=G88, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
-      <c r="D89" s="113"/>
-      <c r="E89" s="164">
-        <f>D89</f>
-        <v>0</v>
-      </c>
+      <c r="D89" s="184"/>
+      <c r="E89" s="12"/>
       <c r="F89" s="7"/>
       <c r="H89" s="150"/>
-      <c r="I89" s="109"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="95" t="s">
-        <v>17</v>
-      </c>
-      <c r="B90" s="95"/>
-      <c r="C90" s="95"/>
-      <c r="D90" s="107">
-        <f>SUM(D88:D89)</f>
-        <v>103480</v>
-      </c>
-      <c r="E90" s="107">
-        <f>SUM(E88:E89)</f>
-        <v>95108.467999999993</v>
-      </c>
-      <c r="F90" s="107">
-        <f>SUM(F88:F89)</f>
-        <v>8371.5319999999992</v>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="99"/>
+      <c r="C90" s="99"/>
+      <c r="D90" s="185"/>
+      <c r="E90" s="118">
+        <f>D90*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="136">
+        <f>D90*8.09%</f>
+        <v>0</v>
       </c>
       <c r="G90" s="109">
         <f>E90+F90</f>
-        <v>103480</v>
+        <v>0</v>
       </c>
       <c r="H90" s="150" t="str">
         <f>IF(D90=G90, "", "Error")</f>
         <v/>
       </c>
-      <c r="J90" s="109"/>
-    </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="185"/>
-      <c r="E91" s="115"/>
-      <c r="F91" s="7"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="D91" s="182"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="157"/>
       <c r="H91" s="150"/>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="185"/>
-      <c r="E92" s="114"/>
-      <c r="F92" s="7"/>
-      <c r="H92" s="150"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="94" t="s">
-        <v>13</v>
-      </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="185"/>
-      <c r="E93" s="114"/>
-      <c r="F93" s="7"/>
-      <c r="H93" s="150"/>
-    </row>
-    <row r="94" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="113">
-        <v>246000</v>
-      </c>
-      <c r="E94" s="149">
-        <f>D94*91.91%</f>
-        <v>226098.59999999998</v>
-      </c>
-      <c r="F94" s="134">
-        <f>D94*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G94" t="s">
-        <v>163</v>
-      </c>
-      <c r="H94" s="150"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="197">
-        <v>30000</v>
-      </c>
-      <c r="E95" s="149">
-        <f>D95*91.91%</f>
-        <v>27572.999999999996</v>
-      </c>
-      <c r="F95" s="134">
-        <f>D95*8.09%</f>
-        <v>2427</v>
-      </c>
-      <c r="H95" s="150"/>
-      <c r="J95" s="113"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="185"/>
-      <c r="E96" s="116"/>
-      <c r="F96" s="7"/>
-      <c r="H96" s="150"/>
-      <c r="J96" s="109"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="95" t="s">
-        <v>101</v>
-      </c>
-      <c r="B97" s="95"/>
-      <c r="C97" s="95"/>
-      <c r="D97" s="107">
-        <f>SUM(D94:D96)</f>
-        <v>276000</v>
-      </c>
-      <c r="E97" s="107">
-        <f>SUM(E94:E96)</f>
-        <v>253671.59999999998</v>
-      </c>
-      <c r="F97" s="107">
-        <f>SUM(F94:F96)</f>
-        <v>22328.400000000001</v>
-      </c>
-      <c r="G97" s="109">
-        <f>E97+F97</f>
-        <v>276000</v>
-      </c>
-      <c r="H97" s="150" t="str">
-        <f>IF(D97=G97, "", "Error")</f>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="60"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="186">
+        <f>SUM(D90+D88+D84+D77+D71+D49+D32+D27+D44)</f>
+        <v>8307924.1200000001</v>
+      </c>
+      <c r="E92" s="148">
+        <f>SUM(E90+E88+E84+E77+E71+E49+E32+E27+E44)</f>
+        <v>7857478.1784999995</v>
+      </c>
+      <c r="F92" s="148">
+        <f>SUM(F90+F88+F84+F77+F71+F49+F32+F27+F44)</f>
+        <v>450445.94150000002</v>
+      </c>
+      <c r="G92" s="109">
+        <f>E92+F92</f>
+        <v>8307924.1199999992</v>
+      </c>
+      <c r="H92" s="150" t="str">
+        <f>IF(D92=G92, "", "Error")</f>
         <v/>
       </c>
-      <c r="J97" s="109"/>
-    </row>
-    <row r="98" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="113"/>
-      <c r="E98" s="117"/>
-      <c r="F98" s="7"/>
-      <c r="H98" s="150"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="113">
-        <v>116023.77</v>
-      </c>
-      <c r="E99" s="149">
-        <f>D99*91.91%</f>
-        <v>106637.447007</v>
-      </c>
-      <c r="F99" s="134">
-        <f>D99*8.09%</f>
-        <v>9386.3229929999998</v>
-      </c>
-      <c r="H99" s="150"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="122"/>
-      <c r="D100" s="113">
-        <v>44400</v>
-      </c>
-      <c r="E100" s="149">
-        <f>D100*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F100" s="134">
-        <f>D100*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H100" s="150"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" s="95"/>
-      <c r="C101" s="95"/>
-      <c r="D101" s="158">
-        <f>SUM(D99:D100)</f>
-        <v>160423.77000000002</v>
-      </c>
-      <c r="E101" s="147">
-        <f t="shared" ref="E101:F101" si="21">SUM(E99:E100)</f>
-        <v>147445.48700699999</v>
-      </c>
-      <c r="F101" s="147">
-        <f t="shared" si="21"/>
-        <v>12978.282993000001</v>
-      </c>
-      <c r="G101" s="109">
-        <f>E101+F101</f>
-        <v>160423.76999999999</v>
-      </c>
-      <c r="H101" s="150" t="str">
-        <f>IF(D101=G101, "", "Error")</f>
+      <c r="I92" s="178">
+        <f>D92-G92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="182"/>
+      <c r="E93" s="109"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="141"/>
+      <c r="C94" s="141"/>
+      <c r="E94" s="109"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="C95" s="139"/>
+      <c r="E95" s="109"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1"/>
+      <c r="C96" s="139"/>
+      <c r="E96" s="109"/>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="143" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" s="144"/>
+      <c r="C97" s="140">
+        <f>SUM(C95:C96)</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="109"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E98" s="109"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E99" s="137"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="217" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" s="218"/>
+      <c r="C100" s="218"/>
+      <c r="D100" s="218"/>
+      <c r="E100" s="171" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="172" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="214"/>
+      <c r="B101" s="215"/>
+      <c r="C101" s="216"/>
+      <c r="D101" s="166"/>
+      <c r="E101" s="149"/>
+      <c r="F101" s="134"/>
+    </row>
+    <row r="102" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="211"/>
+      <c r="B102" s="212"/>
+      <c r="C102" s="173"/>
+      <c r="D102" s="113"/>
+      <c r="E102" s="149">
+        <f t="shared" ref="E102:E103" si="19">D102*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="134">
+        <f t="shared" ref="F102:F103" si="20">D102*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="211"/>
+      <c r="B103" s="212"/>
+      <c r="C103" s="173"/>
+      <c r="D103" s="113"/>
+      <c r="E103" s="149">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="134">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="211"/>
+      <c r="B104" s="212"/>
+      <c r="C104" s="213"/>
+      <c r="D104" s="113"/>
+      <c r="E104" s="149">
+        <f>D104*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="134">
+        <f>D104*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="208" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="209"/>
+      <c r="C105" s="210"/>
+      <c r="D105" s="170">
+        <f>SUM(D101:D104)</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="170">
+        <f>SUM(E101:E104)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="170">
+        <f>SUM(F101:F104)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="109">
+        <f>E105+F105</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="150" t="str">
+        <f>IF(D105=H105, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="186"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="7"/>
-      <c r="H102" s="150"/>
-    </row>
-    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="B103" s="99"/>
-      <c r="C103" s="99"/>
-      <c r="D103" s="187"/>
-      <c r="E103" s="118">
-        <f>D103*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F103" s="136">
-        <f>D103*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G103" s="109">
-        <f>E103+F103</f>
-        <v>0</v>
-      </c>
-      <c r="H103" s="150" t="str">
-        <f>IF(D103=G103, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="1"/>
-      <c r="D104" s="184"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="157"/>
-      <c r="H104" s="150"/>
-    </row>
-    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="4" t="s">
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="109"/>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="60"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="188">
-        <f>SUM(D103+D101+D97+D90+D84+D49+D32+D27+D44)</f>
-        <v>11409417</v>
-      </c>
-      <c r="E105" s="148">
-        <f>SUM(E103+E101+E97+E90+E84+E49+E32+E27+E44)</f>
-        <v>10953779.175605001</v>
-      </c>
-      <c r="F105" s="148">
-        <f>SUM(F103+F101+F97+F90+F84+F49+F32+F27+F44)</f>
-        <v>455637.824395</v>
-      </c>
-      <c r="G105" s="109">
-        <f>E105+F105</f>
-        <v>11409417</v>
-      </c>
-      <c r="H105" s="150" t="str">
-        <f>IF(D105=G105, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I105" s="178">
-        <f>D105-G105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D106" s="184"/>
-      <c r="E106" s="109"/>
-    </row>
-    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="142" t="s">
-        <v>121</v>
-      </c>
-      <c r="B107" s="141"/>
-      <c r="C107" s="141"/>
-      <c r="E107" s="109"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A108" s="1"/>
-      <c r="C108" s="139"/>
-      <c r="E108" s="109"/>
-    </row>
-    <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="1"/>
-      <c r="C109" s="139"/>
-      <c r="E109" s="109"/>
-    </row>
-    <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="143" t="s">
-        <v>30</v>
-      </c>
-      <c r="B110" s="144"/>
-      <c r="C110" s="140">
-        <f>SUM(C108:C109)</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="109"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E111" s="109"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E112" s="137"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="221" t="s">
+      <c r="B108" s="103">
+        <f>D92</f>
+        <v>8307924.1200000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B109" s="105">
+        <f>D92-D90</f>
+        <v>8307924.1200000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D110" s="198"/>
+      <c r="E110" s="198"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B111" s="75"/>
+      <c r="C111" s="76"/>
+      <c r="D111" s="198"/>
+      <c r="E111" s="198"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" s="11">
+        <v>3924460.3236006536</v>
+      </c>
+      <c r="C112" s="78"/>
+      <c r="D112" s="198"/>
+      <c r="E112" s="198"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B113" s="92" t="e">
+        <f>PRORRATEO!G52</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C113" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D113" s="198"/>
+      <c r="E113" s="198"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="175">
+        <f>-B109</f>
+        <v>-8307924.1200000001</v>
+      </c>
+      <c r="C114" s="76"/>
+      <c r="D114" s="198"/>
+      <c r="E114" s="198"/>
+      <c r="G114" s="113"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="B113" s="222"/>
-      <c r="C113" s="222"/>
-      <c r="D113" s="222"/>
-      <c r="E113" s="171" t="s">
-        <v>22</v>
-      </c>
-      <c r="F113" s="172" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="218"/>
-      <c r="B114" s="219"/>
-      <c r="C114" s="220"/>
-      <c r="D114" s="166"/>
-      <c r="E114" s="149"/>
-      <c r="F114" s="134"/>
-    </row>
-    <row r="115" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="198"/>
-      <c r="B115" s="199"/>
-      <c r="C115" s="173"/>
-      <c r="D115" s="113"/>
-      <c r="E115" s="149">
-        <f t="shared" ref="E115:E116" si="22">D115*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F115" s="134">
-        <f t="shared" ref="F115:F116" si="23">D115*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="198"/>
-      <c r="B116" s="199"/>
-      <c r="C116" s="173"/>
-      <c r="D116" s="113"/>
-      <c r="E116" s="149">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="F116" s="134">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="198"/>
-      <c r="B117" s="199"/>
-      <c r="C117" s="203"/>
-      <c r="D117" s="113"/>
-      <c r="E117" s="149">
-        <f>D117*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F117" s="134">
-        <f>D117*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="215" t="s">
-        <v>30</v>
-      </c>
-      <c r="B118" s="216"/>
-      <c r="C118" s="217"/>
-      <c r="D118" s="170">
-        <f>SUM(D114:D117)</f>
-        <v>0</v>
-      </c>
-      <c r="E118" s="170">
-        <f>SUM(E114:E117)</f>
-        <v>0</v>
-      </c>
-      <c r="F118" s="170">
-        <f>SUM(F114:F117)</f>
-        <v>0</v>
-      </c>
-      <c r="H118" s="109">
-        <f>E118+F118</f>
-        <v>0</v>
-      </c>
-      <c r="I118" s="150" t="str">
-        <f>IF(D118=H118, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E120" s="109"/>
-    </row>
-    <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="102" t="s">
+      <c r="B115" s="175">
+        <f>-D105</f>
+        <v>0</v>
+      </c>
+      <c r="C115" s="76"/>
+      <c r="D115" s="198"/>
+      <c r="E115" s="198"/>
+      <c r="G115" s="125"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="B121" s="103">
-        <f>D105</f>
-        <v>11409417</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B122" s="105">
-        <f>D105-D103</f>
-        <v>11409417</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D123" s="205"/>
-      <c r="E123" s="205"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="B124" s="75"/>
-      <c r="C124" s="76"/>
-      <c r="D124" s="205"/>
-      <c r="E124" s="205"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="B125" s="11">
-        <v>3924460.3236006536</v>
-      </c>
-      <c r="C125" s="78"/>
-      <c r="D125" s="205"/>
-      <c r="E125" s="205"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="B126" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>5340180.0816379944</v>
-      </c>
-      <c r="C126" s="78" t="s">
+      <c r="B116" s="175">
+        <f>-B123</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="80"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="93">
+        <f>-C97</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="80"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="79"/>
+      <c r="B118" s="75"/>
+      <c r="C118" s="80"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="D126" s="205"/>
-      <c r="E126" s="205"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="B127" s="175">
-        <f>-B122</f>
-        <v>-11409417</v>
-      </c>
-      <c r="C127" s="76"/>
-      <c r="D127" s="205"/>
-      <c r="E127" s="205"/>
-      <c r="G127" s="113"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B128" s="175">
-        <f>-D118</f>
-        <v>0</v>
-      </c>
+      <c r="B119" s="81" t="e">
+        <f>SUM(B112:B118)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C119" s="154"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="80"/>
+      <c r="C120" s="76"/>
+      <c r="D120" s="83"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C121" s="76"/>
+      <c r="D121" s="109"/>
+      <c r="E121" s="178"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="11">
+        <v>-365694.54000000004</v>
+      </c>
+      <c r="C122" s="82"/>
+      <c r="D122" s="178"/>
+      <c r="E122" s="178"/>
+      <c r="F122" s="178"/>
+    </row>
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="B123" s="93"/>
+      <c r="C123" s="82"/>
+      <c r="D123" s="178"/>
+      <c r="E123" s="193"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" s="175">
+        <v>-37000</v>
+      </c>
+      <c r="C124" s="82"/>
+      <c r="E124" s="109"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="77"/>
+      <c r="B125" s="175"/>
+      <c r="C125" s="82"/>
+      <c r="E125" s="109"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B126" s="101">
+        <f>SUM(B122:B125)</f>
+        <v>-402694.54000000004</v>
+      </c>
+      <c r="C126" s="82"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C127" s="83"/>
+      <c r="D127" s="178"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B128" s="80"/>
       <c r="C128" s="76"/>
-      <c r="D128" s="205"/>
-      <c r="E128" s="205"/>
-      <c r="G128" s="125"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="B129" s="175">
-        <f>-B136</f>
-        <v>0</v>
-      </c>
-      <c r="C129" s="80"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="79" t="s">
-        <v>121</v>
-      </c>
-      <c r="B130" s="93">
-        <f>-C110</f>
-        <v>0</v>
-      </c>
-      <c r="C130" s="80"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="79"/>
-      <c r="B131" s="75"/>
-      <c r="C131" s="80"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="B132" s="81">
-        <f>SUM(B125:B131)</f>
-        <v>-2144776.594761353</v>
-      </c>
-      <c r="C132" s="154"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="80"/>
-      <c r="C133" s="76"/>
-      <c r="D133" s="83"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C134" s="76"/>
-      <c r="D134" s="109"/>
-      <c r="E134" s="178"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B135" s="11">
-        <v>-365694.54000000004</v>
-      </c>
-      <c r="C135" s="82"/>
-      <c r="D135" s="178"/>
-      <c r="E135" s="178"/>
-      <c r="F135" s="178"/>
-    </row>
-    <row r="136" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="77" t="s">
-        <v>139</v>
-      </c>
-      <c r="B136" s="93"/>
-      <c r="C136" s="82"/>
-      <c r="D136" s="178"/>
-      <c r="E136" s="195"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="77"/>
-      <c r="B137" s="175"/>
-      <c r="C137" s="82"/>
-      <c r="E137" s="109"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="77"/>
-      <c r="B138" s="175"/>
-      <c r="C138" s="82"/>
-      <c r="E138" s="109"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="100" t="s">
-        <v>30</v>
-      </c>
-      <c r="B139" s="101">
-        <f>SUM(B135:B138)</f>
-        <v>-365694.54000000004</v>
-      </c>
-      <c r="C139" s="82"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C140" s="83"/>
-      <c r="D140" s="178"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B141" s="80"/>
-      <c r="C141" s="76"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N143" s="12"/>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B146" s="204"/>
-      <c r="C146" s="204"/>
-      <c r="D146" s="204"/>
-      <c r="E146" s="204"/>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B147" s="204"/>
-      <c r="C147" s="204"/>
-      <c r="D147" s="204"/>
-      <c r="E147" s="204"/>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B148" s="204"/>
-      <c r="C148" s="204"/>
-      <c r="D148" s="204"/>
-      <c r="E148" s="204"/>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B149" s="204"/>
-      <c r="C149" s="204"/>
-      <c r="D149" s="204"/>
-      <c r="E149" s="204"/>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B150" s="204"/>
-      <c r="C150" s="204"/>
-      <c r="D150" s="204"/>
-      <c r="E150" s="204"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N130" s="12"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B133" s="197"/>
+      <c r="C133" s="197"/>
+      <c r="D133" s="197"/>
+      <c r="E133" s="197"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="197"/>
+      <c r="C134" s="197"/>
+      <c r="D134" s="197"/>
+      <c r="E134" s="197"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="197"/>
+      <c r="C135" s="197"/>
+      <c r="D135" s="197"/>
+      <c r="E135" s="197"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="197"/>
+      <c r="C136" s="197"/>
+      <c r="D136" s="197"/>
+      <c r="E136" s="197"/>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="197"/>
+      <c r="C137" s="197"/>
+      <c r="D137" s="197"/>
+      <c r="E137" s="197"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B146:E150"/>
-    <mergeCell ref="D123:E128"/>
+  <mergeCells count="12">
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="B133:E137"/>
+    <mergeCell ref="D110:E115"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A102:B102"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4544,53 +4093,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="L1" s="236">
-        <f>RESUMEN!D105</f>
-        <v>11409417</v>
-      </c>
-      <c r="M1" s="237"/>
+        <v>124</v>
+      </c>
+      <c r="L1" s="225">
+        <f>RESUMEN!D92</f>
+        <v>8307924.1200000001</v>
+      </c>
+      <c r="M1" s="226"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>923021.83530000004</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>672111.061308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4602,7 +4151,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="152">
@@ -4612,10 +4161,10 @@
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>510167.15519200003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>259256.3812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 14/08</v>
@@ -4630,17 +4179,17 @@
       <c r="I3" s="8"/>
       <c r="J3" s="9"/>
       <c r="K3" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="128">
-        <f>RESUMEN!D118</f>
+        <f>RESUMEN!D105</f>
         <v>0</v>
       </c>
       <c r="N3" s="151"/>
       <c r="O3" s="73"/>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -4655,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="128">
@@ -4663,76 +4212,76 @@
       </c>
       <c r="N4" s="124"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="229" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="222" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="236" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="231" t="s">
+      <c r="C5" s="222" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="229" t="s">
+      <c r="D5" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="233" t="s">
+      <c r="E5" s="222" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="229" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="229" t="s">
+      <c r="G5" s="222" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="229" t="s">
+      <c r="H5" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="240" t="s">
+      <c r="I5" s="234" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="227" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="233" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="238" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="238" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="243" t="s">
-        <v>124</v>
-      </c>
-      <c r="M5" s="238" t="s">
+      <c r="K5" s="227" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="232" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5" s="227" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="238" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="230"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="241"/>
-      <c r="I6" s="245"/>
-      <c r="J6" s="239"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="239"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="223"/>
+      <c r="B6" s="237"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="238"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="228"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="231"/>
+      <c r="N6" s="228"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="7">
         <v>8.09</v>
@@ -4740,7 +4289,7 @@
       <c r="F7" s="88">
         <v>423542.38923799997</v>
       </c>
-      <c r="G7" s="191">
+      <c r="G7" s="189">
         <f>F7</f>
         <v>423542.38923799997</v>
       </c>
@@ -4767,16 +4316,16 @@
         <v>436887.14091447997</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7">
         <v>24</v>
       </c>
       <c r="D8" s="133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" s="7">
         <v>2.21</v>
@@ -4784,7 +4333,7 @@
       <c r="F8" s="88">
         <v>151158.84501451589</v>
       </c>
-      <c r="G8" s="191">
+      <c r="G8" s="189">
         <v>144100</v>
       </c>
       <c r="H8" s="131">
@@ -4815,16 +4364,16 @@
         <v>183638.86791538683</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7">
         <v>25</v>
       </c>
       <c r="D9" s="133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" s="7">
         <v>4.21</v>
@@ -4832,7 +4381,7 @@
       <c r="F9" s="88">
         <v>177670.97348426332</v>
       </c>
-      <c r="G9" s="192">
+      <c r="G9" s="190">
         <f>214701-G34</f>
         <v>177670.97519999999</v>
       </c>
@@ -4863,16 +4412,16 @@
         <v>346174.13038131909</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7">
         <v>26</v>
       </c>
       <c r="D10" s="133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="7">
         <v>2.84</v>
@@ -4880,7 +4429,7 @@
       <c r="F10" s="88">
         <v>229352.20620596872</v>
       </c>
-      <c r="G10" s="191">
+      <c r="G10" s="189">
         <v>185159</v>
       </c>
       <c r="H10" s="131">
@@ -4911,16 +4460,16 @@
         <v>273217.84737832687</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7">
         <v>27</v>
       </c>
       <c r="D11" s="133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="7">
         <v>3.43</v>
@@ -4928,7 +4477,7 @@
       <c r="F11" s="88">
         <v>235209.2316</v>
       </c>
-      <c r="G11" s="191">
+      <c r="G11" s="189">
         <f>223626</f>
         <v>223626</v>
       </c>
@@ -4961,16 +4510,16 @@
       </c>
       <c r="P11" s="109"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7">
         <v>28</v>
       </c>
       <c r="D12" s="133" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="7">
         <v>2.84</v>
@@ -4978,7 +4527,7 @@
       <c r="F12" s="88">
         <v>194750.50080000001</v>
       </c>
-      <c r="G12" s="192">
+      <c r="G12" s="190">
         <f>F12</f>
         <v>194750.50080000001</v>
       </c>
@@ -5009,16 +4558,16 @@
         <v>236973.04880000002</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7">
         <v>29</v>
       </c>
       <c r="D13" s="133" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" s="7">
         <v>3.43</v>
@@ -5026,7 +4575,7 @@
       <c r="F13" s="88">
         <v>235208.87231924172</v>
       </c>
-      <c r="G13" s="192">
+      <c r="G13" s="190">
         <f>235209-G50</f>
         <v>194750.26919999998</v>
       </c>
@@ -5057,16 +4606,16 @@
         <v>326887.37190639623</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7">
         <v>30</v>
       </c>
       <c r="D14" s="133" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="7">
         <v>2.84</v>
@@ -5074,7 +4623,7 @@
       <c r="F14" s="88">
         <v>194750.50080000001</v>
       </c>
-      <c r="G14" s="191">
+      <c r="G14" s="189">
         <f>185159</f>
         <v>185159</v>
       </c>
@@ -5106,16 +4655,16 @@
         <v>236540.03964800003</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7">
         <v>31</v>
       </c>
       <c r="D15" s="133" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
@@ -5123,7 +4672,7 @@
       <c r="F15" s="88">
         <v>235208.61604653395</v>
       </c>
-      <c r="G15" s="192">
+      <c r="G15" s="190">
         <f>235209+34287-G35</f>
         <v>235208.94</v>
       </c>
@@ -5155,16 +4704,16 @@
         <v>273400.90920932597</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7">
         <v>32</v>
       </c>
       <c r="D16" s="133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
@@ -5172,7 +4721,7 @@
       <c r="F16" s="88">
         <v>220949.42580066071</v>
       </c>
-      <c r="G16" s="192">
+      <c r="G16" s="190">
         <f>220949+33601-G49</f>
         <v>220948.68119999999</v>
       </c>
@@ -5203,16 +4752,16 @@
         <v>226373.83807670037</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7">
         <v>33</v>
       </c>
       <c r="D17" s="133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" s="7">
         <v>3.43</v>
@@ -5220,7 +4769,7 @@
       <c r="F17" s="88">
         <v>250529.74491111474</v>
       </c>
-      <c r="G17" s="191">
+      <c r="G17" s="189">
         <f>318418-G47-G48</f>
         <v>250529.62119999999</v>
       </c>
@@ -5252,16 +4801,16 @@
         <v>273401.38373378164</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7">
         <v>34</v>
       </c>
       <c r="D18" s="133" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" s="7">
         <v>2.84</v>
@@ -5269,7 +4818,7 @@
       <c r="F18" s="88">
         <v>194180.49558325135</v>
       </c>
-      <c r="G18" s="191">
+      <c r="G18" s="189">
         <f>223000-G51</f>
         <v>183912.75160000002</v>
       </c>
@@ -5301,16 +4850,16 @@
         <v>237256.85742224642</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7">
         <v>35</v>
       </c>
       <c r="D19" s="133" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="7">
         <v>3.43</v>
@@ -5318,7 +4867,7 @@
       <c r="F19" s="88">
         <v>235209.45796516797</v>
       </c>
-      <c r="G19" s="192">
+      <c r="G19" s="190">
         <f>272239-G41</f>
         <v>235208.97519999999</v>
       </c>
@@ -5350,16 +4899,16 @@
         <v>273401.76433107804</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7">
         <v>36</v>
       </c>
       <c r="D20" s="133" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="7">
         <v>2.84</v>
@@ -5367,7 +4916,7 @@
       <c r="F20" s="88">
         <v>194750.27110707472</v>
       </c>
-      <c r="G20" s="191">
+      <c r="G20" s="189">
         <f>217106-G38</f>
         <v>183504.68119999999</v>
       </c>
@@ -5399,16 +4948,16 @@
         <v>238293.37410149921</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7">
         <v>37</v>
       </c>
       <c r="D21" s="133" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" s="7">
         <v>3.43</v>
@@ -5416,7 +4965,7 @@
       <c r="F21" s="88">
         <v>235209.86029179581</v>
       </c>
-      <c r="G21" s="191">
+      <c r="G21" s="189">
         <f>272240-G45</f>
         <v>235209.97519999999</v>
       </c>
@@ -5448,16 +4997,16 @@
         <v>273401.13079730357</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7">
         <v>38</v>
       </c>
       <c r="D22" s="167" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
@@ -5465,7 +5014,7 @@
       <c r="F22" s="88">
         <v>194750.50080000001</v>
       </c>
-      <c r="G22" s="191">
+      <c r="G22" s="189">
         <v>185159</v>
       </c>
       <c r="H22" s="131">
@@ -5496,16 +5045,16 @@
         <v>236540.03964800003</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7">
         <v>39</v>
       </c>
       <c r="D23" s="133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" s="7">
         <v>3.43</v>
@@ -5513,7 +5062,7 @@
       <c r="F23" s="88">
         <v>57370.666484095156</v>
       </c>
-      <c r="G23" s="192">
+      <c r="G23" s="190">
         <f>118871-G46</f>
         <v>84583.94</v>
       </c>
@@ -5544,16 +5093,16 @@
         <v>255155.18267314087</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7">
         <v>40</v>
       </c>
       <c r="D24" s="133" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" s="7">
         <v>2.84</v>
@@ -5561,7 +5110,7 @@
       <c r="F24" s="88">
         <v>191483.98867107474</v>
       </c>
-      <c r="G24" s="191">
+      <c r="G24" s="189">
         <f>232000-G37</f>
         <v>198398.68119999999</v>
       </c>
@@ -5569,7 +5118,7 @@
         <f t="shared" si="0"/>
         <v>-6914.692528925254</v>
       </c>
-      <c r="I24" s="181">
+      <c r="I24" s="179">
         <v>5</v>
       </c>
       <c r="J24" s="88">
@@ -5593,16 +5142,16 @@
         <v>219043.47471933925</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7">
         <v>41</v>
       </c>
       <c r="D25" s="133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="7">
         <v>3.43</v>
@@ -5610,7 +5159,7 @@
       <c r="F25" s="88">
         <v>235209.2316</v>
       </c>
-      <c r="G25" s="191">
+      <c r="G25" s="189">
         <f>F25</f>
         <v>235209.2316</v>
       </c>
@@ -5641,16 +5190,16 @@
         <v>284001.25259999995</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7">
         <v>42</v>
       </c>
       <c r="D26" s="133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="7">
         <v>6</v>
@@ -5658,7 +5207,7 @@
       <c r="F26" s="88">
         <v>-556256.30998396303</v>
       </c>
-      <c r="G26" s="192">
+      <c r="G26" s="190">
         <f>-G30-G31-G36</f>
         <v>-109032.8508</v>
       </c>
@@ -5690,16 +5239,16 @@
         <v>4196.0532649992037</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7">
         <v>43</v>
       </c>
       <c r="D27" s="133" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" s="7">
         <v>5.89</v>
@@ -5707,7 +5256,7 @@
       <c r="F27" s="88">
         <v>403845.12633526558</v>
       </c>
-      <c r="G27" s="191">
+      <c r="G27" s="189">
         <f>483391-G39-G40</f>
         <v>403845.0208</v>
       </c>
@@ -5739,16 +5288,16 @@
         <v>469485.06166738155</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7">
         <v>44</v>
       </c>
       <c r="D28" s="133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" s="7">
         <v>5.89</v>
@@ -5756,7 +5305,7 @@
       <c r="F28" s="88">
         <v>304604.19637654093</v>
       </c>
-      <c r="G28" s="191">
+      <c r="G28" s="189">
         <f>353860-G32-G33</f>
         <v>281171.43280000001</v>
       </c>
@@ -5788,16 +5337,16 @@
         <v>494323.67919113341</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7">
         <v>45</v>
       </c>
       <c r="D29" s="133" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29" s="7">
         <v>5.89</v>
@@ -5805,13 +5354,13 @@
       <c r="F29" s="88">
         <v>316080.21825669997</v>
       </c>
-      <c r="G29" s="192">
-        <f>-G42-G43-G44+RESUMEN!D60</f>
-        <v>-12010.373200000002</v>
-      </c>
-      <c r="H29" s="132">
+      <c r="G29" s="190" t="e">
+        <f>-G42-G43-G44+RESUMEN!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H29" s="132" t="e">
         <f t="shared" si="0"/>
-        <v>328090.5914567</v>
+        <v>#REF!</v>
       </c>
       <c r="I29" s="106">
         <v>5</v>
@@ -5828,25 +5377,25 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="6" t="e">
         <f t="shared" si="4"/>
-        <v>771000.92145669996</v>
-      </c>
-      <c r="N29" s="11">
+        <v>#REF!</v>
+      </c>
+      <c r="N29" s="11" t="e">
         <f t="shared" si="1"/>
-        <v>817260.97674410196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7">
         <v>1</v>
       </c>
       <c r="D30" s="133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="7">
         <v>0.54</v>
@@ -5854,7 +5403,7 @@
       <c r="F30" s="88">
         <v>37030.024799999999</v>
       </c>
-      <c r="G30" s="191">
+      <c r="G30" s="189">
         <f t="shared" ref="G30:G34" si="6">F30</f>
         <v>37030.024799999999</v>
       </c>
@@ -5884,16 +5433,16 @@
         <v>43042.762800000004</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7">
         <v>2</v>
       </c>
       <c r="D31" s="133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" s="7">
         <v>0.55000000000000004</v>
@@ -5901,7 +5450,7 @@
       <c r="F31" s="88">
         <v>37715.766000000003</v>
       </c>
-      <c r="G31" s="191">
+      <c r="G31" s="189">
         <f t="shared" si="6"/>
         <v>37715.766000000003</v>
       </c>
@@ -5931,16 +5480,16 @@
         <v>43839.85100000001</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7">
         <v>3</v>
       </c>
       <c r="D32" s="133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" s="7">
         <v>0.45</v>
@@ -5948,7 +5497,7 @@
       <c r="F32" s="88">
         <v>30858.354000000003</v>
       </c>
-      <c r="G32" s="191">
+      <c r="G32" s="189">
         <f>F32</f>
         <v>30858.354000000003</v>
       </c>
@@ -5978,16 +5527,16 @@
         <v>35868.969000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7">
         <v>4</v>
       </c>
       <c r="D33" s="133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E33" s="7">
         <v>0.61</v>
@@ -5995,7 +5544,7 @@
       <c r="F33" s="88">
         <v>41830.213199999998</v>
       </c>
-      <c r="G33" s="191">
+      <c r="G33" s="189">
         <f t="shared" si="6"/>
         <v>41830.213199999998</v>
       </c>
@@ -6025,16 +5574,16 @@
         <v>48622.3802</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7">
         <v>5</v>
       </c>
       <c r="D34" s="133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" s="7">
         <v>0.54</v>
@@ -6042,7 +5591,7 @@
       <c r="F34" s="88">
         <v>37030.024799999999</v>
       </c>
-      <c r="G34" s="191">
+      <c r="G34" s="189">
         <f t="shared" si="6"/>
         <v>37030.024799999999</v>
       </c>
@@ -6072,16 +5621,16 @@
         <v>43042.762800000004</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7">
         <v>6</v>
       </c>
       <c r="D35" s="133" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
@@ -6089,7 +5638,7 @@
       <c r="F35" s="11">
         <v>34287.06</v>
       </c>
-      <c r="G35" s="192">
+      <c r="G35" s="190">
         <f>F35</f>
         <v>34287.06</v>
       </c>
@@ -6119,16 +5668,16 @@
         <v>39854.410000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7">
         <v>7</v>
       </c>
       <c r="D36" s="133" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E36" s="7">
         <v>0.5</v>
@@ -6136,7 +5685,7 @@
       <c r="F36" s="88">
         <v>34287.06</v>
       </c>
-      <c r="G36" s="191">
+      <c r="G36" s="189">
         <f t="shared" ref="G36:G41" si="7">F36</f>
         <v>34287.06</v>
       </c>
@@ -6166,16 +5715,16 @@
         <v>39854.410000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7">
         <v>8</v>
       </c>
       <c r="D37" s="133" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="7">
         <v>0.49</v>
@@ -6183,7 +5732,7 @@
       <c r="F37" s="88">
         <v>33601.318800000001</v>
       </c>
-      <c r="G37" s="191">
+      <c r="G37" s="189">
         <f t="shared" si="7"/>
         <v>33601.318800000001</v>
       </c>
@@ -6213,16 +5762,16 @@
         <v>39057.321799999998</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7">
         <v>9</v>
       </c>
       <c r="D38" s="133" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38" s="7">
         <v>0.49</v>
@@ -6230,7 +5779,7 @@
       <c r="F38" s="88">
         <v>33601.318800000001</v>
       </c>
-      <c r="G38" s="191">
+      <c r="G38" s="189">
         <f t="shared" si="7"/>
         <v>33601.318800000001</v>
       </c>
@@ -6260,16 +5809,16 @@
         <v>39057.321799999998</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7">
         <v>10</v>
       </c>
       <c r="D39" s="133" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" s="7">
         <v>0.59</v>
@@ -6277,7 +5826,7 @@
       <c r="F39" s="88">
         <v>40458.730800000005</v>
       </c>
-      <c r="G39" s="191">
+      <c r="G39" s="189">
         <f t="shared" si="7"/>
         <v>40458.730800000005</v>
       </c>
@@ -6307,16 +5856,16 @@
         <v>47028.203800000003</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7">
         <v>11</v>
       </c>
       <c r="D40" s="133" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40" s="7">
         <v>0.56999999999999995</v>
@@ -6324,7 +5873,7 @@
       <c r="F40" s="88">
         <v>39087.248399999997</v>
       </c>
-      <c r="G40" s="191">
+      <c r="G40" s="189">
         <f t="shared" si="7"/>
         <v>39087.248399999997</v>
       </c>
@@ -6354,16 +5903,16 @@
         <v>45434.027399999999</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7">
         <v>12</v>
       </c>
       <c r="D41" s="133" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E41" s="7">
         <v>0.54</v>
@@ -6371,7 +5920,7 @@
       <c r="F41" s="88">
         <v>37030.024799999999</v>
       </c>
-      <c r="G41" s="191">
+      <c r="G41" s="189">
         <f t="shared" si="7"/>
         <v>37030.024799999999</v>
       </c>
@@ -6401,16 +5950,16 @@
         <v>43042.762800000004</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7">
         <v>13</v>
       </c>
       <c r="D42" s="133" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E42" s="7">
         <v>0.55000000000000004</v>
@@ -6418,7 +5967,7 @@
       <c r="F42" s="88">
         <v>37715.766000000003</v>
       </c>
-      <c r="G42" s="191">
+      <c r="G42" s="189">
         <f>F42</f>
         <v>37715.766000000003</v>
       </c>
@@ -6448,16 +5997,16 @@
         <v>43839.85100000001</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7">
         <v>14</v>
       </c>
       <c r="D43" s="133" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="7">
         <v>0.45</v>
@@ -6465,7 +6014,7 @@
       <c r="F43" s="88">
         <v>30858.354000000003</v>
       </c>
-      <c r="G43" s="191">
+      <c r="G43" s="189">
         <f t="shared" ref="G43:G44" si="8">F43</f>
         <v>30858.354000000003</v>
       </c>
@@ -6496,19 +6045,19 @@
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>4085903.0498919981</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>984410.16989199817</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7">
         <v>15</v>
       </c>
       <c r="D44" s="133" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E44" s="7">
         <v>0.61</v>
@@ -6516,7 +6065,7 @@
       <c r="F44" s="88">
         <v>41830.213199999998</v>
       </c>
-      <c r="G44" s="191">
+      <c r="G44" s="189">
         <f t="shared" si="8"/>
         <v>41830.213199999998</v>
       </c>
@@ -6546,16 +6095,16 @@
         <v>48622.3802</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7">
         <v>16</v>
       </c>
       <c r="D45" s="133" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E45" s="7">
         <v>0.54</v>
@@ -6563,7 +6112,7 @@
       <c r="F45" s="88">
         <v>37030.024799999999</v>
       </c>
-      <c r="G45" s="191">
+      <c r="G45" s="189">
         <f t="shared" ref="G45:G51" si="9">F45</f>
         <v>37030.024799999999</v>
       </c>
@@ -6593,16 +6142,16 @@
         <v>43042.762800000004</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7">
         <v>17</v>
       </c>
       <c r="D46" s="133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E46" s="7">
         <v>0.5</v>
@@ -6610,7 +6159,7 @@
       <c r="F46" s="88">
         <v>34287.06</v>
       </c>
-      <c r="G46" s="191">
+      <c r="G46" s="189">
         <f>F46</f>
         <v>34287.06</v>
       </c>
@@ -6640,19 +6189,19 @@
         <v>39854.410000000003</v>
       </c>
       <c r="Q46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7">
         <v>18</v>
       </c>
       <c r="D47" s="133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E47" s="7">
         <v>0.5</v>
@@ -6660,7 +6209,7 @@
       <c r="F47" s="88">
         <v>34287.06</v>
       </c>
-      <c r="G47" s="191">
+      <c r="G47" s="189">
         <f t="shared" si="9"/>
         <v>34287.06</v>
       </c>
@@ -6695,16 +6244,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7">
         <v>19</v>
       </c>
       <c r="D48" s="133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E48" s="7">
         <v>0.49</v>
@@ -6712,7 +6261,7 @@
       <c r="F48" s="88">
         <v>33601.318800000001</v>
       </c>
-      <c r="G48" s="191">
+      <c r="G48" s="189">
         <f t="shared" si="9"/>
         <v>33601.318800000001</v>
       </c>
@@ -6742,9 +6291,9 @@
         <v>39057.321799999998</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7">
@@ -6760,7 +6309,7 @@
       <c r="F49" s="88">
         <v>33601.318800000001</v>
       </c>
-      <c r="G49" s="191">
+      <c r="G49" s="189">
         <f>F49</f>
         <v>33601.318800000001</v>
       </c>
@@ -6790,16 +6339,16 @@
         <v>39057.321799999998</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7">
         <v>21</v>
       </c>
       <c r="D50" s="133" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E50" s="7">
         <v>0.59</v>
@@ -6807,7 +6356,7 @@
       <c r="F50" s="88">
         <v>40458.730800000005</v>
       </c>
-      <c r="G50" s="192">
+      <c r="G50" s="190">
         <f>F50</f>
         <v>40458.730800000005</v>
       </c>
@@ -6837,16 +6386,16 @@
         <v>47028.203800000003</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7">
         <v>22</v>
       </c>
       <c r="D51" s="133" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E51" s="7">
         <v>0.56999999999999995</v>
@@ -6854,7 +6403,7 @@
       <c r="F51" s="88">
         <v>39087.248399999997</v>
       </c>
-      <c r="G51" s="191">
+      <c r="G51" s="189">
         <f t="shared" si="9"/>
         <v>39087.248399999997</v>
       </c>
@@ -6884,7 +6433,7 @@
         <v>45434.027399999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="89"/>
       <c r="B52" s="89"/>
       <c r="C52" s="89"/>
@@ -6897,9 +6446,9 @@
         <f>SUM(F7:F51)</f>
         <v>5354343.2489072988</v>
       </c>
-      <c r="G52" s="90">
+      <c r="G52" s="90" t="e">
         <f>SUM(G7:G51)</f>
-        <v>5340180.0816379944</v>
+        <v>#REF!</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
@@ -6915,51 +6464,51 @@
         <f>SUM(L7:L51)</f>
         <v>50000</v>
       </c>
-      <c r="M52" s="91">
+      <c r="M52" s="91" t="e">
         <f>SUM(M7:M51)</f>
-        <v>7387677.1173773035</v>
-      </c>
-      <c r="N52" s="90">
+        <v>#REF!</v>
+      </c>
+      <c r="N52" s="90" t="e">
         <f>SUM(N7:N51)</f>
-        <v>7830937.744419938</v>
+        <v>#REF!</v>
       </c>
       <c r="P52" s="135"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-4085903.0498919981</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="235"/>
-      <c r="D54" s="235"/>
-      <c r="E54" s="235"/>
-      <c r="F54" s="235"/>
-      <c r="G54" s="235"/>
-      <c r="H54" s="235"/>
-      <c r="I54" s="235"/>
-      <c r="J54" s="235"/>
-      <c r="K54" s="235"/>
-      <c r="L54" s="235"/>
-      <c r="M54" s="235"/>
-      <c r="N54" s="235"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="235"/>
-      <c r="D55" s="235"/>
-      <c r="E55" s="235"/>
-      <c r="F55" s="235"/>
-      <c r="G55" s="235"/>
-      <c r="H55" s="235"/>
-      <c r="I55" s="235"/>
-      <c r="J55" s="235"/>
-      <c r="K55" s="235"/>
-      <c r="L55" s="235"/>
-      <c r="M55" s="235"/>
-      <c r="N55" s="235"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-984410.16989199817</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="224"/>
+      <c r="D54" s="224"/>
+      <c r="E54" s="224"/>
+      <c r="F54" s="224"/>
+      <c r="G54" s="224"/>
+      <c r="H54" s="224"/>
+      <c r="I54" s="224"/>
+      <c r="J54" s="224"/>
+      <c r="K54" s="224"/>
+      <c r="L54" s="224"/>
+      <c r="M54" s="224"/>
+      <c r="N54" s="224"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="224"/>
+      <c r="D55" s="224"/>
+      <c r="E55" s="224"/>
+      <c r="F55" s="224"/>
+      <c r="G55" s="224"/>
+      <c r="H55" s="224"/>
+      <c r="I55" s="224"/>
+      <c r="J55" s="224"/>
+      <c r="K55" s="224"/>
+      <c r="L55" s="224"/>
+      <c r="M55" s="224"/>
+      <c r="N55" s="224"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="168"/>
       <c r="D56" s="168"/>
       <c r="E56" s="168"/>
@@ -6973,108 +6522,113 @@
       <c r="M56" s="168"/>
       <c r="N56" s="168"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="235" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="235"/>
-      <c r="E57" s="235"/>
-      <c r="F57" s="235"/>
-      <c r="G57" s="235"/>
-      <c r="H57" s="235"/>
-      <c r="I57" s="235"/>
-      <c r="J57" s="235"/>
-      <c r="K57" s="235"/>
-      <c r="L57" s="235"/>
-      <c r="M57" s="235"/>
-      <c r="N57" s="235"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="235"/>
-      <c r="D58" s="235"/>
-      <c r="E58" s="235"/>
-      <c r="F58" s="235"/>
-      <c r="G58" s="235"/>
-      <c r="H58" s="235"/>
-      <c r="I58" s="235"/>
-      <c r="J58" s="235"/>
-      <c r="K58" s="235"/>
-      <c r="L58" s="235"/>
-      <c r="M58" s="235"/>
-      <c r="N58" s="235"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="235"/>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
-      <c r="H59" s="235"/>
-      <c r="I59" s="235"/>
-      <c r="J59" s="235"/>
-      <c r="K59" s="235"/>
-      <c r="L59" s="235"/>
-      <c r="M59" s="235"/>
-      <c r="N59" s="235"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="235"/>
-      <c r="D60" s="235"/>
-      <c r="E60" s="235"/>
-      <c r="F60" s="235"/>
-      <c r="G60" s="235"/>
-      <c r="H60" s="235"/>
-      <c r="I60" s="235"/>
-      <c r="J60" s="235"/>
-      <c r="K60" s="235"/>
-      <c r="L60" s="235"/>
-      <c r="M60" s="235"/>
-      <c r="N60" s="235"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="235"/>
-      <c r="D61" s="235"/>
-      <c r="E61" s="235"/>
-      <c r="F61" s="235"/>
-      <c r="G61" s="235"/>
-      <c r="H61" s="235"/>
-      <c r="I61" s="235"/>
-      <c r="J61" s="235"/>
-      <c r="K61" s="235"/>
-      <c r="L61" s="235"/>
-      <c r="M61" s="235"/>
-      <c r="N61" s="235"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="235"/>
-      <c r="D62" s="235"/>
-      <c r="E62" s="235"/>
-      <c r="F62" s="235"/>
-      <c r="G62" s="235"/>
-      <c r="H62" s="235"/>
-      <c r="I62" s="235"/>
-      <c r="J62" s="235"/>
-      <c r="K62" s="235"/>
-      <c r="L62" s="235"/>
-      <c r="M62" s="235"/>
-      <c r="N62" s="235"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="235"/>
-      <c r="D63" s="235"/>
-      <c r="E63" s="235"/>
-      <c r="F63" s="235"/>
-      <c r="G63" s="235"/>
-      <c r="H63" s="235"/>
-      <c r="I63" s="235"/>
-      <c r="J63" s="235"/>
-      <c r="K63" s="235"/>
-      <c r="L63" s="235"/>
-      <c r="M63" s="235"/>
-      <c r="N63" s="235"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="224" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="224"/>
+      <c r="E57" s="224"/>
+      <c r="F57" s="224"/>
+      <c r="G57" s="224"/>
+      <c r="H57" s="224"/>
+      <c r="I57" s="224"/>
+      <c r="J57" s="224"/>
+      <c r="K57" s="224"/>
+      <c r="L57" s="224"/>
+      <c r="M57" s="224"/>
+      <c r="N57" s="224"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="224"/>
+      <c r="D58" s="224"/>
+      <c r="E58" s="224"/>
+      <c r="F58" s="224"/>
+      <c r="G58" s="224"/>
+      <c r="H58" s="224"/>
+      <c r="I58" s="224"/>
+      <c r="J58" s="224"/>
+      <c r="K58" s="224"/>
+      <c r="L58" s="224"/>
+      <c r="M58" s="224"/>
+      <c r="N58" s="224"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="224"/>
+      <c r="D59" s="224"/>
+      <c r="E59" s="224"/>
+      <c r="F59" s="224"/>
+      <c r="G59" s="224"/>
+      <c r="H59" s="224"/>
+      <c r="I59" s="224"/>
+      <c r="J59" s="224"/>
+      <c r="K59" s="224"/>
+      <c r="L59" s="224"/>
+      <c r="M59" s="224"/>
+      <c r="N59" s="224"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="224"/>
+      <c r="D60" s="224"/>
+      <c r="E60" s="224"/>
+      <c r="F60" s="224"/>
+      <c r="G60" s="224"/>
+      <c r="H60" s="224"/>
+      <c r="I60" s="224"/>
+      <c r="J60" s="224"/>
+      <c r="K60" s="224"/>
+      <c r="L60" s="224"/>
+      <c r="M60" s="224"/>
+      <c r="N60" s="224"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="224"/>
+      <c r="D61" s="224"/>
+      <c r="E61" s="224"/>
+      <c r="F61" s="224"/>
+      <c r="G61" s="224"/>
+      <c r="H61" s="224"/>
+      <c r="I61" s="224"/>
+      <c r="J61" s="224"/>
+      <c r="K61" s="224"/>
+      <c r="L61" s="224"/>
+      <c r="M61" s="224"/>
+      <c r="N61" s="224"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="224"/>
+      <c r="D62" s="224"/>
+      <c r="E62" s="224"/>
+      <c r="F62" s="224"/>
+      <c r="G62" s="224"/>
+      <c r="H62" s="224"/>
+      <c r="I62" s="224"/>
+      <c r="J62" s="224"/>
+      <c r="K62" s="224"/>
+      <c r="L62" s="224"/>
+      <c r="M62" s="224"/>
+      <c r="N62" s="224"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="224"/>
+      <c r="D63" s="224"/>
+      <c r="E63" s="224"/>
+      <c r="F63" s="224"/>
+      <c r="G63" s="224"/>
+      <c r="H63" s="224"/>
+      <c r="I63" s="224"/>
+      <c r="J63" s="224"/>
+      <c r="K63" s="224"/>
+      <c r="L63" s="224"/>
+      <c r="M63" s="224"/>
+      <c r="N63" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -7087,11 +6641,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -7101,21 +6650,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="48"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
       <c r="D1" s="50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="50"/>
       <c r="F1" s="49"/>
@@ -7125,7 +6674,7 @@
       <c r="J1" s="49"/>
       <c r="K1" s="49"/>
       <c r="L1" s="50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M1" s="49"/>
       <c r="N1" s="52" t="str">
@@ -7134,12 +6683,12 @@
       </c>
       <c r="O1" s="52"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="49"/>
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
       <c r="D2" s="50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="49"/>
       <c r="F2" s="49"/>
@@ -7153,7 +6702,7 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
@@ -7164,7 +6713,7 @@
       <c r="H3" s="49"/>
       <c r="I3" s="49"/>
       <c r="J3" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K3" s="50"/>
       <c r="L3" s="53">
@@ -7176,7 +6725,7 @@
       </c>
       <c r="O3" s="54"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -7187,7 +6736,7 @@
       <c r="H4" s="49"/>
       <c r="I4" s="49"/>
       <c r="J4" s="50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K4" s="50"/>
       <c r="L4" s="53">
@@ -7197,92 +6746,92 @@
       <c r="N4" s="49"/>
       <c r="O4" s="49"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="246" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="239" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="239" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="246" t="s">
+      <c r="D5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="E5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="239" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="246" t="s">
+      <c r="G5" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="H5" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="J5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="K5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="41"/>
+      <c r="N5" s="239" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="37" t="s">
+      <c r="O5" s="239" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="240"/>
+      <c r="B6" s="240"/>
+      <c r="C6" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="41"/>
-      <c r="N5" s="246" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="246" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="247"/>
-      <c r="B6" s="247"/>
-      <c r="C6" s="56" t="s">
+      <c r="E6" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="240"/>
+      <c r="G6" s="44" t="s">
         <v>81</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="247"/>
-      <c r="G6" s="44" t="s">
-        <v>82</v>
       </c>
       <c r="H6" s="45">
         <v>0.06</v>
       </c>
       <c r="I6" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="47" t="s">
+      <c r="L6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="L6" s="44" t="s">
-        <v>85</v>
-      </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="247"/>
-      <c r="O6" s="247"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="240"/>
+      <c r="O6" s="240"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>1</v>
       </c>
       <c r="B7" s="84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="87">
         <v>5.4</v>
@@ -7323,12 +6872,12 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2</v>
       </c>
       <c r="B8" s="84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="87">
         <v>5.5</v>
@@ -7369,12 +6918,12 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>3</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="87">
         <v>4.5</v>
@@ -7415,12 +6964,12 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>4</v>
       </c>
       <c r="B10" s="84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="87">
         <v>6.1</v>
@@ -7461,12 +7010,12 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>5</v>
       </c>
       <c r="B11" s="84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="87">
         <v>5.4</v>
@@ -7507,12 +7056,12 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>6</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="87">
         <v>5</v>
@@ -7553,12 +7102,12 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>7</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="87">
         <v>5</v>
@@ -7599,12 +7148,12 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>8</v>
       </c>
       <c r="B14" s="84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="87">
         <v>4.9000000000000004</v>
@@ -7645,12 +7194,12 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>9</v>
       </c>
       <c r="B15" s="84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="87">
         <v>4.9000000000000004</v>
@@ -7691,12 +7240,12 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>10</v>
       </c>
       <c r="B16" s="84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="87">
         <v>5.9</v>
@@ -7737,12 +7286,12 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>11</v>
       </c>
       <c r="B17" s="84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="87">
         <v>5.7</v>
@@ -7783,12 +7332,12 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>12</v>
       </c>
       <c r="B18" s="84" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="87">
         <v>5.4</v>
@@ -7829,12 +7378,12 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>13</v>
       </c>
       <c r="B19" s="84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="87">
         <v>5.5</v>
@@ -7875,12 +7424,12 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>14</v>
       </c>
       <c r="B20" s="84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="87">
         <v>4.5</v>
@@ -7921,12 +7470,12 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>15</v>
       </c>
       <c r="B21" s="84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="87">
         <v>6.1</v>
@@ -7967,12 +7516,12 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>16</v>
       </c>
       <c r="B22" s="84" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="87">
         <v>5.4</v>
@@ -8013,12 +7562,12 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>17</v>
       </c>
       <c r="B23" s="84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="87">
         <v>5</v>
@@ -8059,12 +7608,12 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>18</v>
       </c>
       <c r="B24" s="84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="87">
         <v>5</v>
@@ -8105,12 +7654,12 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>19</v>
       </c>
       <c r="B25" s="84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="87">
         <v>4.9000000000000004</v>
@@ -8151,12 +7700,12 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>20</v>
       </c>
       <c r="B26" s="84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="87">
         <v>4.9000000000000004</v>
@@ -8197,12 +7746,12 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>21</v>
       </c>
       <c r="B27" s="84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="87">
         <v>5.9</v>
@@ -8243,12 +7792,12 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>22</v>
       </c>
       <c r="B28" s="86" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="87">
         <v>5.7</v>
@@ -8289,7 +7838,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -8306,7 +7855,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="57">
@@ -8347,7 +7896,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
     </row>

--- a/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
+++ b/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90BB971-2B50-48B3-B655-D18EB9D9A53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FF792-8844-4D2D-8B52-8A1F3FA21A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="COCHERA" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId3"/>
+    <sheet name="COCHERA" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$128</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="180">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -474,24 +475,9 @@
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
-    <t>Ingreso mes de MAYO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kromacolor </t>
   </si>
   <si>
-    <t>Numero 1859135 Debito automatico 02/06</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 04/06</t>
-  </si>
-  <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 12/06</t>
-  </si>
-  <si>
     <t>Contessi - Mantenimiento de ascensores</t>
   </si>
   <si>
@@ -504,18 +490,9 @@
     <t>Subidos en jun de 2025</t>
   </si>
   <si>
-    <t>Kromacolor - Compra de materiales para hall, gimnasio, membrana, recuplast para terraza, lija, etc</t>
-  </si>
-  <si>
-    <t>Kromacolor - Compra de materiales sistemal, aguarras</t>
-  </si>
-  <si>
     <t>Kromacolor</t>
   </si>
   <si>
-    <t>QUEDARON PENDIENTES TRES PARA JULI</t>
-  </si>
-  <si>
     <t>BALBOA, ARIEL</t>
   </si>
   <si>
@@ -561,17 +538,77 @@
     <t xml:space="preserve">Sr. Diego Britez </t>
   </si>
   <si>
-    <t xml:space="preserve">Leonardo Balcalazza - </t>
-  </si>
-  <si>
     <t>Honorarios JULIO</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 01/07</t>
+  </si>
+  <si>
+    <t>Debito 14/07</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 01/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra de materiales </t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Recapeo vereda, puntas de canteros</t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Mano de obra montavehiculos, pintura piso y paredes</t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Pintura techo hall de entrada</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 10/07</t>
+  </si>
+  <si>
+    <t>Vto. 04/07</t>
+  </si>
+  <si>
+    <t>Vto. 31/07</t>
+  </si>
+  <si>
+    <t>EL MES ANTERIOR ATILIO QUEDO CON UN SALDO A FAVOR DE:</t>
+  </si>
+  <si>
+    <t>UF 42</t>
+  </si>
+  <si>
+    <t>COCHERA 1</t>
+  </si>
+  <si>
+    <t>COCHERA 2</t>
+  </si>
+  <si>
+    <t>COCHERA 7</t>
+  </si>
+  <si>
+    <t>SI A LAS EXPENSAS DEL MES PASADO LES CONTEMPLAMOS EL DINERO A FAVOR:</t>
+  </si>
+  <si>
+    <t>LAS EXPENSAS DEL MES PASADO FUERON (AL 01/07):</t>
+  </si>
+  <si>
+    <t>DINERO TOTAL A ABONAR:</t>
+  </si>
+  <si>
+    <t>YA ABONO:</t>
+  </si>
+  <si>
+    <t>Ingreso mes de JUNIO</t>
+  </si>
+  <si>
+    <t>A GASTON LO HABIAMOS PUESTO COMO DEUDOR( FIJARSE EN EL PDF) Y NO LO ERA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
@@ -580,6 +617,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0000"/>
     <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1292,7 +1330,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1451,7 +1489,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1564,20 +1601,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1644,21 +1699,24 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1689,19 +1747,25 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="2" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1710,16 +1774,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="170" fontId="6" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2085,7 +2140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2143,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
@@ -2174,26 +2229,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="199" t="s">
+      <c r="B14" s="204" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="200"/>
-      <c r="D14" s="201"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="206"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="202"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="204"/>
+      <c r="B15" s="207"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="209"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="202"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="204"/>
+      <c r="B16" s="207"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="209"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="205"/>
-      <c r="C17" s="206"/>
-      <c r="D17" s="207"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="212"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
@@ -2206,85 +2261,85 @@
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="59"/>
-      <c r="E21" s="146" t="s">
+      <c r="E21" s="145" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="145" t="s">
+      <c r="F21" s="144" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="121" t="s">
-        <v>165</v>
+      <c r="A22" s="120" t="s">
+        <v>157</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="130"/>
+      <c r="D22" s="129"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="121" t="s">
+      <c r="A23" s="120" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="180">
-        <v>1869737.25</v>
-      </c>
-      <c r="E23" s="134">
+      <c r="D23" s="179">
+        <v>1262522.3</v>
+      </c>
+      <c r="E23" s="133">
         <f>D23*91.91%</f>
-        <v>1718475.5064749999</v>
-      </c>
-      <c r="F23" s="134">
+        <v>1160384.24593</v>
+      </c>
+      <c r="F23" s="133">
         <f>D23*8.09%</f>
-        <v>151261.743525</v>
+        <v>102138.05407</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="121" t="s">
+      <c r="A24" s="120" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="180">
-        <v>-406667.86</v>
-      </c>
-      <c r="E24" s="134">
+      <c r="D24" s="179">
+        <v>-274598.59999999998</v>
+      </c>
+      <c r="E24" s="133">
         <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
-        <v>-373768.43012599996</v>
-      </c>
-      <c r="F24" s="134">
+        <v>-252383.57325999995</v>
+      </c>
+      <c r="F24" s="133">
         <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
-        <v>-32899.429874000001</v>
+        <v>-22215.026739999998</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="121" t="s">
+      <c r="A25" s="120" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="180">
-        <v>0.61</v>
-      </c>
-      <c r="E25" s="134">
+      <c r="D25" s="179">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="133">
         <f t="shared" si="0"/>
-        <v>0.5606509999999999</v>
-      </c>
-      <c r="F25" s="134">
+        <v>0.27572999999999998</v>
+      </c>
+      <c r="F25" s="133">
         <f t="shared" si="1"/>
-        <v>4.9348999999999997E-2</v>
+        <v>2.427E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="121"/>
+      <c r="A26" s="120"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="180"/>
-      <c r="E26" s="134"/>
+      <c r="D26" s="179"/>
+      <c r="E26" s="133"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2295,21 +2350,21 @@
       <c r="C27" s="95"/>
       <c r="D27" s="107">
         <f>SUM(D23:D26)</f>
-        <v>1463070.0000000002</v>
+        <v>987924.00000000012</v>
       </c>
       <c r="E27" s="107">
         <f>SUM(E23:E26)</f>
-        <v>1344707.6369999999</v>
+        <v>908000.94839999999</v>
       </c>
       <c r="F27" s="107">
         <f>SUM(F23:F26)</f>
-        <v>118362.363</v>
-      </c>
-      <c r="G27" s="109">
+        <v>79923.051599999992</v>
+      </c>
+      <c r="G27" s="108">
         <f>E27+F27</f>
-        <v>1463069.9999999998</v>
-      </c>
-      <c r="H27" s="150" t="str">
+        <v>987924</v>
+      </c>
+      <c r="H27" s="149" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
@@ -2320,53 +2375,53 @@
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="181">
-        <v>0</v>
-      </c>
-      <c r="E28" s="134">
+      <c r="D28" s="180">
+        <v>0</v>
+      </c>
+      <c r="E28" s="133">
         <f>D28*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F28" s="134">
+      <c r="F28" s="133">
         <f>D28*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H28" s="150"/>
+      <c r="H28" s="149"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="180">
-        <v>0</v>
-      </c>
-      <c r="E29" s="134">
+      <c r="D29" s="179">
+        <v>0</v>
+      </c>
+      <c r="E29" s="133">
         <f>D29*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F29" s="134">
+      <c r="F29" s="133">
         <f>D29*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H29" s="150"/>
+      <c r="H29" s="149"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="180"/>
+      <c r="D30" s="179"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="H30" s="150"/>
+      <c r="H30" s="149"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="180"/>
+      <c r="D31" s="179"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="H31" s="150"/>
+      <c r="H31" s="149"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="95" t="s">
@@ -2386,11 +2441,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G32" s="109">
+      <c r="G32" s="108">
         <f>E32+F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="150" t="str">
+      <c r="H32" s="149" t="str">
         <f>IF(D32=G32, "", "Error")</f>
         <v/>
       </c>
@@ -2401,16 +2456,16 @@
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="181"/>
-      <c r="E33" s="134">
+      <c r="D33" s="180"/>
+      <c r="E33" s="133">
         <f>D33*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F33" s="134">
+      <c r="F33" s="133">
         <f>D33*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H33" s="150"/>
+      <c r="H33" s="149"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2418,16 +2473,16 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="180"/>
-      <c r="E34" s="134">
+      <c r="D34" s="179"/>
+      <c r="E34" s="133">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F34" s="134">
+      <c r="F34" s="133">
         <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H34" s="150"/>
+      <c r="H34" s="149"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="94" t="s">
@@ -2435,16 +2490,16 @@
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="180"/>
-      <c r="E35" s="134">
+      <c r="D35" s="179"/>
+      <c r="E35" s="133">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="134">
+      <c r="F35" s="133">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="150"/>
+      <c r="H35" s="149"/>
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="95" t="s">
@@ -2460,38 +2515,38 @@
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="119">
+      <c r="F36" s="118">
         <f>E36*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H36" s="150"/>
+      <c r="H36" s="149"/>
     </row>
     <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="129"/>
+      <c r="A37" s="128"/>
       <c r="B37" s="98"/>
       <c r="C37" s="98"/>
-      <c r="D37" s="180"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="H37" s="150"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="119"/>
+      <c r="H37" s="149"/>
     </row>
     <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="129"/>
+      <c r="A38" s="128"/>
       <c r="B38" s="98"/>
       <c r="C38" s="98"/>
-      <c r="D38" s="180"/>
-      <c r="E38" s="120"/>
-      <c r="F38" s="120"/>
-      <c r="H38" s="150"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="119"/>
+      <c r="H38" s="149"/>
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="98"/>
       <c r="B39" s="98"/>
-      <c r="C39" s="111"/>
-      <c r="D39" s="180"/>
-      <c r="E39" s="120"/>
-      <c r="F39" s="120"/>
-      <c r="H39" s="150"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="H39" s="149"/>
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
@@ -2500,68 +2555,68 @@
       <c r="B40" s="95"/>
       <c r="C40" s="95"/>
       <c r="D40" s="107"/>
-      <c r="E40" s="112">
+      <c r="E40" s="111">
         <f>SUM(D37:D39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="110">
+      <c r="F40" s="109">
         <f>(D37)*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H40" s="150"/>
+      <c r="H40" s="149"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="94" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="195">
+      <c r="D41" s="112">
         <v>3567.21</v>
       </c>
-      <c r="E41" s="134">
+      <c r="E41" s="133">
         <f>D41*91.91%</f>
         <v>3278.6227109999995</v>
       </c>
-      <c r="F41" s="134">
+      <c r="F41" s="133">
         <f>D41*8.09%</f>
         <v>288.587289</v>
       </c>
-      <c r="H41" s="150"/>
+      <c r="H41" s="149"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="94" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="195">
+      <c r="D42" s="112">
         <v>37000</v>
       </c>
-      <c r="E42" s="134">
+      <c r="E42" s="133">
         <f>D42*91.91%</f>
         <v>34006.699999999997</v>
       </c>
-      <c r="F42" s="134">
+      <c r="F42" s="133">
         <f>D42*8.09%</f>
         <v>2993.3</v>
       </c>
-      <c r="H42" s="150"/>
+      <c r="H42" s="149"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="94"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="134">
+      <c r="D43" s="182"/>
+      <c r="E43" s="133">
         <f>D43*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F43" s="134">
+      <c r="F43" s="133">
         <f>D43*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H43" s="150"/>
+      <c r="H43" s="149"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
@@ -2573,19 +2628,19 @@
         <f>SUM(D41:D43)</f>
         <v>40567.21</v>
       </c>
-      <c r="E44" s="159">
+      <c r="E44" s="158">
         <f>SUM(E41:E43)</f>
         <v>37285.322710999993</v>
       </c>
-      <c r="F44" s="169">
+      <c r="F44" s="168">
         <f>SUM(F41:F43)</f>
         <v>3281.8872890000002</v>
       </c>
-      <c r="G44" s="109">
+      <c r="G44" s="108">
         <f>E44+F44</f>
         <v>40567.209999999992</v>
       </c>
-      <c r="H44" s="150"/>
+      <c r="H44" s="149"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
@@ -2593,1496 +2648,1521 @@
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="114"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="113"/>
       <c r="F45" s="100"/>
-      <c r="H45" s="150"/>
+      <c r="H45" s="149"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="98"/>
-      <c r="D46" s="113">
+      <c r="D46" s="112">
         <v>5020</v>
       </c>
-      <c r="E46" s="134">
+      <c r="E46" s="133">
         <f>D46*91.91%</f>
         <v>4613.8819999999996</v>
       </c>
-      <c r="F46" s="134">
+      <c r="F46" s="133">
         <f>D46*8.09%</f>
         <v>406.11799999999999</v>
       </c>
-      <c r="H46" s="150"/>
+      <c r="H46" s="149"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="94" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="195">
+      <c r="D47" s="112">
         <f>157828.92+9348.69+84138.18</f>
         <v>251315.79</v>
       </c>
-      <c r="E47" s="134">
+      <c r="E47" s="133">
         <f>D47*91.91%</f>
         <v>230984.34258899998</v>
       </c>
-      <c r="F47" s="134">
+      <c r="F47" s="133">
         <f>D47*8.09%</f>
         <v>20331.447411000001</v>
       </c>
-      <c r="H47" s="150"/>
+      <c r="H47" s="149"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="94" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="195">
+      <c r="D48" s="112">
         <v>828107.55</v>
       </c>
-      <c r="E48" s="134">
+      <c r="E48" s="133">
         <f>D48*91.91%</f>
         <v>761113.64920500002</v>
       </c>
-      <c r="F48" s="134">
+      <c r="F48" s="133">
         <f>D48*8.09%</f>
         <v>66993.900795000009</v>
       </c>
-      <c r="H48" s="150"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H48" s="149"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="96"/>
       <c r="C49" s="96"/>
-      <c r="D49" s="108">
+      <c r="D49" s="107">
         <f>SUM(D46:D48)</f>
         <v>1084443.3400000001</v>
       </c>
-      <c r="E49" s="108">
+      <c r="E49" s="107">
         <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
         <v>996711.87379400001</v>
       </c>
-      <c r="F49" s="108">
+      <c r="F49" s="107">
         <f t="shared" si="6"/>
         <v>87731.466206000012</v>
       </c>
-      <c r="G49" s="109">
+      <c r="G49" s="108">
         <f>E49+F49</f>
         <v>1084443.3400000001</v>
       </c>
-      <c r="H49" s="150" t="str">
+      <c r="H49" s="149" t="str">
         <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="115"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="114"/>
       <c r="F50" s="7"/>
-      <c r="H50" s="150"/>
-    </row>
-    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="188" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="176"/>
-      <c r="C51" s="177"/>
-      <c r="D51" s="196">
+      <c r="H50" s="149"/>
+    </row>
+    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="187" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" s="175"/>
+      <c r="C51" s="176"/>
+      <c r="D51" s="182">
         <v>960000</v>
       </c>
-      <c r="E51" s="149">
+      <c r="E51" s="148">
         <f>D51</f>
         <v>960000</v>
       </c>
       <c r="F51" s="7"/>
-      <c r="G51" s="109">
+      <c r="G51" s="108">
         <f>D51</f>
         <v>960000</v>
       </c>
-      <c r="H51" s="161">
+      <c r="H51" s="160">
         <f>E51+F51</f>
         <v>960000</v>
       </c>
-      <c r="I51" s="178">
-        <f t="shared" ref="I51:I69" si="7">H51-D51</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="178">
-        <f t="shared" ref="J51:J69" si="8">G51-D51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="188" t="s">
-        <v>143</v>
-      </c>
-      <c r="B52" s="176"/>
-      <c r="C52" s="177"/>
-      <c r="D52" s="195">
+      <c r="I51" s="177">
+        <f t="shared" ref="I51:I70" si="7">H51-D51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="177">
+        <f t="shared" ref="J51:J70" si="8">G51-D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="187" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="175"/>
+      <c r="C52" s="176"/>
+      <c r="D52" s="112">
         <v>372000</v>
       </c>
-      <c r="E52" s="149">
+      <c r="E52" s="148">
         <f>D52</f>
         <v>372000</v>
       </c>
       <c r="F52" s="7"/>
-      <c r="G52" s="109">
+      <c r="G52" s="108">
         <f>D52</f>
         <v>372000</v>
       </c>
-      <c r="H52" s="161">
+      <c r="H52" s="160">
         <f>E52+F52</f>
         <v>372000</v>
       </c>
-      <c r="I52" s="178">
+      <c r="I52" s="177">
         <f>H52-D52</f>
         <v>0</v>
       </c>
-      <c r="J52" s="178"/>
-    </row>
-    <row r="53" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="242" t="s">
-        <v>163</v>
-      </c>
-      <c r="B53" s="243"/>
-      <c r="C53" s="244"/>
-      <c r="D53" s="195">
+      <c r="J52" s="177"/>
+    </row>
+    <row r="53" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="199" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="200"/>
+      <c r="C53" s="201"/>
+      <c r="D53" s="112">
         <v>165500</v>
       </c>
-      <c r="E53" s="149">
-        <f t="shared" ref="E53:E58" si="9">D53*91.91%</f>
+      <c r="E53" s="148">
+        <f t="shared" ref="E53:E59" si="9">D53*91.91%</f>
         <v>152111.04999999999</v>
       </c>
-      <c r="F53" s="134">
-        <f t="shared" ref="F53:F58" si="10">D53*8.09%</f>
+      <c r="F53" s="133">
+        <f t="shared" ref="F53:F59" si="10">D53*8.09%</f>
         <v>13388.95</v>
       </c>
-      <c r="G53" s="109">
-        <f t="shared" ref="G53:G69" si="11">D53</f>
+      <c r="G53" s="108">
+        <f t="shared" ref="G53:G70" si="11">D53</f>
         <v>165500</v>
       </c>
-      <c r="H53" s="161">
-        <f t="shared" ref="H53:H69" si="12">E53+F53</f>
+      <c r="H53" s="160">
+        <f t="shared" ref="H53:H70" si="12">E53+F53</f>
         <v>165500</v>
       </c>
-      <c r="I53" s="178">
+      <c r="I53" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J53" s="178">
+      <c r="J53" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="121" t="s">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="163"/>
+      <c r="B54" s="162"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="195">
+      <c r="D54" s="112">
         <v>148124.67000000001</v>
       </c>
-      <c r="E54" s="149">
+      <c r="E54" s="148">
         <f t="shared" si="9"/>
         <v>136141.38419700001</v>
       </c>
-      <c r="F54" s="134">
+      <c r="F54" s="133">
         <f t="shared" si="10"/>
         <v>11983.285803000001</v>
       </c>
-      <c r="G54" s="109">
+      <c r="G54" s="108">
         <f t="shared" si="11"/>
         <v>148124.67000000001</v>
       </c>
-      <c r="H54" s="161">
+      <c r="H54" s="160">
         <f t="shared" si="12"/>
         <v>148124.67000000001</v>
       </c>
-      <c r="I54" s="178"/>
-      <c r="J54" s="178"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I54" s="177"/>
+      <c r="J54" s="177"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="94" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="195">
+      <c r="D55" s="112">
         <v>148200</v>
       </c>
-      <c r="E55" s="149">
+      <c r="E55" s="148">
         <f t="shared" si="9"/>
         <v>136210.62</v>
       </c>
-      <c r="F55" s="134">
+      <c r="F55" s="133">
         <f t="shared" si="10"/>
         <v>11989.38</v>
       </c>
-      <c r="G55" s="109">
+      <c r="G55" s="108">
         <f t="shared" si="11"/>
         <v>148200</v>
       </c>
-      <c r="H55" s="161">
+      <c r="H55" s="160">
         <f t="shared" si="12"/>
         <v>148200</v>
       </c>
-      <c r="I55" s="178">
+      <c r="I55" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J55" s="178">
+      <c r="J55" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="94" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="113">
-        <v>74623.7</v>
-      </c>
-      <c r="E56" s="149">
+      <c r="D56" s="112">
+        <v>129320</v>
+      </c>
+      <c r="E56" s="148">
         <f>D56*91.91%</f>
-        <v>68586.642669999987</v>
-      </c>
-      <c r="F56" s="134">
+        <v>118858.01199999999</v>
+      </c>
+      <c r="F56" s="133">
         <f t="shared" si="10"/>
-        <v>6037.0573299999996</v>
-      </c>
-      <c r="G56" s="109">
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G56" s="108">
         <f t="shared" si="11"/>
-        <v>74623.7</v>
-      </c>
-      <c r="H56" s="161">
+        <v>129320</v>
+      </c>
+      <c r="H56" s="160">
         <f>E56+F56</f>
-        <v>74623.699999999983</v>
-      </c>
-      <c r="I56" s="178">
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I56" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J56" s="178">
+      <c r="J56" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="7"/>
+      <c r="B57" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="C57" s="7"/>
-      <c r="D57" s="195">
+      <c r="D57" s="112">
         <v>614674.98</v>
       </c>
-      <c r="E57" s="149">
+      <c r="E57" s="148">
         <f t="shared" si="9"/>
         <v>564947.77411799994</v>
       </c>
-      <c r="F57" s="134">
+      <c r="F57" s="133">
         <f t="shared" si="10"/>
         <v>49727.205881999995</v>
       </c>
-      <c r="G57" s="109">
+      <c r="G57" s="108">
         <f t="shared" si="11"/>
         <v>614674.98</v>
       </c>
-      <c r="H57" s="161">
+      <c r="H57" s="160">
         <f t="shared" si="12"/>
         <v>614674.98</v>
       </c>
-      <c r="I57" s="178">
+      <c r="I57" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J57" s="178">
+      <c r="J57" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="129" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="112">
+        <v>641235.69999999995</v>
+      </c>
+      <c r="E58" s="148">
+        <f t="shared" si="9"/>
+        <v>589359.7318699999</v>
+      </c>
+      <c r="F58" s="133">
+        <f t="shared" si="10"/>
+        <v>51875.968129999994</v>
+      </c>
+      <c r="G58" s="108">
+        <f t="shared" si="11"/>
+        <v>641235.69999999995</v>
+      </c>
+      <c r="H58" s="160">
+        <f t="shared" si="12"/>
+        <v>641235.69999999995</v>
+      </c>
+      <c r="I58" s="177">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="177">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="98" t="s">
-        <v>160</v>
-      </c>
-      <c r="C58" s="98"/>
-      <c r="D58" s="195">
+      <c r="B59" s="98" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="98"/>
+      <c r="D59" s="112">
         <v>1101493.94</v>
       </c>
-      <c r="E58" s="149">
+      <c r="E59" s="148">
         <f t="shared" si="9"/>
         <v>1012383.0802539999</v>
       </c>
-      <c r="F58" s="134">
+      <c r="F59" s="133">
         <f t="shared" si="10"/>
         <v>89110.859746000002</v>
       </c>
-      <c r="G58" s="109">
+      <c r="G59" s="108">
         <f t="shared" si="11"/>
         <v>1101493.94</v>
       </c>
-      <c r="H58" s="161">
+      <c r="H59" s="160">
         <f t="shared" si="12"/>
         <v>1101493.94</v>
       </c>
-      <c r="I58" s="178">
+      <c r="I59" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J58" s="178">
+      <c r="J59" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="219" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59" s="220"/>
-      <c r="C59" s="221"/>
-      <c r="D59" s="195">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="196" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="197"/>
+      <c r="C60" s="198"/>
+      <c r="D60" s="112">
         <v>65500</v>
       </c>
-      <c r="E59" s="149">
-        <f t="shared" ref="E59:E63" si="13">D59</f>
+      <c r="E60" s="148">
+        <f t="shared" ref="E60:E65" si="13">D60</f>
         <v>65500</v>
       </c>
-      <c r="F59" s="134"/>
-      <c r="G59" s="109">
+      <c r="F60" s="133"/>
+      <c r="G60" s="108">
         <f t="shared" si="11"/>
         <v>65500</v>
       </c>
-      <c r="H59" s="161">
+      <c r="H60" s="160">
         <f t="shared" si="12"/>
         <v>65500</v>
       </c>
-      <c r="I59" s="178">
+      <c r="I60" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J59" s="178">
+      <c r="J60" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="191" t="s">
-        <v>158</v>
-      </c>
-      <c r="B60" s="192"/>
-      <c r="C60" s="187"/>
-      <c r="D60" s="195">
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="188" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="189"/>
+      <c r="C61" s="186"/>
+      <c r="D61" s="112">
         <v>90000</v>
       </c>
-      <c r="E60" s="149">
+      <c r="E61" s="148">
         <f t="shared" si="13"/>
         <v>90000</v>
       </c>
-      <c r="F60" s="134"/>
-      <c r="G60" s="109">
+      <c r="F61" s="133"/>
+      <c r="G61" s="108">
         <f t="shared" si="11"/>
         <v>90000</v>
       </c>
-      <c r="H60" s="161">
+      <c r="H61" s="160">
         <f t="shared" si="12"/>
         <v>90000</v>
       </c>
-      <c r="I60" s="178">
+      <c r="I61" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J60" s="178">
+      <c r="J61" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B61" s="114"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="195">
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" s="113"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="112">
         <v>29200</v>
       </c>
-      <c r="E61" s="149">
+      <c r="E62" s="148">
         <f t="shared" si="13"/>
         <v>29200</v>
       </c>
-      <c r="F61" s="134"/>
-      <c r="G61" s="109">
+      <c r="F62" s="133"/>
+      <c r="G62" s="108">
         <f t="shared" si="11"/>
         <v>29200</v>
       </c>
-      <c r="H61" s="161">
+      <c r="H62" s="160">
         <f t="shared" si="12"/>
         <v>29200</v>
       </c>
-      <c r="I61" s="178">
+      <c r="I62" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J61" s="178"/>
-    </row>
-    <row r="62" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="219" t="s">
-        <v>166</v>
-      </c>
-      <c r="B62" s="220"/>
-      <c r="C62" s="221"/>
-      <c r="D62" s="241"/>
-      <c r="E62" s="149">
+      <c r="J62" s="177"/>
+    </row>
+    <row r="63" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="196" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="197"/>
+      <c r="C63" s="198"/>
+      <c r="D63" s="112">
+        <f>380000+350000</f>
+        <v>730000</v>
+      </c>
+      <c r="E63" s="148">
+        <f t="shared" ref="E63:E69" si="14">D63*91.91%</f>
+        <v>670942.99999999988</v>
+      </c>
+      <c r="F63" s="133">
+        <f t="shared" ref="F63:F69" si="15">D63*8.09%</f>
+        <v>59057</v>
+      </c>
+      <c r="G63" s="108">
+        <f t="shared" si="11"/>
+        <v>730000</v>
+      </c>
+      <c r="H63" s="160">
+        <f t="shared" si="12"/>
+        <v>729999.99999999988</v>
+      </c>
+      <c r="I63" s="177">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="177"/>
+    </row>
+    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="196" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="197"/>
+      <c r="C64" s="198"/>
+      <c r="D64" s="112">
+        <v>120000</v>
+      </c>
+      <c r="E64" s="148">
+        <f t="shared" si="14"/>
+        <v>110291.99999999999</v>
+      </c>
+      <c r="F64" s="133">
+        <f t="shared" si="15"/>
+        <v>9708</v>
+      </c>
+      <c r="G64" s="108"/>
+      <c r="H64" s="160"/>
+      <c r="I64" s="177"/>
+      <c r="J64" s="177"/>
+    </row>
+    <row r="65" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="196" t="s">
+        <v>164</v>
+      </c>
+      <c r="B65" s="197"/>
+      <c r="C65" s="198"/>
+      <c r="D65" s="112">
+        <v>480000</v>
+      </c>
+      <c r="E65" s="148">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="109">
+        <v>480000</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="160"/>
+      <c r="I65" s="177"/>
+      <c r="J65" s="177"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" s="98"/>
+      <c r="D66" s="112">
+        <v>232510.18</v>
+      </c>
+      <c r="E66" s="148">
+        <f t="shared" si="14"/>
+        <v>213700.10643799999</v>
+      </c>
+      <c r="F66" s="133">
+        <f t="shared" si="15"/>
+        <v>18810.073561999998</v>
+      </c>
+      <c r="G66" s="108">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="161">
+        <v>232510.18</v>
+      </c>
+      <c r="H66" s="160">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="178">
+        <v>232510.18</v>
+      </c>
+      <c r="I66" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J62" s="178"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="194" t="s">
-        <v>147</v>
-      </c>
-      <c r="B63" s="194"/>
-      <c r="C63" s="194"/>
-      <c r="D63" s="241">
-        <v>736429.26</v>
-      </c>
-      <c r="E63" s="149">
-        <f t="shared" si="13"/>
-        <v>736429.26</v>
-      </c>
-      <c r="F63" s="134"/>
-      <c r="G63" s="109">
+      <c r="J66" s="177">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M66" s="191" t="s">
+        <v>137</v>
+      </c>
+      <c r="N66" s="7"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="192">
+        <v>357622.29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" s="98"/>
+      <c r="D67" s="112">
+        <v>357622.29</v>
+      </c>
+      <c r="E67" s="148">
+        <f t="shared" si="14"/>
+        <v>328690.64673899993</v>
+      </c>
+      <c r="F67" s="133">
+        <f t="shared" si="15"/>
+        <v>28931.643260999997</v>
+      </c>
+      <c r="G67" s="108">
         <f t="shared" si="11"/>
-        <v>736429.26</v>
-      </c>
-      <c r="H63" s="161">
+        <v>357622.29</v>
+      </c>
+      <c r="H67" s="160">
         <f t="shared" si="12"/>
-        <v>736429.26</v>
-      </c>
-      <c r="I63" s="178">
+        <v>357622.28999999992</v>
+      </c>
+      <c r="I67" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J63" s="178">
+      <c r="J67" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M63" s="194" t="s">
-        <v>149</v>
-      </c>
-      <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="195">
-        <v>232510.18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="194" t="s">
-        <v>149</v>
-      </c>
-      <c r="B64" s="194" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" s="194"/>
-      <c r="D64" s="241"/>
-      <c r="E64" s="149">
-        <f t="shared" ref="E64:E68" si="14">D64*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F64" s="134">
-        <f t="shared" ref="F64:F68" si="15">D64*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="109">
+      <c r="M67" s="191" t="s">
+        <v>137</v>
+      </c>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="192">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" s="98"/>
+      <c r="D68" s="112">
+        <v>358487.12</v>
+      </c>
+      <c r="E68" s="148">
+        <f t="shared" si="14"/>
+        <v>329485.51199199999</v>
+      </c>
+      <c r="F68" s="133">
+        <f t="shared" si="15"/>
+        <v>29001.608007999999</v>
+      </c>
+      <c r="G68" s="108">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="161">
+        <v>358487.12</v>
+      </c>
+      <c r="H68" s="160">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="178">
+        <v>358487.12</v>
+      </c>
+      <c r="I68" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J64" s="178">
+      <c r="J68" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M64" s="194" t="s">
-        <v>138</v>
-      </c>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="195">
-        <v>357622.29</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="194" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="194" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" s="194"/>
-      <c r="D65" s="241"/>
-      <c r="E65" s="149">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="134">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G65" s="109">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="178">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="178">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="194" t="s">
-        <v>138</v>
-      </c>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="195">
-        <v>358487.12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="194" t="s">
-        <v>138</v>
-      </c>
-      <c r="B66" s="194" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" s="194"/>
-      <c r="D66" s="241"/>
-      <c r="E66" s="149">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F66" s="134">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G66" s="109">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="161">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="178">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="178">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="194" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" s="194"/>
-      <c r="C67" s="194"/>
-      <c r="D67" s="241">
-        <v>186859.86</v>
-      </c>
-      <c r="E67" s="149">
-        <f t="shared" ref="E67" si="16">D67</f>
-        <v>186859.86</v>
-      </c>
-      <c r="F67" s="134"/>
-      <c r="G67" s="109">
-        <f t="shared" si="11"/>
-        <v>186859.86</v>
-      </c>
-      <c r="H67" s="161">
-        <f t="shared" si="12"/>
-        <v>186859.86</v>
-      </c>
-      <c r="I67" s="178">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="178">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+    </row>
+    <row r="69" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="195">
+      <c r="B69" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="112">
         <v>83283.39</v>
       </c>
-      <c r="E68" s="149">
+      <c r="E69" s="148">
         <f t="shared" si="14"/>
         <v>76545.763748999991</v>
       </c>
-      <c r="F68" s="134">
+      <c r="F69" s="133">
         <f t="shared" si="15"/>
         <v>6737.6262509999997</v>
       </c>
-      <c r="G68" s="109">
+      <c r="G69" s="108">
         <f t="shared" si="11"/>
         <v>83283.39</v>
       </c>
-      <c r="H68" s="161">
+      <c r="H69" s="160">
         <f t="shared" si="12"/>
         <v>83283.389999999985</v>
       </c>
-      <c r="I68" s="178">
+      <c r="I69" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J68" s="178">
+      <c r="J69" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="98" t="s">
-        <v>161</v>
-      </c>
-      <c r="B69" s="114"/>
-      <c r="C69" s="162"/>
-      <c r="D69" s="195">
+    <row r="70" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="98" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="113"/>
+      <c r="C70" s="161"/>
+      <c r="D70" s="112">
         <v>300000</v>
       </c>
-      <c r="E69" s="149">
-        <f t="shared" ref="E69" si="17">D69</f>
+      <c r="E70" s="148">
+        <f t="shared" ref="E70" si="16">D70</f>
         <v>300000</v>
       </c>
-      <c r="F69" s="134"/>
-      <c r="G69" s="109">
+      <c r="F70" s="133"/>
+      <c r="G70" s="108">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="H69" s="161">
+      <c r="H70" s="160">
         <f t="shared" si="12"/>
         <v>300000</v>
       </c>
-      <c r="I69" s="178">
+      <c r="I70" s="177">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J69" s="178">
+      <c r="J70" s="177">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="155"/>
-      <c r="B70" s="156"/>
-      <c r="C70" s="156"/>
-      <c r="D70" s="166"/>
-      <c r="E70" s="149"/>
-      <c r="F70" s="134"/>
-      <c r="G70" s="109"/>
-      <c r="H70" s="161"/>
-      <c r="I70" t="str">
-        <f>IF(G70=H70, "", "Error")</f>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="154"/>
+      <c r="B71" s="155"/>
+      <c r="C71" s="155"/>
+      <c r="D71" s="165"/>
+      <c r="E71" s="148"/>
+      <c r="F71" s="133"/>
+      <c r="G71" s="108"/>
+      <c r="H71" s="160"/>
+      <c r="I71" t="str">
+        <f>IF(G71=H71, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="96" t="s">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="B71" s="96"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="108">
-        <f>SUM(D51:D70)</f>
-        <v>5075889.8</v>
-      </c>
-      <c r="E71" s="108">
-        <f>SUM(E51:E70)</f>
-        <v>4886915.4349879995</v>
-      </c>
-      <c r="F71" s="108">
-        <f>SUM(F51:F70)</f>
-        <v>188974.36501199999</v>
-      </c>
-      <c r="G71" s="109">
-        <f>E71+F71</f>
-        <v>5075889.8</v>
-      </c>
-      <c r="H71" s="150" t="str">
-        <f>IF(D71=G71, "", "Error")</f>
+      <c r="B72" s="96"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="107">
+        <f>SUM(D51:D71)</f>
+        <v>7127152.2699999986</v>
+      </c>
+      <c r="E72" s="107">
+        <f>SUM(E51:E71)</f>
+        <v>6736368.6813569991</v>
+      </c>
+      <c r="F72" s="107">
+        <f>SUM(F51:F71)</f>
+        <v>390783.58864299994</v>
+      </c>
+      <c r="G72" s="108">
+        <f>E72+F72</f>
+        <v>7127152.2699999986</v>
+      </c>
+      <c r="H72" s="149" t="str">
+        <f>IF(D72=G72, "", "Error")</f>
         <v/>
       </c>
-      <c r="I71" s="178">
-        <f>D71-G71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="183"/>
-      <c r="E72" s="115"/>
-      <c r="F72" s="7"/>
-      <c r="H72" s="150"/>
+      <c r="I72" s="177">
+        <f>D72-G72</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="183"/>
+      <c r="D73" s="182"/>
       <c r="E73" s="114"/>
       <c r="F73" s="7"/>
-      <c r="H73" s="150"/>
+      <c r="H73" s="149"/>
     </row>
     <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="183"/>
-      <c r="E74" s="114"/>
+      <c r="D74" s="182"/>
+      <c r="E74" s="113"/>
       <c r="F74" s="7"/>
-      <c r="H74" s="150"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="B75" s="98"/>
+      <c r="H74" s="149"/>
+    </row>
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="195">
+      <c r="D75" s="182"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="7"/>
+      <c r="H75" s="149"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="98"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="112">
         <f>127080+80450</f>
         <v>207530</v>
       </c>
-      <c r="E75" s="149">
-        <f>D75*91.91%</f>
+      <c r="E76" s="148">
+        <f>D76*91.91%</f>
         <v>190740.82299999997</v>
       </c>
-      <c r="F75" s="134">
-        <f>D75*8.09%</f>
+      <c r="F76" s="133">
+        <f>D76*8.09%</f>
         <v>16789.177</v>
       </c>
-      <c r="G75" s="160"/>
-      <c r="H75" s="150"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="113"/>
-      <c r="E76" s="164">
-        <f>D76</f>
-        <v>0</v>
-      </c>
-      <c r="F76" s="7"/>
-      <c r="H76" s="150"/>
-      <c r="I76" s="109"/>
-    </row>
-    <row r="77" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="95" t="s">
+      <c r="G76" s="159"/>
+      <c r="H76" s="149"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="112"/>
+      <c r="E77" s="163">
+        <f>D77</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="7"/>
+      <c r="H77" s="149"/>
+      <c r="I77" s="108"/>
+    </row>
+    <row r="78" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="95"/>
-      <c r="C77" s="95"/>
-      <c r="D77" s="107">
-        <f>SUM(D75:D76)</f>
+      <c r="B78" s="95"/>
+      <c r="C78" s="95"/>
+      <c r="D78" s="107">
+        <f>SUM(D76:D77)</f>
         <v>207530</v>
       </c>
-      <c r="E77" s="107">
-        <f>SUM(E75:E76)</f>
+      <c r="E78" s="107">
+        <f>SUM(E76:E77)</f>
         <v>190740.82299999997</v>
       </c>
-      <c r="F77" s="107">
-        <f>SUM(F75:F76)</f>
+      <c r="F78" s="107">
+        <f>SUM(F76:F77)</f>
         <v>16789.177</v>
       </c>
-      <c r="G77" s="109">
-        <f>E77+F77</f>
+      <c r="G78" s="108">
+        <f>E78+F78</f>
         <v>207529.99999999997</v>
       </c>
-      <c r="H77" s="150" t="str">
-        <f>IF(D77=G77, "", "Error")</f>
+      <c r="H78" s="149" t="str">
+        <f>IF(D78=G78, "", "Error")</f>
         <v/>
       </c>
-      <c r="J77" s="109"/>
-    </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="183"/>
-      <c r="E78" s="115"/>
-      <c r="F78" s="7"/>
-      <c r="H78" s="150"/>
+      <c r="J78" s="108"/>
     </row>
     <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="183"/>
+      <c r="D79" s="182"/>
       <c r="E79" s="114"/>
       <c r="F79" s="7"/>
-      <c r="H79" s="150"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="94" t="s">
-        <v>13</v>
-      </c>
+      <c r="H79" s="149"/>
+    </row>
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="183"/>
-      <c r="E80" s="114"/>
+      <c r="D80" s="182"/>
+      <c r="E80" s="113"/>
       <c r="F80" s="7"/>
-      <c r="H80" s="150"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H80" s="149"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="182"/>
+      <c r="E81" s="113"/>
+      <c r="F81" s="7"/>
+      <c r="H81" s="149"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B82" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="195">
+      <c r="C82" s="7"/>
+      <c r="D82" s="112">
         <v>246000</v>
       </c>
-      <c r="E81" s="149">
-        <f>D81*91.91%</f>
+      <c r="E82" s="148">
+        <f>D82*91.91%</f>
         <v>226098.59999999998</v>
       </c>
-      <c r="F81" s="134">
-        <f>D81*8.09%</f>
+      <c r="F82" s="133">
+        <f>D82*8.09%</f>
         <v>19901.400000000001</v>
       </c>
-      <c r="G81" t="s">
-        <v>146</v>
-      </c>
-      <c r="H81" s="150"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="94" t="s">
+      <c r="G82" t="s">
+        <v>141</v>
+      </c>
+      <c r="H82" s="149"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="195">
-        <v>30000</v>
-      </c>
-      <c r="E82" s="149">
-        <f>D82*91.91%</f>
-        <v>27572.999999999996</v>
-      </c>
-      <c r="F82" s="134">
-        <f>D82*8.09%</f>
-        <v>2427</v>
-      </c>
-      <c r="H82" s="150"/>
-      <c r="J82" s="113"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="183"/>
-      <c r="E83" s="116"/>
-      <c r="F83" s="7"/>
-      <c r="H83" s="150"/>
-      <c r="J83" s="109"/>
+      <c r="D83" s="112">
+        <v>30000</v>
+      </c>
+      <c r="E83" s="148">
+        <f>D83*91.91%</f>
+        <v>27572.999999999996</v>
+      </c>
+      <c r="F83" s="133">
+        <f>D83*8.09%</f>
+        <v>2427</v>
+      </c>
+      <c r="H83" s="149"/>
+      <c r="J83" s="112"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="95" t="s">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="182"/>
+      <c r="E84" s="115"/>
+      <c r="F84" s="7"/>
+      <c r="H84" s="149"/>
+      <c r="J84" s="108"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="B84" s="95"/>
-      <c r="C84" s="95"/>
-      <c r="D84" s="107">
-        <f>SUM(D81:D83)</f>
+      <c r="B85" s="95"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="107">
+        <f>SUM(D82:D84)</f>
         <v>276000</v>
       </c>
-      <c r="E84" s="107">
-        <f>SUM(E81:E83)</f>
+      <c r="E85" s="107">
+        <f>SUM(E82:E84)</f>
         <v>253671.59999999998</v>
       </c>
-      <c r="F84" s="107">
-        <f>SUM(F81:F83)</f>
+      <c r="F85" s="107">
+        <f>SUM(F82:F84)</f>
         <v>22328.400000000001</v>
       </c>
-      <c r="G84" s="109">
-        <f>E84+F84</f>
+      <c r="G85" s="108">
+        <f>E85+F85</f>
         <v>276000</v>
       </c>
-      <c r="H84" s="150" t="str">
-        <f>IF(D84=G84, "", "Error")</f>
+      <c r="H85" s="149" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-      <c r="J84" s="109"/>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="113"/>
-      <c r="E85" s="117"/>
-      <c r="F85" s="7"/>
-      <c r="H85" s="150"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="94" t="s">
-        <v>101</v>
-      </c>
+      <c r="J85" s="108"/>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="241">
-        <v>116023.77</v>
-      </c>
-      <c r="E86" s="149">
-        <f>D86*91.91%</f>
-        <v>106637.447007</v>
-      </c>
-      <c r="F86" s="134">
-        <f>D86*8.09%</f>
-        <v>9386.3229929999998</v>
-      </c>
-      <c r="H86" s="150"/>
+      <c r="D86" s="112"/>
+      <c r="E86" s="116"/>
+      <c r="F86" s="7"/>
+      <c r="H86" s="149"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="112">
+        <v>126577.59</v>
+      </c>
+      <c r="E87" s="148">
+        <f>D87*91.91%</f>
+        <v>116337.46296899999</v>
+      </c>
+      <c r="F87" s="133">
+        <f>D87*8.09%</f>
+        <v>10240.127031</v>
+      </c>
+      <c r="H87" s="149"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="B87" s="7"/>
-      <c r="C87" s="122"/>
-      <c r="D87" s="241">
+      <c r="B88" s="7"/>
+      <c r="C88" s="121"/>
+      <c r="D88" s="112">
         <v>44400</v>
       </c>
-      <c r="E87" s="149">
-        <f>D87*91.91%</f>
+      <c r="E88" s="148">
+        <f>D88*91.91%</f>
         <v>40808.039999999994</v>
       </c>
-      <c r="F87" s="134">
-        <f>D87*8.09%</f>
+      <c r="F88" s="133">
+        <f>D88*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H87" s="150"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="95" t="s">
+      <c r="H88" s="149"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B88" s="95"/>
-      <c r="C88" s="95"/>
-      <c r="D88" s="158">
-        <f>SUM(D86:D87)</f>
-        <v>160423.77000000002</v>
-      </c>
-      <c r="E88" s="147">
-        <f t="shared" ref="E88:F88" si="18">SUM(E86:E87)</f>
-        <v>147445.48700699999</v>
-      </c>
-      <c r="F88" s="147">
+      <c r="B89" s="95"/>
+      <c r="C89" s="95"/>
+      <c r="D89" s="157">
+        <f>SUM(D87:D88)</f>
+        <v>170977.59</v>
+      </c>
+      <c r="E89" s="146">
+        <f t="shared" ref="E89:F89" si="17">SUM(E87:E88)</f>
+        <v>157145.50296899996</v>
+      </c>
+      <c r="F89" s="146">
+        <f t="shared" si="17"/>
+        <v>13832.087030999999</v>
+      </c>
+      <c r="G89" s="108">
+        <f>E89+F89</f>
+        <v>170977.58999999997</v>
+      </c>
+      <c r="H89" s="149" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="183"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="7"/>
+      <c r="H90" s="149"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="99"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="184"/>
+      <c r="E91" s="117">
+        <f>D91*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="135">
+        <f>D91*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="108">
+        <f>E91+F91</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="149" t="str">
+        <f>IF(D91=G91, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="D92" s="181"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="156"/>
+      <c r="H92" s="149"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="60"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="185">
+        <f>SUM(D91+D89+D85+D78+D72+D49+D32+D27+D44)</f>
+        <v>9894594.4100000001</v>
+      </c>
+      <c r="E93" s="147">
+        <f>SUM(E91+E89+E85+E78+E72+E49+E32+E27+E44)</f>
+        <v>9279924.7522309981</v>
+      </c>
+      <c r="F93" s="147">
+        <f>SUM(F91+F89+F85+F78+F72+F49+F32+F27+F44)</f>
+        <v>614669.65776899992</v>
+      </c>
+      <c r="G93" s="108">
+        <f>E93+F93</f>
+        <v>9894594.4099999983</v>
+      </c>
+      <c r="H93" s="149" t="str">
+        <f>IF(D93=G93, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I93" s="177">
+        <f>D93-G93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="181"/>
+      <c r="E94" s="108"/>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="141" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" s="140"/>
+      <c r="C95" s="140"/>
+      <c r="E95" s="108"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="C96" s="138"/>
+      <c r="E96" s="108"/>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+      <c r="C97" s="138"/>
+      <c r="E97" s="108"/>
+    </row>
+    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" s="143"/>
+      <c r="C98" s="139">
+        <f>SUM(C96:C97)</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="108"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E99" s="108"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E100" s="136"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="222" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="223"/>
+      <c r="C101" s="223"/>
+      <c r="D101" s="223"/>
+      <c r="E101" s="170" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" s="171" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="219"/>
+      <c r="B102" s="220"/>
+      <c r="C102" s="221"/>
+      <c r="D102" s="165"/>
+      <c r="E102" s="148"/>
+      <c r="F102" s="133"/>
+    </row>
+    <row r="103" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="216"/>
+      <c r="B103" s="217"/>
+      <c r="C103" s="172"/>
+      <c r="D103" s="112"/>
+      <c r="E103" s="148">
+        <f t="shared" ref="E103:E104" si="18">D103*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="133">
+        <f t="shared" ref="F103:F104" si="19">D103*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="216"/>
+      <c r="B104" s="217"/>
+      <c r="C104" s="172"/>
+      <c r="D104" s="112"/>
+      <c r="E104" s="148">
         <f t="shared" si="18"/>
-        <v>12978.282993000001</v>
-      </c>
-      <c r="G88" s="109">
-        <f>E88+F88</f>
-        <v>160423.76999999999</v>
-      </c>
-      <c r="H88" s="150" t="str">
-        <f>IF(D88=G88, "", "Error")</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="133">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="216"/>
+      <c r="B105" s="217"/>
+      <c r="C105" s="218"/>
+      <c r="D105" s="112"/>
+      <c r="E105" s="148">
+        <f>D105*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="133">
+        <f>D105*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="213" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" s="214"/>
+      <c r="C106" s="215"/>
+      <c r="D106" s="169">
+        <f>SUM(D102:D105)</f>
+        <v>0</v>
+      </c>
+      <c r="E106" s="169">
+        <f>SUM(E102:E105)</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="169">
+        <f>SUM(F102:F105)</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="108">
+        <f>E106+F106</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="149" t="str">
+        <f>IF(D106=H106, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="184"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="7"/>
-      <c r="H89" s="150"/>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B90" s="99"/>
-      <c r="C90" s="99"/>
-      <c r="D90" s="185"/>
-      <c r="E90" s="118">
-        <f>D90*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="136">
-        <f>D90*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G90" s="109">
-        <f>E90+F90</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="150" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="D91" s="182"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="157"/>
-      <c r="H91" s="150"/>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="60"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="186">
-        <f>SUM(D90+D88+D84+D77+D71+D49+D32+D27+D44)</f>
-        <v>8307924.1200000001</v>
-      </c>
-      <c r="E92" s="148">
-        <f>SUM(E90+E88+E84+E77+E71+E49+E32+E27+E44)</f>
-        <v>7857478.1784999995</v>
-      </c>
-      <c r="F92" s="148">
-        <f>SUM(F90+F88+F84+F77+F71+F49+F32+F27+F44)</f>
-        <v>450445.94150000002</v>
-      </c>
-      <c r="G92" s="109">
-        <f>E92+F92</f>
-        <v>8307924.1199999992</v>
-      </c>
-      <c r="H92" s="150" t="str">
-        <f>IF(D92=G92, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I92" s="178">
-        <f>D92-G92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="182"/>
-      <c r="E93" s="109"/>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="142" t="s">
-        <v>120</v>
-      </c>
-      <c r="B94" s="141"/>
-      <c r="C94" s="141"/>
-      <c r="E94" s="109"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="C95" s="139"/>
-      <c r="E95" s="109"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-      <c r="C96" s="139"/>
-      <c r="E96" s="109"/>
-    </row>
-    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="143" t="s">
-        <v>29</v>
-      </c>
-      <c r="B97" s="144"/>
-      <c r="C97" s="140">
-        <f>SUM(C95:C96)</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="109"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E98" s="109"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E99" s="137"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="217" t="s">
-        <v>113</v>
-      </c>
-      <c r="B100" s="218"/>
-      <c r="C100" s="218"/>
-      <c r="D100" s="218"/>
-      <c r="E100" s="171" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="172" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="214"/>
-      <c r="B101" s="215"/>
-      <c r="C101" s="216"/>
-      <c r="D101" s="166"/>
-      <c r="E101" s="149"/>
-      <c r="F101" s="134"/>
-    </row>
-    <row r="102" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="211"/>
-      <c r="B102" s="212"/>
-      <c r="C102" s="173"/>
-      <c r="D102" s="113"/>
-      <c r="E102" s="149">
-        <f t="shared" ref="E102:E103" si="19">D102*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F102" s="134">
-        <f t="shared" ref="F102:F103" si="20">D102*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="211"/>
-      <c r="B103" s="212"/>
-      <c r="C103" s="173"/>
-      <c r="D103" s="113"/>
-      <c r="E103" s="149">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="134">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="211"/>
-      <c r="B104" s="212"/>
-      <c r="C104" s="213"/>
-      <c r="D104" s="113"/>
-      <c r="E104" s="149">
-        <f>D104*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F104" s="134">
-        <f>D104*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="208" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="209"/>
-      <c r="C105" s="210"/>
-      <c r="D105" s="170">
-        <f>SUM(D101:D104)</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="170">
-        <f>SUM(E101:E104)</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="170">
-        <f>SUM(F101:F104)</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="109">
-        <f>E105+F105</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="150" t="str">
-        <f>IF(D105=H105, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E107" s="109"/>
-    </row>
     <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="102" t="s">
+      <c r="E108" s="108"/>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="103">
-        <f>D92</f>
-        <v>8307924.1200000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="104" t="s">
+      <c r="B109" s="103">
+        <f>D93</f>
+        <v>9894594.4100000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="B109" s="105">
-        <f>D92-D90</f>
-        <v>8307924.1200000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D110" s="198"/>
-      <c r="E110" s="198"/>
+      <c r="B110" s="105">
+        <f>D93-D91</f>
+        <v>9894594.4100000001</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="74" t="s">
+      <c r="D111" s="203"/>
+      <c r="E111" s="203"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B111" s="75"/>
-      <c r="C111" s="76"/>
-      <c r="D111" s="198"/>
-      <c r="E111" s="198"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="77" t="s">
+      <c r="B112" s="75"/>
+      <c r="C112" s="76"/>
+      <c r="D112" s="203"/>
+      <c r="E112" s="203"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="B112" s="11">
-        <v>3924460.3236006536</v>
-      </c>
-      <c r="C112" s="78"/>
-      <c r="D112" s="198"/>
-      <c r="E112" s="198"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B113" s="92" t="e">
-        <f>PRORRATEO!G52</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C113" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="D113" s="198"/>
-      <c r="E113" s="198"/>
+      <c r="B113" s="11">
+        <v>-630321.16476135515</v>
+      </c>
+      <c r="C113" s="78"/>
+      <c r="D113" s="203"/>
+      <c r="E113" s="203"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114" s="175">
-        <f>-B109</f>
-        <v>-8307924.1200000001</v>
-      </c>
-      <c r="C114" s="76"/>
-      <c r="D114" s="198"/>
-      <c r="E114" s="198"/>
-      <c r="G114" s="113"/>
+        <v>92</v>
+      </c>
+      <c r="B114" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>6975889.7925080024</v>
+      </c>
+      <c r="C114" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D114" s="203"/>
+      <c r="E114" s="203"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="175">
-        <f>-D105</f>
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="B115" s="174">
+        <f>-B110</f>
+        <v>-9894594.4100000001</v>
       </c>
       <c r="C115" s="76"/>
-      <c r="D115" s="198"/>
-      <c r="E115" s="198"/>
-      <c r="G115" s="125"/>
+      <c r="D115" s="203"/>
+      <c r="E115" s="203"/>
+      <c r="G115" s="112"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="B116" s="175">
-        <f>-B123</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="80"/>
+        <v>114</v>
+      </c>
+      <c r="B116" s="174">
+        <f>-D106</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="76"/>
+      <c r="D116" s="203"/>
+      <c r="E116" s="203"/>
+      <c r="G116" s="124"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117" s="174">
+        <f>-B124</f>
+        <v>-50000</v>
+      </c>
+      <c r="C117" s="80"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B117" s="93">
-        <f>-C97</f>
-        <v>0</v>
-      </c>
-      <c r="C117" s="80"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="79"/>
-      <c r="B118" s="75"/>
+      <c r="B118" s="93">
+        <f>-C98</f>
+        <v>0</v>
+      </c>
       <c r="C118" s="80"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="77" t="s">
+      <c r="A119" s="79"/>
+      <c r="B119" s="75"/>
+      <c r="C119" s="80"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B119" s="81" t="e">
-        <f>SUM(B112:B118)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C119" s="154"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="80"/>
-      <c r="C120" s="76"/>
-      <c r="D120" s="83"/>
+      <c r="B120" s="81">
+        <f>SUM(B113:B119)</f>
+        <v>-3599025.7822533529</v>
+      </c>
+      <c r="C120" s="153"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="80"/>
       <c r="C121" s="76"/>
-      <c r="D121" s="109"/>
-      <c r="E121" s="178"/>
+      <c r="D121" s="83"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="74" t="s">
+      <c r="C122" s="76"/>
+      <c r="D122" s="108"/>
+      <c r="E122" s="177"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B123" s="11">
         <v>-365694.54000000004</v>
       </c>
-      <c r="C122" s="82"/>
-      <c r="D122" s="178"/>
-      <c r="E122" s="178"/>
-      <c r="F122" s="178"/>
-    </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="77" t="s">
-        <v>137</v>
-      </c>
-      <c r="B123" s="93"/>
       <c r="C123" s="82"/>
-      <c r="D123" s="178"/>
-      <c r="E123" s="193"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D123" s="177"/>
+      <c r="E123" s="177"/>
+      <c r="F123" s="177"/>
+    </row>
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="77" t="s">
-        <v>164</v>
-      </c>
-      <c r="B124" s="175">
+        <v>178</v>
+      </c>
+      <c r="B124" s="93">
+        <v>50000</v>
+      </c>
+      <c r="C124" s="82"/>
+      <c r="D124" s="177"/>
+      <c r="E124" s="190"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B125" s="174">
         <v>-37000</v>
       </c>
-      <c r="C124" s="82"/>
-      <c r="E124" s="109"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="77"/>
-      <c r="B125" s="175"/>
       <c r="C125" s="82"/>
-      <c r="E125" s="109"/>
+      <c r="E125" s="108"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="100" t="s">
+      <c r="A126" s="77"/>
+      <c r="B126" s="174"/>
+      <c r="C126" s="82"/>
+      <c r="E126" s="108"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="B126" s="101">
-        <f>SUM(B122:B125)</f>
-        <v>-402694.54000000004</v>
-      </c>
-      <c r="C126" s="82"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C127" s="83"/>
-      <c r="D127" s="178"/>
+      <c r="B127" s="101">
+        <f>SUM(B123:B126)</f>
+        <v>-352694.54000000004</v>
+      </c>
+      <c r="C127" s="82"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B128" s="80"/>
-      <c r="C128" s="76"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N130" s="12"/>
-    </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B133" s="197"/>
-      <c r="C133" s="197"/>
-      <c r="D133" s="197"/>
-      <c r="E133" s="197"/>
+      <c r="C128" s="83"/>
+      <c r="D128" s="177"/>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B129" s="80"/>
+      <c r="C129" s="76"/>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N131" s="12"/>
     </row>
     <row r="134" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B134" s="197"/>
-      <c r="C134" s="197"/>
-      <c r="D134" s="197"/>
-      <c r="E134" s="197"/>
+      <c r="B134" s="202"/>
+      <c r="C134" s="202"/>
+      <c r="D134" s="202"/>
+      <c r="E134" s="202"/>
     </row>
     <row r="135" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B135" s="197"/>
-      <c r="C135" s="197"/>
-      <c r="D135" s="197"/>
-      <c r="E135" s="197"/>
+      <c r="B135" s="202"/>
+      <c r="C135" s="202"/>
+      <c r="D135" s="202"/>
+      <c r="E135" s="202"/>
     </row>
     <row r="136" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B136" s="197"/>
-      <c r="C136" s="197"/>
-      <c r="D136" s="197"/>
-      <c r="E136" s="197"/>
+      <c r="B136" s="202"/>
+      <c r="C136" s="202"/>
+      <c r="D136" s="202"/>
+      <c r="E136" s="202"/>
     </row>
     <row r="137" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B137" s="197"/>
-      <c r="C137" s="197"/>
-      <c r="D137" s="197"/>
-      <c r="E137" s="197"/>
+      <c r="B137" s="202"/>
+      <c r="C137" s="202"/>
+      <c r="D137" s="202"/>
+      <c r="E137" s="202"/>
+    </row>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B138" s="202"/>
+      <c r="C138" s="202"/>
+      <c r="D138" s="202"/>
+      <c r="E138" s="202"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A62:C62"/>
+  <mergeCells count="14">
+    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A53:C53"/>
-    <mergeCell ref="B133:E137"/>
-    <mergeCell ref="D110:E115"/>
+    <mergeCell ref="B134:E138"/>
+    <mergeCell ref="D111:E116"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A104:B104"/>
     <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4128,15 +4208,15 @@
       <c r="K1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="225">
-        <f>RESUMEN!D92</f>
-        <v>8307924.1200000001</v>
-      </c>
-      <c r="M1" s="226"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="135">
+      <c r="L1" s="231">
+        <f>RESUMEN!D93</f>
+        <v>9894594.4100000001</v>
+      </c>
+      <c r="M1" s="232"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="134">
         <f>L1*8.09%</f>
-        <v>672111.061308</v>
+        <v>800472.68776899995</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4154,14 +4234,14 @@
         <v>125</v>
       </c>
       <c r="L2" s="8"/>
-      <c r="M2" s="152">
-        <f>(5500000-150000-3015-250-12+1997000+170000+5497+450+30)</f>
-        <v>7519700</v>
-      </c>
-      <c r="N2" s="153"/>
-      <c r="O2" s="135">
+      <c r="M2" s="151">
+        <f>7519700+7519700*10%</f>
+        <v>8271670</v>
+      </c>
+      <c r="N2" s="152"/>
+      <c r="O2" s="134">
         <f>O1-K7-553-50-86-8</f>
-        <v>259256.3812</v>
+        <v>185106.03000000003</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4182,11 +4262,11 @@
         <v>131</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="128">
-        <f>RESUMEN!D105</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="151"/>
+      <c r="M3" s="127">
+        <f>RESUMEN!D106</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="150"/>
       <c r="O3" s="73"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4199,7 +4279,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="123">
+      <c r="J4" s="122">
         <f>(J3*8.09%)/44</f>
         <v>0</v>
       </c>
@@ -4207,70 +4287,70 @@
         <v>125</v>
       </c>
       <c r="L4" s="8"/>
-      <c r="M4" s="128">
-        <v>0</v>
-      </c>
-      <c r="N4" s="124"/>
+      <c r="M4" s="127">
+        <v>0</v>
+      </c>
+      <c r="N4" s="123"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="222" t="s">
+      <c r="A5" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="236" t="s">
+      <c r="B5" s="226" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="224" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="234" t="s">
+      <c r="D5" s="228" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="222" t="s">
+      <c r="E5" s="224" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="222" t="s">
+      <c r="F5" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="222" t="s">
+      <c r="G5" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="229" t="s">
+      <c r="H5" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="234" t="s">
+      <c r="I5" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="227" t="s">
+      <c r="J5" s="233" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="227" t="s">
+      <c r="K5" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="232" t="s">
+      <c r="L5" s="238" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="227" t="s">
+      <c r="M5" s="233" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="227" t="s">
+      <c r="N5" s="233" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="223"/>
-      <c r="B6" s="237"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="238"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="230"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="228"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="228"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="227"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="236"/>
+      <c r="I6" s="240"/>
+      <c r="J6" s="234"/>
+      <c r="K6" s="237"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="237"/>
+      <c r="N6" s="234"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4280,40 +4360,40 @@
       <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="133" t="s">
+      <c r="D7" s="132" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="7">
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>423542.38923799997</v>
-      </c>
-      <c r="G7" s="189">
+        <v>412157.680108</v>
+      </c>
+      <c r="G7" s="194">
         <f>F7</f>
-        <v>423542.38923799997</v>
-      </c>
-      <c r="H7" s="131">
+        <v>412157.680108</v>
+      </c>
+      <c r="H7" s="130">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="106">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" s="88"/>
       <c r="K7" s="88">
-        <v>412157.680108</v>
+        <v>614669.65776899992</v>
       </c>
       <c r="L7" s="98">
         <v>0</v>
       </c>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>412157.680108</v>
+        <v>614669.65776899992</v>
       </c>
       <c r="N7" s="11">
         <f>M7*6% + M7</f>
-        <v>436887.14091447997</v>
+        <v>651549.83723513992</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4324,24 +4404,24 @@
       <c r="C8" s="7">
         <v>24</v>
       </c>
-      <c r="D8" s="133" t="s">
+      <c r="D8" s="132" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="7">
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>151158.84501451589</v>
-      </c>
-      <c r="G8" s="189">
-        <v>144100</v>
-      </c>
-      <c r="H8" s="131">
+        <v>173244.21501451588</v>
+      </c>
+      <c r="G8" s="194">
+        <v>175000</v>
+      </c>
+      <c r="H8" s="130">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>7058.8450145158859</v>
+        <v>-1755.7849854841188</v>
       </c>
       <c r="I8" s="106">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="88">
         <f>M$4*E8%</f>
@@ -4349,19 +4429,19 @@
       </c>
       <c r="K8" s="88">
         <f>M$2*E8 /100</f>
-        <v>166185.37</v>
-      </c>
-      <c r="L8" s="165">
+        <v>182803.90700000001</v>
+      </c>
+      <c r="L8" s="164">
         <f>J$3*E8%+J$4</f>
         <v>0</v>
       </c>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>173244.21501451588</v>
+        <v>181048.12201451589</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>183638.86791538683</v>
+        <v>191911.00933538683</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4372,25 +4452,25 @@
       <c r="C9" s="7">
         <v>25</v>
       </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="132" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="7">
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>177670.97348426332</v>
-      </c>
-      <c r="G9" s="190">
-        <f>214701-G34</f>
-        <v>177670.97519999999</v>
-      </c>
-      <c r="H9" s="131">
+        <v>326579.3682842633</v>
+      </c>
+      <c r="G9" s="195">
+        <f>366606-G34</f>
+        <v>325999.62</v>
+      </c>
+      <c r="H9" s="130">
         <f t="shared" si="0"/>
-        <v>-1.7157366673927754E-3</v>
+        <v>579.7482842633035</v>
       </c>
       <c r="I9" s="106">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
@@ -4398,18 +4478,19 @@
       </c>
       <c r="K9" s="88">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>316579.37</v>
-      </c>
-      <c r="L9" s="165">
-        <v>10000</v>
+        <v>348237.30700000003</v>
+      </c>
+      <c r="L9" s="164">
+        <f t="shared" ref="L9:L50" si="4">J$3*E9%+J$4</f>
+        <v>0</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>326579.3682842633</v>
+        <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
+        <v>348817.05528426333</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>346174.13038131909</v>
+        <v>369746.07860131911</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4420,24 +4501,24 @@
       <c r="C10" s="7">
         <v>26</v>
       </c>
-      <c r="D10" s="133" t="s">
+      <c r="D10" s="132" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="7">
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>229352.20620596872</v>
-      </c>
-      <c r="G10" s="189">
-        <v>185159</v>
-      </c>
-      <c r="H10" s="131">
+        <v>257752.68620596873</v>
+      </c>
+      <c r="G10" s="194">
+        <v>213558</v>
+      </c>
+      <c r="H10" s="130">
         <f t="shared" si="0"/>
-        <v>44193.206205968716</v>
+        <v>44194.686205968726</v>
       </c>
       <c r="I10" s="106">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
@@ -4445,19 +4526,19 @@
       </c>
       <c r="K10" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L10" s="165">
-        <f t="shared" ref="L10:L51" si="5">J$3*E10%+J$4</f>
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L10" s="164">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M10" s="6">
-        <f t="shared" si="4"/>
-        <v>257752.68620596873</v>
+        <f t="shared" si="5"/>
+        <v>279110.11420596868</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>273217.84737832687</v>
+        <v>295856.72105832677</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4468,25 +4549,25 @@
       <c r="C11" s="7">
         <v>27</v>
       </c>
-      <c r="D11" s="133" t="s">
+      <c r="D11" s="132" t="s">
         <v>40</v>
       </c>
       <c r="E11" s="7">
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>235209.2316</v>
-      </c>
-      <c r="G11" s="189">
-        <f>223626</f>
-        <v>223626</v>
-      </c>
-      <c r="H11" s="131">
+        <v>269508.94160000002</v>
+      </c>
+      <c r="G11" s="194">
+        <f>F11</f>
+        <v>269508.94160000002</v>
+      </c>
+      <c r="H11" s="130">
         <f t="shared" si="0"/>
-        <v>11583.231599999999</v>
+        <v>0</v>
       </c>
       <c r="I11" s="106">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
@@ -4494,21 +4575,21 @@
       </c>
       <c r="K11" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L11" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L11" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <f t="shared" si="4"/>
-        <v>269508.94160000002</v>
+        <v>283718.28100000002</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>285679.47809600004</v>
-      </c>
-      <c r="P11" s="109"/>
+        <v>300741.37786000001</v>
+      </c>
+      <c r="P11" s="108"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -4518,25 +4599,25 @@
       <c r="C12" s="7">
         <v>28</v>
       </c>
-      <c r="D12" s="133" t="s">
+      <c r="D12" s="132" t="s">
         <v>111</v>
       </c>
       <c r="E12" s="7">
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>194750.50080000001</v>
-      </c>
-      <c r="G12" s="190">
+        <v>223559.48</v>
+      </c>
+      <c r="G12" s="195">
         <f>F12</f>
-        <v>194750.50080000001</v>
-      </c>
-      <c r="H12" s="131">
+        <v>223559.48</v>
+      </c>
+      <c r="H12" s="130">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="106">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
@@ -4544,18 +4625,19 @@
       </c>
       <c r="K12" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L12" s="165">
-        <v>10000</v>
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L12" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="4"/>
-        <v>223559.48</v>
+        <f t="shared" si="5"/>
+        <v>234915.42799999996</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="1"/>
-        <v>236973.04880000002</v>
+        <v>249010.35367999994</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4566,22 +4648,22 @@
       <c r="C13" s="7">
         <v>29</v>
       </c>
-      <c r="D13" s="133" t="s">
+      <c r="D13" s="132" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="7">
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>235208.87231924172</v>
-      </c>
-      <c r="G13" s="190">
-        <f>235209-G50</f>
-        <v>194750.26919999998</v>
-      </c>
-      <c r="H13" s="131">
+        <v>308384.31311924173</v>
+      </c>
+      <c r="G13" s="195">
+        <f>352750-G50</f>
+        <v>308383.77</v>
+      </c>
+      <c r="H13" s="130">
         <f t="shared" si="0"/>
-        <v>40458.603119241743</v>
+        <v>0.54311924171634018</v>
       </c>
       <c r="I13" s="106">
         <v>3</v>
@@ -4592,18 +4674,19 @@
       </c>
       <c r="K13" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L13" s="165">
-        <v>10000</v>
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L13" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="4"/>
-        <v>308384.31311924173</v>
+        <f t="shared" si="5"/>
+        <v>283718.82411924173</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>326887.37190639623</v>
+        <v>300741.95356639626</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4614,25 +4697,25 @@
       <c r="C14" s="7">
         <v>30</v>
       </c>
-      <c r="D14" s="133" t="s">
+      <c r="D14" s="132" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="7">
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>194750.50080000001</v>
-      </c>
-      <c r="G14" s="189">
-        <f>185159</f>
-        <v>185159</v>
-      </c>
-      <c r="H14" s="131">
+        <v>223150.98080000002</v>
+      </c>
+      <c r="G14" s="194">
+        <f>214000</f>
+        <v>214000</v>
+      </c>
+      <c r="H14" s="130">
         <f t="shared" si="0"/>
-        <v>9591.5008000000089</v>
+        <v>9150.9808000000194</v>
       </c>
       <c r="I14" s="106">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
@@ -4640,19 +4723,19 @@
       </c>
       <c r="K14" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L14" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L14" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
-        <f t="shared" si="4"/>
-        <v>223150.98080000002</v>
+        <v>244066.40879999998</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>236540.03964800003</v>
+        <v>258710.39332799998</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4663,25 +4746,25 @@
       <c r="C15" s="7">
         <v>31</v>
       </c>
-      <c r="D15" s="133" t="s">
-        <v>151</v>
+      <c r="D15" s="132" t="s">
+        <v>143</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>235208.61604653395</v>
-      </c>
-      <c r="G15" s="190">
-        <f>235209+34287-G35</f>
-        <v>235208.94</v>
-      </c>
-      <c r="H15" s="131">
+        <v>257925.38604653394</v>
+      </c>
+      <c r="G15" s="195">
+        <f>295524-G35</f>
+        <v>257925.5</v>
+      </c>
+      <c r="H15" s="130">
         <f t="shared" si="0"/>
-        <v>-0.32395346605335362</v>
+        <v>-0.1139534660615027</v>
       </c>
       <c r="I15" s="106">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
@@ -4689,19 +4772,19 @@
       </c>
       <c r="K15" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L15" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L15" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" si="4"/>
-        <v>257925.38604653394</v>
+        <v>283718.16704653396</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>273400.90920932597</v>
+        <v>300741.25706932601</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4712,25 +4795,25 @@
       <c r="C16" s="7">
         <v>32</v>
       </c>
-      <c r="D16" s="133" t="s">
+      <c r="D16" s="132" t="s">
         <v>136</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>220949.42580066071</v>
-      </c>
-      <c r="G16" s="190">
-        <f>220949+33601-G49</f>
-        <v>220948.68119999999</v>
-      </c>
-      <c r="H16" s="131">
+        <v>213560.22460066073</v>
+      </c>
+      <c r="G16" s="249">
+        <f>250407-G49</f>
+        <v>213560.47</v>
+      </c>
+      <c r="H16" s="130">
         <f t="shared" si="0"/>
-        <v>0.74460066072060727</v>
+        <v>-0.24539933927007951</v>
       </c>
       <c r="I16" s="106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
@@ -4738,18 +4821,22 @@
       </c>
       <c r="K16" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L16" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L16" s="164">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="4"/>
-        <v>213560.22460066073</v>
+        <f t="shared" si="5"/>
+        <v>234915.18260066069</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>226373.83807670037</v>
+        <v>249010.09355670033</v>
+      </c>
+      <c r="P16" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -4760,25 +4847,25 @@
       <c r="C17" s="7">
         <v>33</v>
       </c>
-      <c r="D17" s="133" t="s">
+      <c r="D17" s="132" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="7">
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>250529.74491111474</v>
-      </c>
-      <c r="G17" s="189">
-        <f>318418-G47-G48</f>
-        <v>250529.62119999999</v>
-      </c>
-      <c r="H17" s="131">
+        <v>257925.83371111474</v>
+      </c>
+      <c r="G17" s="194">
+        <f>332372-G47-G48</f>
+        <v>257926.97</v>
+      </c>
+      <c r="H17" s="130">
         <f t="shared" si="0"/>
-        <v>0.1237111147493124</v>
+        <v>-1.1362888852600008</v>
       </c>
       <c r="I17" s="106">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
@@ -4786,19 +4873,18 @@
       </c>
       <c r="K17" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L17" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L17" s="164">
+        <v>10000</v>
+      </c>
+      <c r="M17" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="6">
-        <f t="shared" si="4"/>
-        <v>257925.83371111474</v>
+        <v>293717.14471111476</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>273401.38373378164</v>
+        <v>311340.17339378165</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -4809,25 +4895,25 @@
       <c r="C18" s="7">
         <v>34</v>
       </c>
-      <c r="D18" s="133" t="s">
+      <c r="D18" s="132" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="7">
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>194180.49558325135</v>
-      </c>
-      <c r="G18" s="189">
-        <f>223000-G51</f>
-        <v>183912.75160000002</v>
-      </c>
-      <c r="H18" s="131">
+        <v>223827.22398325134</v>
+      </c>
+      <c r="G18" s="194">
+        <f>270000-G51</f>
+        <v>227137.71</v>
+      </c>
+      <c r="H18" s="130">
         <f t="shared" si="0"/>
-        <v>10267.743983251334</v>
+        <v>-3310.4860167486477</v>
       </c>
       <c r="I18" s="106">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
@@ -4835,19 +4921,19 @@
       </c>
       <c r="K18" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L18" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L18" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6">
-        <f t="shared" si="4"/>
-        <v>223827.22398325134</v>
+        <v>231604.94198325131</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>237256.85742224642</v>
+        <v>245501.23850224639</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -4858,22 +4944,22 @@
       <c r="C19" s="7">
         <v>35</v>
       </c>
-      <c r="D19" s="133" t="s">
+      <c r="D19" s="132" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="7">
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>235209.45796516797</v>
-      </c>
-      <c r="G19" s="190">
-        <f>272239-G41</f>
-        <v>235208.97519999999</v>
-      </c>
-      <c r="H19" s="131">
+        <v>257926.19276516797</v>
+      </c>
+      <c r="G19" s="195">
+        <f>298532-G41</f>
+        <v>257925.62</v>
+      </c>
+      <c r="H19" s="130">
         <f t="shared" si="0"/>
-        <v>0.48276516798068769</v>
+        <v>0.57276516797719523</v>
       </c>
       <c r="I19" s="106">
         <v>3</v>
@@ -4884,19 +4970,19 @@
       </c>
       <c r="K19" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L19" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L19" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" si="4"/>
-        <v>257926.19276516797</v>
+        <v>283718.85376516799</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>273401.76433107804</v>
+        <v>300741.98499107809</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -4907,22 +4993,22 @@
       <c r="C20" s="7">
         <v>36</v>
       </c>
-      <c r="D20" s="133" t="s">
+      <c r="D20" s="132" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="7">
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>194750.27110707472</v>
-      </c>
-      <c r="G20" s="189">
-        <f>217106-G38</f>
-        <v>183504.68119999999</v>
-      </c>
-      <c r="H20" s="131">
+        <v>224805.06990707474</v>
+      </c>
+      <c r="G20" s="194">
+        <f>250406-G38</f>
+        <v>213559.47</v>
+      </c>
+      <c r="H20" s="130">
         <f t="shared" si="0"/>
-        <v>11245.589907074725</v>
+        <v>11245.599907074735</v>
       </c>
       <c r="I20" s="106">
         <v>3</v>
@@ -4933,19 +5019,19 @@
       </c>
       <c r="K20" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L20" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L20" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" si="4"/>
-        <v>224805.06990707474</v>
+        <v>246161.02790707469</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>238293.37410149921</v>
+        <v>260930.68958149917</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -4956,22 +5042,22 @@
       <c r="C21" s="7">
         <v>37</v>
       </c>
-      <c r="D21" s="133" t="s">
+      <c r="D21" s="132" t="s">
         <v>53</v>
       </c>
       <c r="E21" s="7">
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>235209.86029179581</v>
-      </c>
-      <c r="G21" s="189">
-        <f>272240-G45</f>
-        <v>235209.97519999999</v>
-      </c>
-      <c r="H21" s="131">
+        <v>257925.59509179581</v>
+      </c>
+      <c r="G21" s="194">
+        <f>298532-G45</f>
+        <v>257925.62</v>
+      </c>
+      <c r="H21" s="130">
         <f t="shared" si="0"/>
-        <v>-0.1149082041811198</v>
+        <v>-2.4908204184612259E-2</v>
       </c>
       <c r="I21" s="106">
         <v>4</v>
@@ -4982,19 +5068,19 @@
       </c>
       <c r="K21" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L21" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L21" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
-        <f t="shared" si="4"/>
-        <v>257925.59509179581</v>
+        <v>283718.25609179586</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>273401.13079730357</v>
+        <v>300741.35145730362</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -5005,24 +5091,25 @@
       <c r="C22" s="7">
         <v>38</v>
       </c>
-      <c r="D22" s="167" t="s">
+      <c r="D22" s="166" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="7">
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>194750.50080000001</v>
-      </c>
-      <c r="G22" s="189">
-        <v>185159</v>
-      </c>
-      <c r="H22" s="131">
+        <v>223150.98080000002</v>
+      </c>
+      <c r="G22" s="194">
+        <f>F22</f>
+        <v>223150.98080000002</v>
+      </c>
+      <c r="H22" s="130">
         <f t="shared" si="0"/>
-        <v>9591.5008000000089</v>
+        <v>0</v>
       </c>
       <c r="I22" s="106">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
@@ -5030,19 +5117,18 @@
       </c>
       <c r="K22" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L22" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L22" s="164">
+        <v>20000</v>
+      </c>
+      <c r="M22" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <f t="shared" si="4"/>
-        <v>223150.98080000002</v>
+        <v>254915.42799999996</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>236540.03964800003</v>
+        <v>270210.35367999994</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -5053,25 +5139,25 @@
       <c r="C23" s="7">
         <v>39</v>
       </c>
-      <c r="D23" s="133" t="s">
+      <c r="D23" s="132" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="7">
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>57370.666484095156</v>
-      </c>
-      <c r="G23" s="190">
-        <f>118871-G46</f>
-        <v>84583.94</v>
-      </c>
-      <c r="H23" s="131">
+        <v>240712.43648409515</v>
+      </c>
+      <c r="G23" s="195">
+        <f>280000-G46</f>
+        <v>242401.5</v>
+      </c>
+      <c r="H23" s="130">
         <f t="shared" si="0"/>
-        <v>-27213.273515904846</v>
+        <v>-1689.0635159048543</v>
       </c>
       <c r="I23" s="106">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
@@ -5079,18 +5165,18 @@
       </c>
       <c r="K23" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L23" s="165">
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L23" s="164">
         <v>10000</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="4"/>
-        <v>240712.43648409515</v>
+        <f t="shared" si="5"/>
+        <v>292029.21748409513</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>255155.18267314087</v>
+        <v>309550.97053314082</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -5101,25 +5187,25 @@
       <c r="C24" s="7">
         <v>40</v>
       </c>
-      <c r="D24" s="133" t="s">
+      <c r="D24" s="132" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="7">
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>191483.98867107474</v>
-      </c>
-      <c r="G24" s="189">
-        <f>232000-G37</f>
-        <v>198398.68119999999</v>
-      </c>
-      <c r="H24" s="131">
+        <v>206644.78747107476</v>
+      </c>
+      <c r="G24" s="194">
+        <f>245000-G37</f>
+        <v>208153.47</v>
+      </c>
+      <c r="H24" s="130">
         <f t="shared" si="0"/>
-        <v>-6914.692528925254</v>
-      </c>
-      <c r="I24" s="179">
-        <v>5</v>
+        <v>-1508.6825289252447</v>
+      </c>
+      <c r="I24" s="178">
+        <v>7</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
@@ -5127,19 +5213,19 @@
       </c>
       <c r="K24" s="88">
         <f t="shared" si="3"/>
-        <v>213559.48</v>
-      </c>
-      <c r="L24" s="165">
+        <v>234915.42799999996</v>
+      </c>
+      <c r="L24" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
-        <f t="shared" si="4"/>
-        <v>206644.78747107476</v>
+        <v>233406.74547107471</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>219043.47471933925</v>
+        <v>247411.1501993392</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -5150,25 +5236,25 @@
       <c r="C25" s="7">
         <v>41</v>
       </c>
-      <c r="D25" s="133" t="s">
+      <c r="D25" s="132" t="s">
         <v>58</v>
       </c>
       <c r="E25" s="7">
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>235209.2316</v>
-      </c>
-      <c r="G25" s="189">
+        <v>267925.70999999996</v>
+      </c>
+      <c r="G25" s="194">
         <f>F25</f>
-        <v>235209.2316</v>
-      </c>
-      <c r="H25" s="131">
+        <v>267925.70999999996</v>
+      </c>
+      <c r="H25" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="106">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
@@ -5176,18 +5262,19 @@
       </c>
       <c r="K25" s="88">
         <f t="shared" si="3"/>
-        <v>257925.71</v>
-      </c>
-      <c r="L25" s="165">
-        <v>10000</v>
+        <v>283718.28100000002</v>
+      </c>
+      <c r="L25" s="164">
+        <f>10000+K25*0.1</f>
+        <v>38371.828099999999</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" si="4"/>
-        <v>267925.70999999996</v>
+        <f t="shared" si="5"/>
+        <v>322090.1091</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>284001.25259999995</v>
+        <v>341415.51564599999</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -5198,22 +5285,22 @@
       <c r="C26" s="7">
         <v>42</v>
       </c>
-      <c r="D26" s="133" t="s">
+      <c r="D26" s="132" t="s">
         <v>60</v>
       </c>
       <c r="E26" s="7">
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>-556256.30998396303</v>
-      </c>
-      <c r="G26" s="190">
-        <f>-G30-G31-G36</f>
-        <v>-109032.8508</v>
-      </c>
-      <c r="H26" s="132">
+        <v>3958.5408160369843</v>
+      </c>
+      <c r="G26" s="195">
+        <f>119563+3959-G30-G31-G36</f>
+        <v>3958.7699999999895</v>
+      </c>
+      <c r="H26" s="131">
         <f t="shared" si="0"/>
-        <v>-447223.45918396302</v>
+        <v>-0.22918396300519817</v>
       </c>
       <c r="I26" s="106">
         <v>5</v>
@@ -5224,19 +5311,19 @@
       </c>
       <c r="K26" s="88">
         <f t="shared" si="3"/>
-        <v>451182</v>
-      </c>
-      <c r="L26" s="165">
+        <v>496300.2</v>
+      </c>
+      <c r="L26" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="4"/>
-        <v>3958.5408160369843</v>
+        <v>496299.97081603704</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>4196.0532649992037</v>
+        <v>526077.96906499926</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -5247,25 +5334,25 @@
       <c r="C27" s="7">
         <v>43</v>
       </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="132" t="s">
         <v>62</v>
       </c>
       <c r="E27" s="7">
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>403845.12633526558</v>
-      </c>
-      <c r="G27" s="189">
-        <f>483391-G39-G40</f>
-        <v>403845.0208</v>
-      </c>
-      <c r="H27" s="131">
+        <v>442910.4355352656</v>
+      </c>
+      <c r="G27" s="194">
+        <f>526378-G39-G40</f>
+        <v>439149.48000000004</v>
+      </c>
+      <c r="H27" s="130">
         <f t="shared" si="0"/>
-        <v>0.10553526558214799</v>
+        <v>3760.9555352655589</v>
       </c>
       <c r="I27" s="106">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
@@ -5273,19 +5360,19 @@
       </c>
       <c r="K27" s="88">
         <f t="shared" si="3"/>
-        <v>442910.33</v>
-      </c>
-      <c r="L27" s="165">
+        <v>487201.36299999995</v>
+      </c>
+      <c r="L27" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="6">
-        <f t="shared" si="4"/>
-        <v>442910.4355352656</v>
+        <v>490962.31853526551</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>469485.06166738155</v>
+        <v>520420.05764738144</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -5296,25 +5383,25 @@
       <c r="C28" s="7">
         <v>44</v>
       </c>
-      <c r="D28" s="133" t="s">
+      <c r="D28" s="132" t="s">
         <v>64</v>
       </c>
       <c r="E28" s="7">
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>304604.19637654093</v>
-      </c>
-      <c r="G28" s="189">
-        <f>353860-G32-G33</f>
-        <v>281171.43280000001</v>
-      </c>
-      <c r="H28" s="131">
+        <v>466343.09357654094</v>
+      </c>
+      <c r="G28" s="194">
+        <f>523000-G32-G33</f>
+        <v>443291.18</v>
+      </c>
+      <c r="H28" s="130">
         <f t="shared" si="0"/>
-        <v>23432.763576540921</v>
+        <v>23051.913576540945</v>
       </c>
       <c r="I28" s="106">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
@@ -5322,19 +5409,19 @@
       </c>
       <c r="K28" s="88">
         <f t="shared" si="3"/>
-        <v>442910.33</v>
-      </c>
-      <c r="L28" s="165">
+        <v>487201.36299999995</v>
+      </c>
+      <c r="L28" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6">
-        <f t="shared" si="4"/>
-        <v>466343.09357654094</v>
+        <v>510253.2765765409</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>494323.67919113341</v>
+        <v>540868.47317113332</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -5345,25 +5432,25 @@
       <c r="C29" s="7">
         <v>45</v>
       </c>
-      <c r="D29" s="133" t="s">
+      <c r="D29" s="132" t="s">
         <v>66</v>
       </c>
       <c r="E29" s="7">
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>316080.21825669997</v>
-      </c>
-      <c r="G29" s="190" t="e">
-        <f>-G42-G43-G44+RESUMEN!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H29" s="132" t="e">
+        <v>771000.92145669996</v>
+      </c>
+      <c r="G29" s="195">
+        <f>564000-G42-G43-G44</f>
+        <v>442932.83</v>
+      </c>
+      <c r="H29" s="131">
         <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>328068.09145669994</v>
       </c>
       <c r="I29" s="106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
@@ -5371,43 +5458,43 @@
       </c>
       <c r="K29" s="88">
         <f t="shared" si="3"/>
-        <v>442910.33</v>
-      </c>
-      <c r="L29" s="165">
+        <v>487201.36299999995</v>
+      </c>
+      <c r="L29" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6" t="e">
-        <f t="shared" si="4"/>
-        <v>#REF!</v>
-      </c>
-      <c r="N29" s="11" t="e">
+        <v>815269.4544566999</v>
+      </c>
+      <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>864185.62172410195</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="126" t="s">
+      <c r="A30" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7">
         <v>1</v>
       </c>
-      <c r="D30" s="133" t="s">
+      <c r="D30" s="132" t="s">
         <v>60</v>
       </c>
       <c r="E30" s="7">
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>37030.024799999999</v>
-      </c>
-      <c r="G30" s="189">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="G30" s="194">
         <f t="shared" ref="G30:G34" si="6">F30</f>
-        <v>37030.024799999999</v>
-      </c>
-      <c r="H30" s="131">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="H30" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5418,43 +5505,43 @@
       </c>
       <c r="K30" s="88">
         <f t="shared" si="3"/>
-        <v>40606.380000000005</v>
-      </c>
-      <c r="L30" s="165">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="L30" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="6">
-        <f t="shared" si="4"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="1"/>
-        <v>43042.762800000004</v>
+        <v>47347.03908000001</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="126" t="s">
+      <c r="A31" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7">
         <v>2</v>
       </c>
-      <c r="D31" s="133" t="s">
+      <c r="D31" s="132" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="7">
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>37715.766000000003</v>
-      </c>
-      <c r="G31" s="189">
+        <v>41358.350000000006</v>
+      </c>
+      <c r="G31" s="194">
         <f t="shared" si="6"/>
-        <v>37715.766000000003</v>
-      </c>
-      <c r="H31" s="131">
+        <v>41358.350000000006</v>
+      </c>
+      <c r="H31" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5465,43 +5552,43 @@
       </c>
       <c r="K31" s="88">
         <f t="shared" si="3"/>
-        <v>41358.350000000006</v>
-      </c>
-      <c r="L31" s="165">
+        <v>45494.184999999998</v>
+      </c>
+      <c r="L31" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="6">
-        <f t="shared" si="4"/>
-        <v>41358.350000000006</v>
+        <v>45494.184999999998</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="1"/>
-        <v>43839.85100000001</v>
+        <v>48223.8361</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="126" t="s">
+      <c r="A32" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7">
         <v>3</v>
       </c>
-      <c r="D32" s="133" t="s">
+      <c r="D32" s="132" t="s">
         <v>64</v>
       </c>
       <c r="E32" s="7">
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>30858.354000000003</v>
-      </c>
-      <c r="G32" s="189">
+        <v>33838.65</v>
+      </c>
+      <c r="G32" s="194">
         <f>F32</f>
-        <v>30858.354000000003</v>
-      </c>
-      <c r="H32" s="131">
+        <v>33838.65</v>
+      </c>
+      <c r="H32" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5512,43 +5599,43 @@
       </c>
       <c r="K32" s="88">
         <f t="shared" si="3"/>
-        <v>33838.65</v>
-      </c>
-      <c r="L32" s="165">
+        <v>37222.514999999999</v>
+      </c>
+      <c r="L32" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="6">
-        <f t="shared" si="4"/>
-        <v>33838.65</v>
+        <v>37222.514999999999</v>
       </c>
       <c r="N32" s="11">
         <f t="shared" si="1"/>
-        <v>35868.969000000005</v>
+        <v>39455.865899999997</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="126" t="s">
+      <c r="A33" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7">
         <v>4</v>
       </c>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="132" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="7">
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>41830.213199999998</v>
-      </c>
-      <c r="G33" s="189">
+        <v>45870.17</v>
+      </c>
+      <c r="G33" s="194">
         <f t="shared" si="6"/>
-        <v>41830.213199999998</v>
-      </c>
-      <c r="H33" s="131">
+        <v>45870.17</v>
+      </c>
+      <c r="H33" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5559,43 +5646,43 @@
       </c>
       <c r="K33" s="88">
         <f t="shared" si="3"/>
-        <v>45870.17</v>
-      </c>
-      <c r="L33" s="165">
+        <v>50457.187000000005</v>
+      </c>
+      <c r="L33" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="6">
-        <f t="shared" si="4"/>
-        <v>45870.17</v>
+        <v>50457.187000000005</v>
       </c>
       <c r="N33" s="11">
         <f t="shared" si="1"/>
-        <v>48622.3802</v>
+        <v>53484.618220000004</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34" s="133" t="s">
+      <c r="D34" s="132" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="7">
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>37030.024799999999</v>
-      </c>
-      <c r="G34" s="189">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="G34" s="194">
         <f t="shared" si="6"/>
-        <v>37030.024799999999</v>
-      </c>
-      <c r="H34" s="131">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="H34" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5606,43 +5693,43 @@
       </c>
       <c r="K34" s="88">
         <f t="shared" si="3"/>
-        <v>40606.380000000005</v>
-      </c>
-      <c r="L34" s="165">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="L34" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="6">
-        <f t="shared" si="4"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="N34" s="11">
         <f t="shared" si="1"/>
-        <v>43042.762800000004</v>
+        <v>47347.03908000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="126" t="s">
+      <c r="A35" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7">
         <v>6</v>
       </c>
-      <c r="D35" s="133" t="s">
-        <v>151</v>
+      <c r="D35" s="132" t="s">
+        <v>143</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>34287.06</v>
-      </c>
-      <c r="G35" s="190">
+        <v>37598.5</v>
+      </c>
+      <c r="G35" s="195">
         <f>F35</f>
-        <v>34287.06</v>
-      </c>
-      <c r="H35" s="131">
+        <v>37598.5</v>
+      </c>
+      <c r="H35" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5653,43 +5740,43 @@
       </c>
       <c r="K35" s="88">
         <f t="shared" si="3"/>
-        <v>37598.5</v>
-      </c>
-      <c r="L35" s="165">
+        <v>41358.35</v>
+      </c>
+      <c r="L35" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="6">
-        <f t="shared" si="4"/>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="N35" s="11">
         <f t="shared" si="1"/>
-        <v>39854.410000000003</v>
+        <v>43839.850999999995</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="126" t="s">
+      <c r="A36" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7">
         <v>7</v>
       </c>
-      <c r="D36" s="133" t="s">
+      <c r="D36" s="132" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="7">
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>34287.06</v>
-      </c>
-      <c r="G36" s="189">
+        <v>37598.5</v>
+      </c>
+      <c r="G36" s="194">
         <f t="shared" ref="G36:G41" si="7">F36</f>
-        <v>34287.06</v>
-      </c>
-      <c r="H36" s="131">
+        <v>37598.5</v>
+      </c>
+      <c r="H36" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5700,43 +5787,43 @@
       </c>
       <c r="K36" s="88">
         <f t="shared" si="3"/>
-        <v>37598.5</v>
-      </c>
-      <c r="L36" s="165">
+        <v>41358.35</v>
+      </c>
+      <c r="L36" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="6">
-        <f t="shared" si="4"/>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="N36" s="11">
         <f t="shared" si="1"/>
-        <v>39854.410000000003</v>
+        <v>43839.850999999995</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="126" t="s">
+      <c r="A37" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7">
         <v>8</v>
       </c>
-      <c r="D37" s="133" t="s">
+      <c r="D37" s="132" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="7">
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>33601.318800000001</v>
-      </c>
-      <c r="G37" s="189">
+        <v>36846.53</v>
+      </c>
+      <c r="G37" s="194">
         <f t="shared" si="7"/>
-        <v>33601.318800000001</v>
-      </c>
-      <c r="H37" s="131">
+        <v>36846.53</v>
+      </c>
+      <c r="H37" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5747,43 +5834,43 @@
       </c>
       <c r="K37" s="88">
         <f t="shared" si="3"/>
-        <v>36846.53</v>
-      </c>
-      <c r="L37" s="165">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="L37" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="6">
-        <f t="shared" si="4"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="1"/>
-        <v>39057.321799999998</v>
+        <v>42963.053979999997</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="126" t="s">
+      <c r="A38" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7">
         <v>9</v>
       </c>
-      <c r="D38" s="133" t="s">
+      <c r="D38" s="132" t="s">
         <v>52</v>
       </c>
       <c r="E38" s="7">
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>33601.318800000001</v>
-      </c>
-      <c r="G38" s="189">
+        <v>36846.53</v>
+      </c>
+      <c r="G38" s="194">
         <f t="shared" si="7"/>
-        <v>33601.318800000001</v>
-      </c>
-      <c r="H38" s="131">
+        <v>36846.53</v>
+      </c>
+      <c r="H38" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5794,43 +5881,43 @@
       </c>
       <c r="K38" s="88">
         <f t="shared" si="3"/>
-        <v>36846.53</v>
-      </c>
-      <c r="L38" s="165">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="L38" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="6">
-        <f t="shared" si="4"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="N38" s="11">
         <f t="shared" si="1"/>
-        <v>39057.321799999998</v>
+        <v>42963.053979999997</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="126" t="s">
+      <c r="A39" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7">
         <v>10</v>
       </c>
-      <c r="D39" s="133" t="s">
+      <c r="D39" s="132" t="s">
         <v>62</v>
       </c>
       <c r="E39" s="7">
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>40458.730800000005</v>
-      </c>
-      <c r="G39" s="189">
+        <v>44366.23</v>
+      </c>
+      <c r="G39" s="194">
         <f t="shared" si="7"/>
-        <v>40458.730800000005</v>
-      </c>
-      <c r="H39" s="131">
+        <v>44366.23</v>
+      </c>
+      <c r="H39" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5841,43 +5928,43 @@
       </c>
       <c r="K39" s="88">
         <f t="shared" si="3"/>
-        <v>44366.23</v>
-      </c>
-      <c r="L39" s="165">
+        <v>48802.852999999996</v>
+      </c>
+      <c r="L39" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="6">
-        <f t="shared" si="4"/>
-        <v>44366.23</v>
+        <v>48802.852999999996</v>
       </c>
       <c r="N39" s="11">
         <f t="shared" si="1"/>
-        <v>47028.203800000003</v>
+        <v>51731.024179999993</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="126" t="s">
+      <c r="A40" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7">
         <v>11</v>
       </c>
-      <c r="D40" s="133" t="s">
+      <c r="D40" s="132" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="7">
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>39087.248399999997</v>
-      </c>
-      <c r="G40" s="189">
+        <v>42862.29</v>
+      </c>
+      <c r="G40" s="194">
         <f t="shared" si="7"/>
-        <v>39087.248399999997</v>
-      </c>
-      <c r="H40" s="131">
+        <v>42862.29</v>
+      </c>
+      <c r="H40" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5888,43 +5975,43 @@
       </c>
       <c r="K40" s="88">
         <f t="shared" si="3"/>
-        <v>42862.29</v>
-      </c>
-      <c r="L40" s="165">
+        <v>47148.518999999993</v>
+      </c>
+      <c r="L40" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="6">
-        <f t="shared" si="4"/>
-        <v>42862.29</v>
+        <v>47148.518999999993</v>
       </c>
       <c r="N40" s="11">
         <f t="shared" si="1"/>
-        <v>45434.027399999999</v>
+        <v>49977.430139999989</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="126" t="s">
+      <c r="A41" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7">
         <v>12</v>
       </c>
-      <c r="D41" s="133" t="s">
+      <c r="D41" s="132" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="7">
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>37030.024799999999</v>
-      </c>
-      <c r="G41" s="189">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="G41" s="194">
         <f t="shared" si="7"/>
-        <v>37030.024799999999</v>
-      </c>
-      <c r="H41" s="131">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="H41" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5935,43 +6022,43 @@
       </c>
       <c r="K41" s="88">
         <f t="shared" si="3"/>
-        <v>40606.380000000005</v>
-      </c>
-      <c r="L41" s="165">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="L41" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="6">
-        <f t="shared" si="4"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="N41" s="11">
         <f t="shared" si="1"/>
-        <v>43042.762800000004</v>
+        <v>47347.03908000001</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="126" t="s">
+      <c r="A42" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7">
         <v>13</v>
       </c>
-      <c r="D42" s="133" t="s">
+      <c r="D42" s="132" t="s">
         <v>66</v>
       </c>
       <c r="E42" s="7">
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>37715.766000000003</v>
-      </c>
-      <c r="G42" s="189">
+        <v>41358.350000000006</v>
+      </c>
+      <c r="G42" s="194">
         <f>F42</f>
-        <v>37715.766000000003</v>
-      </c>
-      <c r="H42" s="131">
+        <v>41358.350000000006</v>
+      </c>
+      <c r="H42" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5982,43 +6069,43 @@
       </c>
       <c r="K42" s="88">
         <f t="shared" si="3"/>
-        <v>41358.350000000006</v>
-      </c>
-      <c r="L42" s="165">
+        <v>45494.184999999998</v>
+      </c>
+      <c r="L42" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="6">
-        <f t="shared" si="4"/>
-        <v>41358.350000000006</v>
+        <v>45494.184999999998</v>
       </c>
       <c r="N42" s="11">
         <f t="shared" si="1"/>
-        <v>43839.85100000001</v>
+        <v>48223.8361</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="126" t="s">
+      <c r="A43" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7">
         <v>14</v>
       </c>
-      <c r="D43" s="133" t="s">
+      <c r="D43" s="132" t="s">
         <v>66</v>
       </c>
       <c r="E43" s="7">
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>30858.354000000003</v>
-      </c>
-      <c r="G43" s="189">
+        <v>33838.65</v>
+      </c>
+      <c r="G43" s="194">
         <f t="shared" ref="G43:G44" si="8">F43</f>
-        <v>30858.354000000003</v>
-      </c>
-      <c r="H43" s="131">
+        <v>33838.65</v>
+      </c>
+      <c r="H43" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6029,47 +6116,47 @@
       </c>
       <c r="K43" s="88">
         <f t="shared" si="3"/>
-        <v>33838.65</v>
-      </c>
-      <c r="L43" s="165">
+        <v>37222.514999999999</v>
+      </c>
+      <c r="L43" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="6">
-        <f t="shared" si="4"/>
-        <v>33838.65</v>
+        <v>37222.514999999999</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="1"/>
-        <v>35868.969000000005</v>
-      </c>
-      <c r="P43" s="109">
+        <v>39455.865899999997</v>
+      </c>
+      <c r="P43" s="108">
         <f>L1-K52</f>
-        <v>984410.16989199817</v>
+        <v>1677432.855231001</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="126" t="s">
+      <c r="A44" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7">
         <v>15</v>
       </c>
-      <c r="D44" s="133" t="s">
+      <c r="D44" s="132" t="s">
         <v>66</v>
       </c>
       <c r="E44" s="7">
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>41830.213199999998</v>
-      </c>
-      <c r="G44" s="189">
+        <v>45870.17</v>
+      </c>
+      <c r="G44" s="194">
         <f t="shared" si="8"/>
-        <v>41830.213199999998</v>
-      </c>
-      <c r="H44" s="131">
+        <v>45870.17</v>
+      </c>
+      <c r="H44" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6080,43 +6167,43 @@
       </c>
       <c r="K44" s="88">
         <f t="shared" si="3"/>
-        <v>45870.17</v>
-      </c>
-      <c r="L44" s="165">
+        <v>50457.187000000005</v>
+      </c>
+      <c r="L44" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="6">
-        <f t="shared" si="4"/>
-        <v>45870.17</v>
+        <v>50457.187000000005</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="1"/>
-        <v>48622.3802</v>
+        <v>53484.618220000004</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="126" t="s">
+      <c r="A45" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7">
         <v>16</v>
       </c>
-      <c r="D45" s="133" t="s">
+      <c r="D45" s="132" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="7">
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>37030.024799999999</v>
-      </c>
-      <c r="G45" s="189">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="G45" s="194">
         <f t="shared" ref="G45:G51" si="9">F45</f>
-        <v>37030.024799999999</v>
-      </c>
-      <c r="H45" s="131">
+        <v>40606.380000000005</v>
+      </c>
+      <c r="H45" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6127,43 +6214,43 @@
       </c>
       <c r="K45" s="88">
         <f t="shared" si="3"/>
-        <v>40606.380000000005</v>
-      </c>
-      <c r="L45" s="165">
+        <v>44667.018000000011</v>
+      </c>
+      <c r="L45" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="6">
-        <f t="shared" si="4"/>
-        <v>40606.380000000005</v>
+        <v>44667.018000000011</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="1"/>
-        <v>43042.762800000004</v>
+        <v>47347.03908000001</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="126" t="s">
+      <c r="A46" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7">
         <v>17</v>
       </c>
-      <c r="D46" s="133" t="s">
+      <c r="D46" s="132" t="s">
         <v>55</v>
       </c>
       <c r="E46" s="7">
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>34287.06</v>
-      </c>
-      <c r="G46" s="189">
+        <v>37598.5</v>
+      </c>
+      <c r="G46" s="194">
         <f>F46</f>
-        <v>34287.06</v>
-      </c>
-      <c r="H46" s="131">
+        <v>37598.5</v>
+      </c>
+      <c r="H46" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6174,46 +6261,46 @@
       </c>
       <c r="K46" s="88">
         <f t="shared" si="3"/>
-        <v>37598.5</v>
-      </c>
-      <c r="L46" s="165">
+        <v>41358.35</v>
+      </c>
+      <c r="L46" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="6">
-        <f t="shared" si="4"/>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" si="1"/>
-        <v>39854.410000000003</v>
+        <v>43839.850999999995</v>
       </c>
       <c r="Q46" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="126" t="s">
+      <c r="A47" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7">
         <v>18</v>
       </c>
-      <c r="D47" s="133" t="s">
+      <c r="D47" s="132" t="s">
         <v>47</v>
       </c>
       <c r="E47" s="7">
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>34287.06</v>
-      </c>
-      <c r="G47" s="189">
+        <v>37598.5</v>
+      </c>
+      <c r="G47" s="194">
         <f t="shared" si="9"/>
-        <v>34287.06</v>
-      </c>
-      <c r="H47" s="131">
+        <v>37598.5</v>
+      </c>
+      <c r="H47" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6224,48 +6311,48 @@
       </c>
       <c r="K47" s="88">
         <f t="shared" si="3"/>
-        <v>37598.5</v>
-      </c>
-      <c r="L47" s="165">
+        <v>41358.35</v>
+      </c>
+      <c r="L47" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="6">
-        <f t="shared" si="4"/>
-        <v>37598.5</v>
+        <v>41358.35</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="1"/>
-        <v>39854.410000000003</v>
-      </c>
-      <c r="O47" s="138"/>
-      <c r="Q47" s="135">
+        <v>43839.850999999995</v>
+      </c>
+      <c r="O47" s="137"/>
+      <c r="Q47" s="134">
         <f>M3-J52</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="126" t="s">
+      <c r="A48" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7">
         <v>19</v>
       </c>
-      <c r="D48" s="133" t="s">
+      <c r="D48" s="132" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="7">
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>33601.318800000001</v>
-      </c>
-      <c r="G48" s="189">
+        <v>36846.53</v>
+      </c>
+      <c r="G48" s="194">
         <f t="shared" si="9"/>
-        <v>33601.318800000001</v>
-      </c>
-      <c r="H48" s="131">
+        <v>36846.53</v>
+      </c>
+      <c r="H48" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6276,30 +6363,30 @@
       </c>
       <c r="K48" s="88">
         <f t="shared" si="3"/>
-        <v>36846.53</v>
-      </c>
-      <c r="L48" s="165">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="L48" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="6">
-        <f t="shared" si="4"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="N48" s="11">
         <f t="shared" si="1"/>
-        <v>39057.321799999998</v>
+        <v>42963.053979999997</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="126" t="s">
+      <c r="A49" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7">
         <v>20</v>
       </c>
-      <c r="D49" s="133" t="str">
+      <c r="D49" s="132" t="str">
         <f>D16</f>
         <v>FEUILLANT, GASTON</v>
       </c>
@@ -6307,13 +6394,13 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>33601.318800000001</v>
-      </c>
-      <c r="G49" s="189">
+        <v>36846.53</v>
+      </c>
+      <c r="G49" s="194">
         <f>F49</f>
-        <v>33601.318800000001</v>
-      </c>
-      <c r="H49" s="131">
+        <v>36846.53</v>
+      </c>
+      <c r="H49" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6324,43 +6411,43 @@
       </c>
       <c r="K49" s="88">
         <f t="shared" si="3"/>
-        <v>36846.53</v>
-      </c>
-      <c r="L49" s="165">
+        <v>40531.182999999997</v>
+      </c>
+      <c r="L49" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="6">
-        <f t="shared" si="4"/>
-        <v>36846.53</v>
+        <v>40531.182999999997</v>
       </c>
       <c r="N49" s="11">
         <f t="shared" si="1"/>
-        <v>39057.321799999998</v>
+        <v>42963.053979999997</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="126" t="s">
+      <c r="A50" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7">
         <v>21</v>
       </c>
-      <c r="D50" s="133" t="s">
+      <c r="D50" s="132" t="s">
         <v>42</v>
       </c>
       <c r="E50" s="7">
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>40458.730800000005</v>
-      </c>
-      <c r="G50" s="190">
+        <v>44366.23</v>
+      </c>
+      <c r="G50" s="195">
         <f>F50</f>
-        <v>40458.730800000005</v>
-      </c>
-      <c r="H50" s="131">
+        <v>44366.23</v>
+      </c>
+      <c r="H50" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6371,43 +6458,43 @@
       </c>
       <c r="K50" s="88">
         <f t="shared" si="3"/>
-        <v>44366.23</v>
-      </c>
-      <c r="L50" s="165">
+        <v>48802.852999999996</v>
+      </c>
+      <c r="L50" s="164">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="6">
-        <f t="shared" si="4"/>
-        <v>44366.23</v>
+        <v>48802.852999999996</v>
       </c>
       <c r="N50" s="11">
         <f t="shared" si="1"/>
-        <v>47028.203800000003</v>
+        <v>51731.024179999993</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="126" t="s">
+      <c r="A51" s="125" t="s">
         <v>96</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7">
         <v>22</v>
       </c>
-      <c r="D51" s="133" t="s">
+      <c r="D51" s="132" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="7">
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>39087.248399999997</v>
-      </c>
-      <c r="G51" s="189">
+        <v>42862.29</v>
+      </c>
+      <c r="G51" s="194">
         <f t="shared" si="9"/>
-        <v>39087.248399999997</v>
-      </c>
-      <c r="H51" s="131">
+        <v>42862.29</v>
+      </c>
+      <c r="H51" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6418,19 +6505,19 @@
       </c>
       <c r="K51" s="88">
         <f t="shared" si="3"/>
-        <v>42862.29</v>
-      </c>
-      <c r="L51" s="165">
+        <v>47148.518999999993</v>
+      </c>
+      <c r="L51" s="164">
+        <f t="shared" ref="L51" si="10">J$3*E51%+J$4</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="6">
-        <f t="shared" si="4"/>
-        <v>42862.29</v>
+        <v>47148.518999999993</v>
       </c>
       <c r="N51" s="11">
         <f t="shared" si="1"/>
-        <v>45434.027399999999</v>
+        <v>49977.430139999989</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6444,191 +6531,186 @@
       </c>
       <c r="F52" s="90">
         <f>SUM(F7:F51)</f>
-        <v>5354343.2489072988</v>
-      </c>
-      <c r="G52" s="90" t="e">
+        <v>7387677.1173773035</v>
+      </c>
+      <c r="G52" s="90">
         <f>SUM(G7:G51)</f>
-        <v>#REF!</v>
+        <v>6975889.7925080024</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
-      <c r="J52" s="127">
+      <c r="J52" s="126">
         <f>SUM(J8:J51)</f>
         <v>0</v>
       </c>
       <c r="K52" s="90">
         <f>SUM(K7:K51)</f>
-        <v>7323513.9501080019</v>
-      </c>
-      <c r="L52" s="174">
+        <v>8217161.5547689991</v>
+      </c>
+      <c r="L52" s="173">
         <f>SUM(L7:L51)</f>
-        <v>50000</v>
-      </c>
-      <c r="M52" s="91" t="e">
+        <v>78371.828099999999</v>
+      </c>
+      <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N52" s="90" t="e">
+        <v>8707320.7077383008</v>
+      </c>
+      <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P52" s="135"/>
+        <v>9229759.950202601</v>
+      </c>
+      <c r="P52" s="134"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="K53" s="138">
+      <c r="K53" s="137">
         <f>K52-L1</f>
-        <v>-984410.16989199817</v>
+        <v>-1677432.855231001</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="224"/>
-      <c r="D54" s="224"/>
-      <c r="E54" s="224"/>
-      <c r="F54" s="224"/>
-      <c r="G54" s="224"/>
-      <c r="H54" s="224"/>
-      <c r="I54" s="224"/>
-      <c r="J54" s="224"/>
-      <c r="K54" s="224"/>
-      <c r="L54" s="224"/>
-      <c r="M54" s="224"/>
-      <c r="N54" s="224"/>
+      <c r="C54" s="230"/>
+      <c r="D54" s="230"/>
+      <c r="E54" s="230"/>
+      <c r="F54" s="230"/>
+      <c r="G54" s="230"/>
+      <c r="H54" s="230"/>
+      <c r="I54" s="230"/>
+      <c r="J54" s="230"/>
+      <c r="K54" s="230"/>
+      <c r="L54" s="230"/>
+      <c r="M54" s="230"/>
+      <c r="N54" s="230"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="224"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="224"/>
-      <c r="F55" s="224"/>
-      <c r="G55" s="224"/>
-      <c r="H55" s="224"/>
-      <c r="I55" s="224"/>
-      <c r="J55" s="224"/>
-      <c r="K55" s="224"/>
-      <c r="L55" s="224"/>
-      <c r="M55" s="224"/>
-      <c r="N55" s="224"/>
+      <c r="C55" s="230"/>
+      <c r="D55" s="230"/>
+      <c r="E55" s="230"/>
+      <c r="F55" s="230"/>
+      <c r="G55" s="230"/>
+      <c r="H55" s="230"/>
+      <c r="I55" s="230"/>
+      <c r="J55" s="230"/>
+      <c r="K55" s="230"/>
+      <c r="L55" s="230"/>
+      <c r="M55" s="230"/>
+      <c r="N55" s="230"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C56" s="168"/>
-      <c r="D56" s="168"/>
-      <c r="E56" s="168"/>
-      <c r="F56" s="168"/>
-      <c r="G56" s="168"/>
-      <c r="H56" s="168"/>
-      <c r="I56" s="168"/>
-      <c r="J56" s="168"/>
-      <c r="K56" s="168"/>
-      <c r="L56" s="168"/>
-      <c r="M56" s="168"/>
-      <c r="N56" s="168"/>
+      <c r="C56" s="167"/>
+      <c r="D56" s="167"/>
+      <c r="E56" s="167"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="167"/>
+      <c r="H56" s="167"/>
+      <c r="I56" s="167"/>
+      <c r="J56" s="167"/>
+      <c r="K56" s="167"/>
+      <c r="L56" s="167"/>
+      <c r="M56" s="167"/>
+      <c r="N56" s="167"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="224" t="s">
+      <c r="C57" s="230" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="224"/>
-      <c r="E57" s="224"/>
-      <c r="F57" s="224"/>
-      <c r="G57" s="224"/>
-      <c r="H57" s="224"/>
-      <c r="I57" s="224"/>
-      <c r="J57" s="224"/>
-      <c r="K57" s="224"/>
-      <c r="L57" s="224"/>
-      <c r="M57" s="224"/>
-      <c r="N57" s="224"/>
+      <c r="D57" s="230"/>
+      <c r="E57" s="230"/>
+      <c r="F57" s="230"/>
+      <c r="G57" s="230"/>
+      <c r="H57" s="230"/>
+      <c r="I57" s="230"/>
+      <c r="J57" s="230"/>
+      <c r="K57" s="230"/>
+      <c r="L57" s="230"/>
+      <c r="M57" s="230"/>
+      <c r="N57" s="230"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="224"/>
-      <c r="D58" s="224"/>
-      <c r="E58" s="224"/>
-      <c r="F58" s="224"/>
-      <c r="G58" s="224"/>
-      <c r="H58" s="224"/>
-      <c r="I58" s="224"/>
-      <c r="J58" s="224"/>
-      <c r="K58" s="224"/>
-      <c r="L58" s="224"/>
-      <c r="M58" s="224"/>
-      <c r="N58" s="224"/>
+      <c r="C58" s="230"/>
+      <c r="D58" s="230"/>
+      <c r="E58" s="230"/>
+      <c r="F58" s="230"/>
+      <c r="G58" s="230"/>
+      <c r="H58" s="230"/>
+      <c r="I58" s="230"/>
+      <c r="J58" s="230"/>
+      <c r="K58" s="230"/>
+      <c r="L58" s="230"/>
+      <c r="M58" s="230"/>
+      <c r="N58" s="230"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="224"/>
-      <c r="D59" s="224"/>
-      <c r="E59" s="224"/>
-      <c r="F59" s="224"/>
-      <c r="G59" s="224"/>
-      <c r="H59" s="224"/>
-      <c r="I59" s="224"/>
-      <c r="J59" s="224"/>
-      <c r="K59" s="224"/>
-      <c r="L59" s="224"/>
-      <c r="M59" s="224"/>
-      <c r="N59" s="224"/>
+      <c r="C59" s="230"/>
+      <c r="D59" s="230"/>
+      <c r="E59" s="230"/>
+      <c r="F59" s="230"/>
+      <c r="G59" s="230"/>
+      <c r="H59" s="230"/>
+      <c r="I59" s="230"/>
+      <c r="J59" s="230"/>
+      <c r="K59" s="230"/>
+      <c r="L59" s="230"/>
+      <c r="M59" s="230"/>
+      <c r="N59" s="230"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="224"/>
-      <c r="D60" s="224"/>
-      <c r="E60" s="224"/>
-      <c r="F60" s="224"/>
-      <c r="G60" s="224"/>
-      <c r="H60" s="224"/>
-      <c r="I60" s="224"/>
-      <c r="J60" s="224"/>
-      <c r="K60" s="224"/>
-      <c r="L60" s="224"/>
-      <c r="M60" s="224"/>
-      <c r="N60" s="224"/>
+      <c r="C60" s="230"/>
+      <c r="D60" s="230"/>
+      <c r="E60" s="230"/>
+      <c r="F60" s="230"/>
+      <c r="G60" s="230"/>
+      <c r="H60" s="230"/>
+      <c r="I60" s="230"/>
+      <c r="J60" s="230"/>
+      <c r="K60" s="230"/>
+      <c r="L60" s="230"/>
+      <c r="M60" s="230"/>
+      <c r="N60" s="230"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="224"/>
-      <c r="D61" s="224"/>
-      <c r="E61" s="224"/>
-      <c r="F61" s="224"/>
-      <c r="G61" s="224"/>
-      <c r="H61" s="224"/>
-      <c r="I61" s="224"/>
-      <c r="J61" s="224"/>
-      <c r="K61" s="224"/>
-      <c r="L61" s="224"/>
-      <c r="M61" s="224"/>
-      <c r="N61" s="224"/>
+      <c r="C61" s="230"/>
+      <c r="D61" s="230"/>
+      <c r="E61" s="230"/>
+      <c r="F61" s="230"/>
+      <c r="G61" s="230"/>
+      <c r="H61" s="230"/>
+      <c r="I61" s="230"/>
+      <c r="J61" s="230"/>
+      <c r="K61" s="230"/>
+      <c r="L61" s="230"/>
+      <c r="M61" s="230"/>
+      <c r="N61" s="230"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="224"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="224"/>
-      <c r="F62" s="224"/>
-      <c r="G62" s="224"/>
-      <c r="H62" s="224"/>
-      <c r="I62" s="224"/>
-      <c r="J62" s="224"/>
-      <c r="K62" s="224"/>
-      <c r="L62" s="224"/>
-      <c r="M62" s="224"/>
-      <c r="N62" s="224"/>
+      <c r="C62" s="230"/>
+      <c r="D62" s="230"/>
+      <c r="E62" s="230"/>
+      <c r="F62" s="230"/>
+      <c r="G62" s="230"/>
+      <c r="H62" s="230"/>
+      <c r="I62" s="230"/>
+      <c r="J62" s="230"/>
+      <c r="K62" s="230"/>
+      <c r="L62" s="230"/>
+      <c r="M62" s="230"/>
+      <c r="N62" s="230"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="224"/>
-      <c r="D63" s="224"/>
-      <c r="E63" s="224"/>
-      <c r="F63" s="224"/>
-      <c r="G63" s="224"/>
-      <c r="H63" s="224"/>
-      <c r="I63" s="224"/>
-      <c r="J63" s="224"/>
-      <c r="K63" s="224"/>
-      <c r="L63" s="224"/>
-      <c r="M63" s="224"/>
-      <c r="N63" s="224"/>
+      <c r="C63" s="230"/>
+      <c r="D63" s="230"/>
+      <c r="E63" s="230"/>
+      <c r="F63" s="230"/>
+      <c r="G63" s="230"/>
+      <c r="H63" s="230"/>
+      <c r="I63" s="230"/>
+      <c r="J63" s="230"/>
+      <c r="K63" s="230"/>
+      <c r="L63" s="230"/>
+      <c r="M63" s="230"/>
+      <c r="N63" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -6641,6 +6723,11 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -6648,6 +6735,170 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
+  <dimension ref="C4:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="193">
+        <v>-447223.45918396302</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="193">
+        <v>451182</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="193">
+        <v>40606.380000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="193">
+        <v>41358.350000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="193">
+        <v>37598.5</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="193">
+        <f>D11+D5</f>
+        <v>3958.5408160369843</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="193">
+        <v>40606.380000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="193">
+        <v>41358.350000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="193">
+        <v>37598.5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="193">
+        <v>-25000</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="241" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="244">
+        <f>SUM(D17:D21)</f>
+        <v>98521.770816036995</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="242"/>
+      <c r="D23" s="245"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="242"/>
+      <c r="D24" s="245"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="243"/>
+      <c r="D25" s="246"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="D22:D25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6747,10 +6998,10 @@
       <c r="O4" s="49"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="239" t="s">
+      <c r="A5" s="247" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="239" t="s">
+      <c r="B5" s="247" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -6762,7 +7013,7 @@
       <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="239" t="s">
+      <c r="F5" s="247" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -6784,16 +7035,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="239" t="s">
+      <c r="N5" s="247" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="239" t="s">
+      <c r="O5" s="247" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="240"/>
-      <c r="B6" s="240"/>
+      <c r="A6" s="248"/>
+      <c r="B6" s="248"/>
       <c r="C6" s="56" t="s">
         <v>80</v>
       </c>
@@ -6803,7 +7054,7 @@
       <c r="E6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="240"/>
+      <c r="F6" s="248"/>
       <c r="G6" s="44" t="s">
         <v>81</v>
       </c>
@@ -6823,8 +7074,8 @@
         <v>84</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="240"/>
-      <c r="O6" s="240"/>
+      <c r="N6" s="248"/>
+      <c r="O6" s="248"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
